--- a/news_daily/2026-10-08.xlsx
+++ b/news_daily/2026-10-08.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BH$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BH$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BH$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BH$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BL$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH31"/>
+  <dimension ref="A1:BL31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -526,6 +526,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -829,6 +833,26 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -841,7 +865,11 @@
           <t>US</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr"/>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Ford Motor Company</t>
@@ -875,17 +903,17 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>待人工覆核</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -938,7 +966,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>64c2c3d7374141a3bc32ffe3c8e5db76</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
           <t>298c3610ce9944a092126e67</t>
@@ -965,7 +997,7 @@
       <c r="AN2" s="2" t="inlineStr"/>
       <c r="AO2" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP2" s="2" t="inlineStr"/>
@@ -1007,6 +1039,22 @@
       </c>
       <c r="BG2" s="2" t="inlineStr"/>
       <c r="BH2" s="2" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="BJ2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -1177,184 +1225,216 @@
         </is>
       </c>
       <c r="BH3" s="3" t="inlineStr"/>
+      <c r="BI3" s="3" t="inlineStr"/>
+      <c r="BJ3" s="3" t="inlineStr"/>
+      <c r="BK3" s="3" t="inlineStr"/>
+      <c r="BL3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>AT&amp;T Inc.</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>2026-10-08T21:09:00+08:00</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Payments could come soon in $177M AT&amp;T settlement: How much will you receive?</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>0.055</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr"/>
+      <c r="Q4" s="3" t="inlineStr"/>
+      <c r="R4" s="3" t="inlineStr"/>
+      <c r="S4" s="3" t="inlineStr"/>
+      <c r="T4" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxNTGhVaHM1VlNJcTFEOGh4WHg1MU91c3NZam9rWUU5UHd0Rk1ZR2dWQ1Y0VmxEX2VaWkNPQTl2RW42UzB1blZmMk1lb3VCRXhwdDJKbmlCQW1ZV3E2RGdldlRFRWdUYWFfUV9PMWEtdndubkxPc1lTTjNxN0RUOURwMG5VcmVYOFBadnJobm1oaEJ5X1lQbDQxZ1E4WlZzOGJ4QmlTc3E5c3gyREowUkIyedIBtgFBVV95cUxNa1VaelBiUnRPZ3JVR0Z1d3REdDNtTHV5ajlFNHUtcWpxaDJRbzNKdnRqWEh2UlM3NTlqS01VcEI1T2hlUFBxTmV6RXNQeFRMb3NKc0NyUHptdzZSeXpqUG9MWU1aZU1SaWZTZFFndGZ5Y0FsU2ktSXVsX2JKb2FCN0RzT294ODdBdGFZU3JwMFhQOU5wNmNkTlplc2dmeTlwZUJ6U3dUYmU4RWs5bTZhSUxUNlBjZw?oc=5</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>The Hill</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr"/>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y4" s="3" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA4" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>2d1f22e2d82f43be94e81f9da286cdc8</t>
+        </is>
+      </c>
+      <c r="AC4" s="3" t="inlineStr">
+        <is>
+          <t>0257b77fa3158891dc098ada</t>
+        </is>
+      </c>
+      <c r="AD4" s="3" t="inlineStr">
+        <is>
+          <t>cd0647af0a2d18ec95909417</t>
+        </is>
+      </c>
+      <c r="AE4" s="3" t="inlineStr">
+        <is>
+          <t>T-REGULATORY_PENALTY-001</t>
+        </is>
+      </c>
+      <c r="AF4" s="3" t="inlineStr"/>
+      <c r="AG4" s="3" t="inlineStr"/>
+      <c r="AH4" s="3" t="inlineStr"/>
+      <c r="AI4" s="3" t="inlineStr"/>
+      <c r="AJ4" s="3" t="inlineStr"/>
+      <c r="AK4" s="3" t="inlineStr"/>
+      <c r="AL4" s="3" t="inlineStr"/>
+      <c r="AM4" s="3" t="inlineStr"/>
+      <c r="AN4" s="3" t="inlineStr"/>
+      <c r="AO4" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0.055</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr"/>
-      <c r="Q4" s="2" t="inlineStr"/>
-      <c r="R4" s="2" t="inlineStr"/>
-      <c r="S4" s="2" t="inlineStr"/>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxNTGhVaHM1VlNJcTFEOGh4WHg1MU91c3NZam9rWUU5UHd0Rk1ZR2dWQ1Y0VmxEX2VaWkNPQTl2RW42UzB1blZmMk1lb3VCRXhwdDJKbmlCQW1ZV3E2RGdldlRFRWdUYWFfUV9PMWEtdndubkxPc1lTTjNxN0RUOURwMG5VcmVYOFBadnJobm1oaEJ5X1lQbDQxZ1E4WlZzOGJ4QmlTc3E5c3gyREowUkIyedIBtgFBVV95cUxNa1VaelBiUnRPZ3JVR0Z1d3REdDNtTHV5ajlFNHUtcWpxaDJRbzNKdnRqWEh2UlM3NTlqS01VcEI1T2hlUFBxTmV6RXNQeFRMb3NKc0NyUHptdzZSeXpqUG9MWU1aZU1SaWZTZFFndGZ5Y0FsU2ktSXVsX2JKb2FCN0RzT294ODdBdGFZU3JwMFhQOU5wNmNkTlplc2dmeTlwZUJ6U3dUYmU4RWs5bTZhSUxUNlBjZw?oc=5</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>The Hill</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr"/>
-      <c r="X4" s="2" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y4" s="2" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z4" s="2" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
-      <c r="AC4" s="2" t="inlineStr">
-        <is>
-          <t>0257b77fa3158891dc098ada</t>
-        </is>
-      </c>
-      <c r="AD4" s="2" t="inlineStr">
-        <is>
-          <t>cd0647af0a2d18ec95909417</t>
-        </is>
-      </c>
-      <c r="AE4" s="2" t="inlineStr">
-        <is>
-          <t>T-REGULATORY_PENALTY-001</t>
-        </is>
-      </c>
-      <c r="AF4" s="2" t="inlineStr"/>
-      <c r="AG4" s="2" t="inlineStr"/>
-      <c r="AH4" s="2" t="inlineStr"/>
-      <c r="AI4" s="2" t="inlineStr"/>
-      <c r="AJ4" s="2" t="inlineStr"/>
-      <c r="AK4" s="2" t="inlineStr"/>
-      <c r="AL4" s="2" t="inlineStr"/>
-      <c r="AM4" s="2" t="inlineStr"/>
-      <c r="AN4" s="2" t="inlineStr"/>
-      <c r="AO4" s="2" t="inlineStr"/>
-      <c r="AP4" s="2" t="inlineStr"/>
-      <c r="AQ4" s="2" t="inlineStr"/>
-      <c r="AR4" s="2" t="inlineStr"/>
-      <c r="AS4" s="2" t="inlineStr"/>
-      <c r="AT4" s="2" t="inlineStr"/>
-      <c r="AU4" s="2" t="inlineStr"/>
-      <c r="AV4" s="2" t="inlineStr"/>
-      <c r="AW4" s="2" t="inlineStr">
+      <c r="AP4" s="3" t="inlineStr"/>
+      <c r="AQ4" s="3" t="inlineStr"/>
+      <c r="AR4" s="3" t="inlineStr"/>
+      <c r="AS4" s="3" t="inlineStr"/>
+      <c r="AT4" s="3" t="inlineStr"/>
+      <c r="AU4" s="3" t="inlineStr"/>
+      <c r="AV4" s="3" t="inlineStr"/>
+      <c r="AW4" s="3" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX4" s="2" t="inlineStr"/>
-      <c r="AY4" s="2" t="inlineStr"/>
-      <c r="AZ4" s="2" t="inlineStr"/>
-      <c r="BA4" s="2" t="inlineStr"/>
-      <c r="BB4" s="2" t="inlineStr">
+      <c r="AX4" s="3" t="inlineStr"/>
+      <c r="AY4" s="3" t="inlineStr"/>
+      <c r="AZ4" s="3" t="inlineStr"/>
+      <c r="BA4" s="3" t="inlineStr"/>
+      <c r="BB4" s="3" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="BC4" s="2" t="inlineStr">
+      <c r="BC4" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD4" s="2" t="inlineStr"/>
-      <c r="BE4" s="2" t="inlineStr">
+      <c r="BD4" s="3" t="inlineStr"/>
+      <c r="BE4" s="3" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF4" s="2" t="inlineStr">
+      <c r="BF4" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG4" s="2" t="inlineStr">
+      <c r="BG4" s="3" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH4" s="2" t="inlineStr"/>
+      <c r="BH4" s="3" t="inlineStr"/>
+      <c r="BI4" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ4" s="3" t="inlineStr"/>
+      <c r="BK4" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL4" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -1533,6 +1613,10 @@
         </is>
       </c>
       <c r="BH5" s="4" t="inlineStr"/>
+      <c r="BI5" s="4" t="inlineStr"/>
+      <c r="BJ5" s="4" t="inlineStr"/>
+      <c r="BK5" s="4" t="inlineStr"/>
+      <c r="BL5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -1703,176 +1787,208 @@
         </is>
       </c>
       <c r="BH6" s="4" t="inlineStr"/>
+      <c r="BI6" s="4" t="inlineStr"/>
+      <c r="BJ6" s="4" t="inlineStr"/>
+      <c r="BK6" s="4" t="inlineStr"/>
+      <c r="BL6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>XOM</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>ExxonMobil</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>2026-10-08T20:10:56+08:00</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>Update: ExxonMobil Director Vote Prompts US SEC Investigation Into Climate Action 100+; Regulator Pursues No Action Against Group</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>監管調查</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>'-0.02</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr"/>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr"/>
+      <c r="S7" s="3" t="inlineStr"/>
+      <c r="T7" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOWHN6U2Vwdl9tNGFVRHFjS0Z1cG5ocXk0bTNOQ2lSS1hPU3h4am1wSHdnTXVjM0RRVVZac21CdEVvd3BXbXIwbGtoT245RWlZOURPMGkzcGhudC1iTkJHaDdLeGpPRTNId1IzUjZYUXVmVFVMWkJYZ2tBOGpZRHpwVlAxc01WQnVDZVVKUVc1VDVPVXVQUHkw?oc=5</t>
+        </is>
+      </c>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="W7" s="3" t="inlineStr"/>
+      <c r="X7" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y7" s="3" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z7" s="3" t="inlineStr">
+        <is>
+          <t>SEC investigation</t>
+        </is>
+      </c>
+      <c r="AA7" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t>5c5171c3bd8249cfb629eb30ddaa42c7</t>
+        </is>
+      </c>
+      <c r="AC7" s="3" t="inlineStr">
+        <is>
+          <t>933ef7caf63052209e76d5c9</t>
+        </is>
+      </c>
+      <c r="AD7" s="3" t="inlineStr">
+        <is>
+          <t>b18ab0e7b0df2c6140112fef</t>
+        </is>
+      </c>
+      <c r="AE7" s="3" t="inlineStr">
+        <is>
+          <t>XOM-REGULATORY_INVESTIGATION-001</t>
+        </is>
+      </c>
+      <c r="AF7" s="3" t="inlineStr"/>
+      <c r="AG7" s="3" t="inlineStr"/>
+      <c r="AH7" s="3" t="inlineStr"/>
+      <c r="AI7" s="3" t="inlineStr"/>
+      <c r="AJ7" s="3" t="inlineStr"/>
+      <c r="AK7" s="3" t="inlineStr"/>
+      <c r="AL7" s="3" t="inlineStr"/>
+      <c r="AM7" s="3" t="inlineStr"/>
+      <c r="AN7" s="3" t="inlineStr"/>
+      <c r="AO7" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>'-0.02</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr"/>
-      <c r="Q7" s="2" t="inlineStr"/>
-      <c r="R7" s="2" t="inlineStr"/>
-      <c r="S7" s="2" t="inlineStr"/>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOWHN6U2Vwdl9tNGFVRHFjS0Z1cG5ocXk0bTNOQ2lSS1hPU3h4am1wSHdnTXVjM0RRVVZac21CdEVvd3BXbXIwbGtoT245RWlZOURPMGkzcGhudC1iTkJHaDdLeGpPRTNId1IzUjZYUXVmVFVMWkJYZ2tBOGpZRHpwVlAxc01WQnVDZVVKUVc1VDVPVXVQUHkw?oc=5</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr"/>
-      <c r="X7" s="2" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y7" s="2" t="inlineStr">
-        <is>
-          <t>REGULATORY_INVESTIGATION</t>
-        </is>
-      </c>
-      <c r="Z7" s="2" t="inlineStr">
-        <is>
-          <t>SEC investigation</t>
-        </is>
-      </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
-      <c r="AC7" s="2" t="inlineStr">
-        <is>
-          <t>933ef7caf63052209e76d5c9</t>
-        </is>
-      </c>
-      <c r="AD7" s="2" t="inlineStr">
-        <is>
-          <t>b18ab0e7b0df2c6140112fef</t>
-        </is>
-      </c>
-      <c r="AE7" s="2" t="inlineStr">
-        <is>
-          <t>XOM-REGULATORY_INVESTIGATION-001</t>
-        </is>
-      </c>
-      <c r="AF7" s="2" t="inlineStr"/>
-      <c r="AG7" s="2" t="inlineStr"/>
-      <c r="AH7" s="2" t="inlineStr"/>
-      <c r="AI7" s="2" t="inlineStr"/>
-      <c r="AJ7" s="2" t="inlineStr"/>
-      <c r="AK7" s="2" t="inlineStr"/>
-      <c r="AL7" s="2" t="inlineStr"/>
-      <c r="AM7" s="2" t="inlineStr"/>
-      <c r="AN7" s="2" t="inlineStr"/>
-      <c r="AO7" s="2" t="inlineStr"/>
-      <c r="AP7" s="2" t="inlineStr"/>
-      <c r="AQ7" s="2" t="inlineStr"/>
-      <c r="AR7" s="2" t="inlineStr"/>
-      <c r="AS7" s="2" t="inlineStr"/>
-      <c r="AT7" s="2" t="inlineStr"/>
-      <c r="AU7" s="2" t="inlineStr"/>
-      <c r="AV7" s="2" t="inlineStr"/>
-      <c r="AW7" s="2" t="inlineStr"/>
-      <c r="AX7" s="2" t="inlineStr"/>
-      <c r="AY7" s="2" t="inlineStr"/>
-      <c r="AZ7" s="2" t="inlineStr"/>
-      <c r="BA7" s="2" t="inlineStr"/>
-      <c r="BB7" s="2" t="inlineStr">
+      <c r="AP7" s="3" t="inlineStr"/>
+      <c r="AQ7" s="3" t="inlineStr"/>
+      <c r="AR7" s="3" t="inlineStr"/>
+      <c r="AS7" s="3" t="inlineStr"/>
+      <c r="AT7" s="3" t="inlineStr"/>
+      <c r="AU7" s="3" t="inlineStr"/>
+      <c r="AV7" s="3" t="inlineStr"/>
+      <c r="AW7" s="3" t="inlineStr"/>
+      <c r="AX7" s="3" t="inlineStr"/>
+      <c r="AY7" s="3" t="inlineStr"/>
+      <c r="AZ7" s="3" t="inlineStr"/>
+      <c r="BA7" s="3" t="inlineStr"/>
+      <c r="BB7" s="3" t="inlineStr">
         <is>
           <t>XOM</t>
         </is>
       </c>
-      <c r="BC7" s="2" t="inlineStr">
+      <c r="BC7" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD7" s="2" t="inlineStr"/>
-      <c r="BE7" s="2" t="inlineStr">
+      <c r="BD7" s="3" t="inlineStr"/>
+      <c r="BE7" s="3" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF7" s="2" t="inlineStr"/>
-      <c r="BG7" s="2" t="inlineStr">
+      <c r="BF7" s="3" t="inlineStr"/>
+      <c r="BG7" s="3" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH7" s="2" t="inlineStr"/>
+      <c r="BH7" s="3" t="inlineStr"/>
+      <c r="BI7" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ7" s="3" t="inlineStr"/>
+      <c r="BK7" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL7" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -2051,6 +2167,10 @@
         </is>
       </c>
       <c r="BH8" s="3" t="inlineStr"/>
+      <c r="BI8" s="3" t="inlineStr"/>
+      <c r="BJ8" s="3" t="inlineStr"/>
+      <c r="BK8" s="3" t="inlineStr"/>
+      <c r="BL8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -2221,176 +2341,208 @@
         </is>
       </c>
       <c r="BH9" s="4" t="inlineStr"/>
+      <c r="BI9" s="4" t="inlineStr"/>
+      <c r="BJ9" s="4" t="inlineStr"/>
+      <c r="BK9" s="4" t="inlineStr"/>
+      <c r="BL9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>XOM</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>ExxonMobil</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>2026-10-08T18:29:34+08:00</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>ExxonMobil Director Vote Prompts US SEC Investigation Into Climate Action 100+; Regulator Pursues No Action Against Group</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>監管調查</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>'-0.069</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr"/>
+      <c r="Q10" s="3" t="inlineStr"/>
+      <c r="R10" s="3" t="inlineStr"/>
+      <c r="S10" s="3" t="inlineStr"/>
+      <c r="T10" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQam9qUlRFMDNUX1duNG40dDlEWTBpeHZwRXpVWFlTRjdwXzF2RzRSRFRXRmEwOTlPUE9DQ3lLQ0NjYnl0aTMydmtTWXBoUW1QenBqS0pkWFZOS29xSkNacGJlMkp6Wl90ZWlOeWVMU3ZoSWFsY0t1OFlkbGJLbktybzgwb3AzZ0tCNV9yVkljSndNSTdmMTdR?oc=5</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="W10" s="3" t="inlineStr"/>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y10" s="3" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
+          <t>SEC investigation</t>
+        </is>
+      </c>
+      <c r="AA10" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" s="3" t="inlineStr">
+        <is>
+          <t>c9d85d31a2674a6ab44673a8732ac025</t>
+        </is>
+      </c>
+      <c r="AC10" s="3" t="inlineStr">
+        <is>
+          <t>52e928852f367f84def58be5</t>
+        </is>
+      </c>
+      <c r="AD10" s="3" t="inlineStr">
+        <is>
+          <t>a853d138cb477793c8bdce64</t>
+        </is>
+      </c>
+      <c r="AE10" s="3" t="inlineStr">
+        <is>
+          <t>XOM-REGULATORY_INVESTIGATION-001</t>
+        </is>
+      </c>
+      <c r="AF10" s="3" t="inlineStr"/>
+      <c r="AG10" s="3" t="inlineStr"/>
+      <c r="AH10" s="3" t="inlineStr"/>
+      <c r="AI10" s="3" t="inlineStr"/>
+      <c r="AJ10" s="3" t="inlineStr"/>
+      <c r="AK10" s="3" t="inlineStr"/>
+      <c r="AL10" s="3" t="inlineStr"/>
+      <c r="AM10" s="3" t="inlineStr"/>
+      <c r="AN10" s="3" t="inlineStr"/>
+      <c r="AO10" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>'-0.069</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr"/>
-      <c r="Q10" s="2" t="inlineStr"/>
-      <c r="R10" s="2" t="inlineStr"/>
-      <c r="S10" s="2" t="inlineStr"/>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQam9qUlRFMDNUX1duNG40dDlEWTBpeHZwRXpVWFlTRjdwXzF2RzRSRFRXRmEwOTlPUE9DQ3lLQ0NjYnl0aTMydmtTWXBoUW1QenBqS0pkWFZOS29xSkNacGJlMkp6Wl90ZWlOeWVMU3ZoSWFsY0t1OFlkbGJLbktybzgwb3AzZ0tCNV9yVkljSndNSTdmMTdR?oc=5</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr"/>
-      <c r="X10" s="2" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y10" s="2" t="inlineStr">
-        <is>
-          <t>REGULATORY_INVESTIGATION</t>
-        </is>
-      </c>
-      <c r="Z10" s="2" t="inlineStr">
-        <is>
-          <t>SEC investigation</t>
-        </is>
-      </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="inlineStr"/>
-      <c r="AC10" s="2" t="inlineStr">
-        <is>
-          <t>52e928852f367f84def58be5</t>
-        </is>
-      </c>
-      <c r="AD10" s="2" t="inlineStr">
-        <is>
-          <t>a853d138cb477793c8bdce64</t>
-        </is>
-      </c>
-      <c r="AE10" s="2" t="inlineStr">
-        <is>
-          <t>XOM-REGULATORY_INVESTIGATION-001</t>
-        </is>
-      </c>
-      <c r="AF10" s="2" t="inlineStr"/>
-      <c r="AG10" s="2" t="inlineStr"/>
-      <c r="AH10" s="2" t="inlineStr"/>
-      <c r="AI10" s="2" t="inlineStr"/>
-      <c r="AJ10" s="2" t="inlineStr"/>
-      <c r="AK10" s="2" t="inlineStr"/>
-      <c r="AL10" s="2" t="inlineStr"/>
-      <c r="AM10" s="2" t="inlineStr"/>
-      <c r="AN10" s="2" t="inlineStr"/>
-      <c r="AO10" s="2" t="inlineStr"/>
-      <c r="AP10" s="2" t="inlineStr"/>
-      <c r="AQ10" s="2" t="inlineStr"/>
-      <c r="AR10" s="2" t="inlineStr"/>
-      <c r="AS10" s="2" t="inlineStr"/>
-      <c r="AT10" s="2" t="inlineStr"/>
-      <c r="AU10" s="2" t="inlineStr"/>
-      <c r="AV10" s="2" t="inlineStr"/>
-      <c r="AW10" s="2" t="inlineStr"/>
-      <c r="AX10" s="2" t="inlineStr"/>
-      <c r="AY10" s="2" t="inlineStr"/>
-      <c r="AZ10" s="2" t="inlineStr"/>
-      <c r="BA10" s="2" t="inlineStr"/>
-      <c r="BB10" s="2" t="inlineStr">
+      <c r="AP10" s="3" t="inlineStr"/>
+      <c r="AQ10" s="3" t="inlineStr"/>
+      <c r="AR10" s="3" t="inlineStr"/>
+      <c r="AS10" s="3" t="inlineStr"/>
+      <c r="AT10" s="3" t="inlineStr"/>
+      <c r="AU10" s="3" t="inlineStr"/>
+      <c r="AV10" s="3" t="inlineStr"/>
+      <c r="AW10" s="3" t="inlineStr"/>
+      <c r="AX10" s="3" t="inlineStr"/>
+      <c r="AY10" s="3" t="inlineStr"/>
+      <c r="AZ10" s="3" t="inlineStr"/>
+      <c r="BA10" s="3" t="inlineStr"/>
+      <c r="BB10" s="3" t="inlineStr">
         <is>
           <t>XOM</t>
         </is>
       </c>
-      <c r="BC10" s="2" t="inlineStr">
+      <c r="BC10" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD10" s="2" t="inlineStr"/>
-      <c r="BE10" s="2" t="inlineStr">
+      <c r="BD10" s="3" t="inlineStr"/>
+      <c r="BE10" s="3" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF10" s="2" t="inlineStr"/>
-      <c r="BG10" s="2" t="inlineStr">
+      <c r="BF10" s="3" t="inlineStr"/>
+      <c r="BG10" s="3" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH10" s="2" t="inlineStr"/>
+      <c r="BH10" s="3" t="inlineStr"/>
+      <c r="BI10" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ10" s="3" t="inlineStr"/>
+      <c r="BK10" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL10" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -2561,6 +2713,10 @@
         </is>
       </c>
       <c r="BH11" s="3" t="inlineStr"/>
+      <c r="BI11" s="3" t="inlineStr"/>
+      <c r="BJ11" s="3" t="inlineStr"/>
+      <c r="BK11" s="3" t="inlineStr"/>
+      <c r="BL11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -2739,6 +2895,10 @@
         </is>
       </c>
       <c r="BH12" s="3" t="inlineStr"/>
+      <c r="BI12" s="3" t="inlineStr"/>
+      <c r="BJ12" s="3" t="inlineStr"/>
+      <c r="BK12" s="3" t="inlineStr"/>
+      <c r="BL12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -2917,6 +3077,10 @@
         </is>
       </c>
       <c r="BH13" s="3" t="inlineStr"/>
+      <c r="BI13" s="3" t="inlineStr"/>
+      <c r="BJ13" s="3" t="inlineStr"/>
+      <c r="BK13" s="3" t="inlineStr"/>
+      <c r="BL13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -3087,6 +3251,10 @@
         </is>
       </c>
       <c r="BH14" s="3" t="inlineStr"/>
+      <c r="BI14" s="3" t="inlineStr"/>
+      <c r="BJ14" s="3" t="inlineStr"/>
+      <c r="BK14" s="3" t="inlineStr"/>
+      <c r="BL14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -3241,6 +3409,10 @@
       <c r="BF15" s="3" t="inlineStr"/>
       <c r="BG15" s="3" t="inlineStr"/>
       <c r="BH15" s="3" t="inlineStr"/>
+      <c r="BI15" s="3" t="inlineStr"/>
+      <c r="BJ15" s="3" t="inlineStr"/>
+      <c r="BK15" s="3" t="inlineStr"/>
+      <c r="BL15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -3419,6 +3591,10 @@
         </is>
       </c>
       <c r="BH16" s="4" t="inlineStr"/>
+      <c r="BI16" s="4" t="inlineStr"/>
+      <c r="BJ16" s="4" t="inlineStr"/>
+      <c r="BK16" s="4" t="inlineStr"/>
+      <c r="BL16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -3589,6 +3765,10 @@
         </is>
       </c>
       <c r="BH17" s="4" t="inlineStr"/>
+      <c r="BI17" s="4" t="inlineStr"/>
+      <c r="BJ17" s="4" t="inlineStr"/>
+      <c r="BK17" s="4" t="inlineStr"/>
+      <c r="BL17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -3767,176 +3947,208 @@
         </is>
       </c>
       <c r="BH18" s="3" t="inlineStr"/>
+      <c r="BI18" s="3" t="inlineStr"/>
+      <c r="BJ18" s="3" t="inlineStr"/>
+      <c r="BK18" s="3" t="inlineStr"/>
+      <c r="BL18" s="3" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>DUK</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>Duke Energy</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>2026-10-08T07:44:03+08:00</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t>Duke Energy Reaches Settlement Requiring Data Centers To Pay Upfront Grid Connection Costs In N.C.</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr"/>
-      <c r="M19" s="2" t="inlineStr">
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t>'-0.904</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr"/>
+      <c r="Q19" s="3" t="inlineStr"/>
+      <c r="R19" s="3" t="inlineStr"/>
+      <c r="S19" s="3" t="inlineStr"/>
+      <c r="T19" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U19" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQSlN2VkVfS3hUVU5EQmh6N2JCa0cwS1FJYUxoWmFqM0JTeWNTLU9VbEtOa083eTd3b3FVOWdaNFUtRFBkVkhWZGo1V2VfR3JhYzlILVNQZHRPNXppT0NaMGJUV0I3TVViMUNkRDdVakdnU0ZMcUtCUzM1Ums0WFhCZzhDSEUzU0ZsOXF1UndvTWcxNmQxVFJBYjJWRWFTQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="V19" s="3" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="W19" s="3" t="inlineStr"/>
+      <c r="X19" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y19" s="3" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z19" s="3" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA19" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" s="3" t="inlineStr">
+        <is>
+          <t>d50af1b4960b428aa871510fe69aeec7</t>
+        </is>
+      </c>
+      <c r="AC19" s="3" t="inlineStr">
+        <is>
+          <t>489ddfc61d708d0afe70f27e</t>
+        </is>
+      </c>
+      <c r="AD19" s="3" t="inlineStr">
+        <is>
+          <t>055c89085873416a44a38958</t>
+        </is>
+      </c>
+      <c r="AE19" s="3" t="inlineStr">
+        <is>
+          <t>DUK-REGULATORY_PENALTY-001</t>
+        </is>
+      </c>
+      <c r="AF19" s="3" t="inlineStr"/>
+      <c r="AG19" s="3" t="inlineStr"/>
+      <c r="AH19" s="3" t="inlineStr"/>
+      <c r="AI19" s="3" t="inlineStr"/>
+      <c r="AJ19" s="3" t="inlineStr"/>
+      <c r="AK19" s="3" t="inlineStr"/>
+      <c r="AL19" s="3" t="inlineStr"/>
+      <c r="AM19" s="3" t="inlineStr"/>
+      <c r="AN19" s="3" t="inlineStr"/>
+      <c r="AO19" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>'-0.904</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr"/>
-      <c r="Q19" s="2" t="inlineStr"/>
-      <c r="R19" s="2" t="inlineStr"/>
-      <c r="S19" s="2" t="inlineStr"/>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQSlN2VkVfS3hUVU5EQmh6N2JCa0cwS1FJYUxoWmFqM0JTeWNTLU9VbEtOa083eTd3b3FVOWdaNFUtRFBkVkhWZGo1V2VfR3JhYzlILVNQZHRPNXppT0NaMGJUV0I3TVViMUNkRDdVakdnU0ZMcUtCUzM1Ums0WFhCZzhDSEUzU0ZsOXF1UndvTWcxNmQxVFJBYjJWRWFTQQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr"/>
-      <c r="X19" s="2" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y19" s="2" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z19" s="2" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB19" s="2" t="inlineStr"/>
-      <c r="AC19" s="2" t="inlineStr">
-        <is>
-          <t>489ddfc61d708d0afe70f27e</t>
-        </is>
-      </c>
-      <c r="AD19" s="2" t="inlineStr">
-        <is>
-          <t>055c89085873416a44a38958</t>
-        </is>
-      </c>
-      <c r="AE19" s="2" t="inlineStr">
-        <is>
-          <t>DUK-REGULATORY_PENALTY-001</t>
-        </is>
-      </c>
-      <c r="AF19" s="2" t="inlineStr"/>
-      <c r="AG19" s="2" t="inlineStr"/>
-      <c r="AH19" s="2" t="inlineStr"/>
-      <c r="AI19" s="2" t="inlineStr"/>
-      <c r="AJ19" s="2" t="inlineStr"/>
-      <c r="AK19" s="2" t="inlineStr"/>
-      <c r="AL19" s="2" t="inlineStr"/>
-      <c r="AM19" s="2" t="inlineStr"/>
-      <c r="AN19" s="2" t="inlineStr"/>
-      <c r="AO19" s="2" t="inlineStr"/>
-      <c r="AP19" s="2" t="inlineStr"/>
-      <c r="AQ19" s="2" t="inlineStr"/>
-      <c r="AR19" s="2" t="inlineStr"/>
-      <c r="AS19" s="2" t="inlineStr"/>
-      <c r="AT19" s="2" t="inlineStr"/>
-      <c r="AU19" s="2" t="inlineStr"/>
-      <c r="AV19" s="2" t="inlineStr"/>
-      <c r="AW19" s="2" t="inlineStr"/>
-      <c r="AX19" s="2" t="inlineStr"/>
-      <c r="AY19" s="2" t="inlineStr"/>
-      <c r="AZ19" s="2" t="inlineStr"/>
-      <c r="BA19" s="2" t="inlineStr"/>
-      <c r="BB19" s="2" t="inlineStr">
+      <c r="AP19" s="3" t="inlineStr"/>
+      <c r="AQ19" s="3" t="inlineStr"/>
+      <c r="AR19" s="3" t="inlineStr"/>
+      <c r="AS19" s="3" t="inlineStr"/>
+      <c r="AT19" s="3" t="inlineStr"/>
+      <c r="AU19" s="3" t="inlineStr"/>
+      <c r="AV19" s="3" t="inlineStr"/>
+      <c r="AW19" s="3" t="inlineStr"/>
+      <c r="AX19" s="3" t="inlineStr"/>
+      <c r="AY19" s="3" t="inlineStr"/>
+      <c r="AZ19" s="3" t="inlineStr"/>
+      <c r="BA19" s="3" t="inlineStr"/>
+      <c r="BB19" s="3" t="inlineStr">
         <is>
           <t>DUK</t>
         </is>
       </c>
-      <c r="BC19" s="2" t="inlineStr">
+      <c r="BC19" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD19" s="2" t="inlineStr"/>
-      <c r="BE19" s="2" t="inlineStr">
+      <c r="BD19" s="3" t="inlineStr"/>
+      <c r="BE19" s="3" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF19" s="2" t="inlineStr"/>
-      <c r="BG19" s="2" t="inlineStr">
+      <c r="BF19" s="3" t="inlineStr"/>
+      <c r="BG19" s="3" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH19" s="2" t="inlineStr"/>
+      <c r="BH19" s="3" t="inlineStr"/>
+      <c r="BI19" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ19" s="3" t="inlineStr"/>
+      <c r="BK19" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL19" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -4107,184 +4319,216 @@
         </is>
       </c>
       <c r="BH20" s="3" t="inlineStr"/>
+      <c r="BI20" s="3" t="inlineStr"/>
+      <c r="BJ20" s="3" t="inlineStr"/>
+      <c r="BK20" s="3" t="inlineStr"/>
+      <c r="BL20" s="3" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>CMS</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>CMS Energy Corporation Common Stock</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E21" s="3" t="inlineStr">
         <is>
           <t>2026-10-08T05:01:21+08:00</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t>Nursing home takes fight over CMS penalty authority to Supreme Court</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr"/>
-      <c r="M21" s="2" t="inlineStr">
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>'-0.484</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr"/>
+      <c r="Q21" s="3" t="inlineStr"/>
+      <c r="R21" s="3" t="inlineStr"/>
+      <c r="S21" s="3" t="inlineStr"/>
+      <c r="T21" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U21" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPamcyWWVnQ09CSXJmMWQ0ZjJxXzZNd01fT3pET20yLXpPS09LZWRqMmdEWUdFWklhZHlXYm1JNFFpUUVvME4tWmQyUHVZZXlqYkZuQWJic1BQSWktLUpTX1RtVkVLUy1qV2o3Zmk5Z3ZsekhXTUFWdi14WWU0OUs3dDdVcGc5WnNwMU5WWVozMGJFUFRNdUNxMlFZWHFWWVdVeVE?oc=5</t>
+        </is>
+      </c>
+      <c r="V21" s="3" t="inlineStr">
+        <is>
+          <t>McKnight's Long-Term Care News</t>
+        </is>
+      </c>
+      <c r="W21" s="3" t="inlineStr"/>
+      <c r="X21" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y21" s="3" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z21" s="3" t="inlineStr">
+        <is>
+          <t>penalty</t>
+        </is>
+      </c>
+      <c r="AA21" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB21" s="3" t="inlineStr">
+        <is>
+          <t>87e3b3072bda425ab96d60d57f5f44f7</t>
+        </is>
+      </c>
+      <c r="AC21" s="3" t="inlineStr">
+        <is>
+          <t>658a733daaf57ab96f019658</t>
+        </is>
+      </c>
+      <c r="AD21" s="3" t="inlineStr">
+        <is>
+          <t>0a40d2da69a8540dbe451850</t>
+        </is>
+      </c>
+      <c r="AE21" s="3" t="inlineStr">
+        <is>
+          <t>CMS-REGULATORY_PENALTY-001</t>
+        </is>
+      </c>
+      <c r="AF21" s="3" t="inlineStr"/>
+      <c r="AG21" s="3" t="inlineStr"/>
+      <c r="AH21" s="3" t="inlineStr"/>
+      <c r="AI21" s="3" t="inlineStr"/>
+      <c r="AJ21" s="3" t="inlineStr"/>
+      <c r="AK21" s="3" t="inlineStr"/>
+      <c r="AL21" s="3" t="inlineStr"/>
+      <c r="AM21" s="3" t="inlineStr"/>
+      <c r="AN21" s="3" t="inlineStr"/>
+      <c r="AO21" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>'-0.484</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr"/>
-      <c r="Q21" s="2" t="inlineStr"/>
-      <c r="R21" s="2" t="inlineStr"/>
-      <c r="S21" s="2" t="inlineStr"/>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPamcyWWVnQ09CSXJmMWQ0ZjJxXzZNd01fT3pET20yLXpPS09LZWRqMmdEWUdFWklhZHlXYm1JNFFpUUVvME4tWmQyUHVZZXlqYkZuQWJic1BQSWktLUpTX1RtVkVLUy1qV2o3Zmk5Z3ZsekhXTUFWdi14WWU0OUs3dDdVcGc5WnNwMU5WWVozMGJFUFRNdUNxMlFZWHFWWVdVeVE?oc=5</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>McKnight's Long-Term Care News</t>
-        </is>
-      </c>
-      <c r="W21" s="2" t="inlineStr"/>
-      <c r="X21" s="2" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y21" s="2" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z21" s="2" t="inlineStr">
-        <is>
-          <t>penalty</t>
-        </is>
-      </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB21" s="2" t="inlineStr"/>
-      <c r="AC21" s="2" t="inlineStr">
-        <is>
-          <t>658a733daaf57ab96f019658</t>
-        </is>
-      </c>
-      <c r="AD21" s="2" t="inlineStr">
-        <is>
-          <t>0a40d2da69a8540dbe451850</t>
-        </is>
-      </c>
-      <c r="AE21" s="2" t="inlineStr">
-        <is>
-          <t>CMS-REGULATORY_PENALTY-001</t>
-        </is>
-      </c>
-      <c r="AF21" s="2" t="inlineStr"/>
-      <c r="AG21" s="2" t="inlineStr"/>
-      <c r="AH21" s="2" t="inlineStr"/>
-      <c r="AI21" s="2" t="inlineStr"/>
-      <c r="AJ21" s="2" t="inlineStr"/>
-      <c r="AK21" s="2" t="inlineStr"/>
-      <c r="AL21" s="2" t="inlineStr"/>
-      <c r="AM21" s="2" t="inlineStr"/>
-      <c r="AN21" s="2" t="inlineStr"/>
-      <c r="AO21" s="2" t="inlineStr"/>
-      <c r="AP21" s="2" t="inlineStr"/>
-      <c r="AQ21" s="2" t="inlineStr"/>
-      <c r="AR21" s="2" t="inlineStr"/>
-      <c r="AS21" s="2" t="inlineStr"/>
-      <c r="AT21" s="2" t="inlineStr"/>
-      <c r="AU21" s="2" t="inlineStr"/>
-      <c r="AV21" s="2" t="inlineStr"/>
-      <c r="AW21" s="2" t="inlineStr">
+      <c r="AP21" s="3" t="inlineStr"/>
+      <c r="AQ21" s="3" t="inlineStr"/>
+      <c r="AR21" s="3" t="inlineStr"/>
+      <c r="AS21" s="3" t="inlineStr"/>
+      <c r="AT21" s="3" t="inlineStr"/>
+      <c r="AU21" s="3" t="inlineStr"/>
+      <c r="AV21" s="3" t="inlineStr"/>
+      <c r="AW21" s="3" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX21" s="2" t="inlineStr"/>
-      <c r="AY21" s="2" t="inlineStr"/>
-      <c r="AZ21" s="2" t="inlineStr"/>
-      <c r="BA21" s="2" t="inlineStr"/>
-      <c r="BB21" s="2" t="inlineStr">
+      <c r="AX21" s="3" t="inlineStr"/>
+      <c r="AY21" s="3" t="inlineStr"/>
+      <c r="AZ21" s="3" t="inlineStr"/>
+      <c r="BA21" s="3" t="inlineStr"/>
+      <c r="BB21" s="3" t="inlineStr">
         <is>
           <t>CMS</t>
         </is>
       </c>
-      <c r="BC21" s="2" t="inlineStr">
+      <c r="BC21" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD21" s="2" t="inlineStr"/>
-      <c r="BE21" s="2" t="inlineStr">
+      <c r="BD21" s="3" t="inlineStr"/>
+      <c r="BE21" s="3" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF21" s="2" t="inlineStr">
+      <c r="BF21" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG21" s="2" t="inlineStr">
+      <c r="BG21" s="3" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH21" s="2" t="inlineStr"/>
+      <c r="BH21" s="3" t="inlineStr"/>
+      <c r="BI21" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ21" s="3" t="inlineStr"/>
+      <c r="BK21" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL21" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
@@ -4439,176 +4683,208 @@
       <c r="BF22" s="3" t="inlineStr"/>
       <c r="BG22" s="3" t="inlineStr"/>
       <c r="BH22" s="3" t="inlineStr"/>
+      <c r="BI22" s="3" t="inlineStr"/>
+      <c r="BJ22" s="3" t="inlineStr"/>
+      <c r="BK22" s="3" t="inlineStr"/>
+      <c r="BL22" s="3" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>DUK</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>Duke Energy</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E23" s="3" t="inlineStr">
         <is>
           <t>2026-10-08T04:13:03+08:00</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F23" s="3" t="inlineStr">
         <is>
           <t>Duke Energy, NC Public Staff Reach Settlement on Data Center Costs</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr"/>
-      <c r="M23" s="2" t="inlineStr">
+      <c r="G23" s="3" t="inlineStr"/>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O23" s="3" t="inlineStr">
+        <is>
+          <t>'-0.87</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="inlineStr"/>
+      <c r="Q23" s="3" t="inlineStr"/>
+      <c r="R23" s="3" t="inlineStr"/>
+      <c r="S23" s="3" t="inlineStr"/>
+      <c r="T23" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U23" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPY0NlM1pNMDZnZlR2bjliMmdxX0hwRng0OEV5elcxR3VyX3h1d213T3NoeWdkdjVLMG9UTmJRR0dCeUdmcjVSZmpRLUtqSTM2Qk5TbTYzU1RPRnNyTTVYRl9vMHhvUXgzU092QUcxR19RcjdnRUtZa1N2YXNPMW44R0Q5dFJad3gxRzZDQ1h1eDA?oc=5</t>
+        </is>
+      </c>
+      <c r="V23" s="3" t="inlineStr">
+        <is>
+          <t>Unite.AI</t>
+        </is>
+      </c>
+      <c r="W23" s="3" t="inlineStr"/>
+      <c r="X23" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y23" s="3" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z23" s="3" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA23" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB23" s="3" t="inlineStr">
+        <is>
+          <t>fdfec1c29a2d42138c65145816f37997</t>
+        </is>
+      </c>
+      <c r="AC23" s="3" t="inlineStr">
+        <is>
+          <t>18411cab75cb71cb78f93e94</t>
+        </is>
+      </c>
+      <c r="AD23" s="3" t="inlineStr">
+        <is>
+          <t>9b059848cb04eeb5f0c3f583</t>
+        </is>
+      </c>
+      <c r="AE23" s="3" t="inlineStr">
+        <is>
+          <t>DUK-REGULATORY_PENALTY-001</t>
+        </is>
+      </c>
+      <c r="AF23" s="3" t="inlineStr"/>
+      <c r="AG23" s="3" t="inlineStr"/>
+      <c r="AH23" s="3" t="inlineStr"/>
+      <c r="AI23" s="3" t="inlineStr"/>
+      <c r="AJ23" s="3" t="inlineStr"/>
+      <c r="AK23" s="3" t="inlineStr"/>
+      <c r="AL23" s="3" t="inlineStr"/>
+      <c r="AM23" s="3" t="inlineStr"/>
+      <c r="AN23" s="3" t="inlineStr"/>
+      <c r="AO23" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>'-0.87</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr"/>
-      <c r="Q23" s="2" t="inlineStr"/>
-      <c r="R23" s="2" t="inlineStr"/>
-      <c r="S23" s="2" t="inlineStr"/>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPY0NlM1pNMDZnZlR2bjliMmdxX0hwRng0OEV5elcxR3VyX3h1d213T3NoeWdkdjVLMG9UTmJRR0dCeUdmcjVSZmpRLUtqSTM2Qk5TbTYzU1RPRnNyTTVYRl9vMHhvUXgzU092QUcxR19RcjdnRUtZa1N2YXNPMW44R0Q5dFJad3gxRzZDQ1h1eDA?oc=5</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>Unite.AI</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr"/>
-      <c r="X23" s="2" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y23" s="2" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z23" s="2" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB23" s="2" t="inlineStr"/>
-      <c r="AC23" s="2" t="inlineStr">
-        <is>
-          <t>18411cab75cb71cb78f93e94</t>
-        </is>
-      </c>
-      <c r="AD23" s="2" t="inlineStr">
-        <is>
-          <t>9b059848cb04eeb5f0c3f583</t>
-        </is>
-      </c>
-      <c r="AE23" s="2" t="inlineStr">
-        <is>
-          <t>DUK-REGULATORY_PENALTY-001</t>
-        </is>
-      </c>
-      <c r="AF23" s="2" t="inlineStr"/>
-      <c r="AG23" s="2" t="inlineStr"/>
-      <c r="AH23" s="2" t="inlineStr"/>
-      <c r="AI23" s="2" t="inlineStr"/>
-      <c r="AJ23" s="2" t="inlineStr"/>
-      <c r="AK23" s="2" t="inlineStr"/>
-      <c r="AL23" s="2" t="inlineStr"/>
-      <c r="AM23" s="2" t="inlineStr"/>
-      <c r="AN23" s="2" t="inlineStr"/>
-      <c r="AO23" s="2" t="inlineStr"/>
-      <c r="AP23" s="2" t="inlineStr"/>
-      <c r="AQ23" s="2" t="inlineStr"/>
-      <c r="AR23" s="2" t="inlineStr"/>
-      <c r="AS23" s="2" t="inlineStr"/>
-      <c r="AT23" s="2" t="inlineStr"/>
-      <c r="AU23" s="2" t="inlineStr"/>
-      <c r="AV23" s="2" t="inlineStr"/>
-      <c r="AW23" s="2" t="inlineStr"/>
-      <c r="AX23" s="2" t="inlineStr"/>
-      <c r="AY23" s="2" t="inlineStr"/>
-      <c r="AZ23" s="2" t="inlineStr"/>
-      <c r="BA23" s="2" t="inlineStr"/>
-      <c r="BB23" s="2" t="inlineStr">
+      <c r="AP23" s="3" t="inlineStr"/>
+      <c r="AQ23" s="3" t="inlineStr"/>
+      <c r="AR23" s="3" t="inlineStr"/>
+      <c r="AS23" s="3" t="inlineStr"/>
+      <c r="AT23" s="3" t="inlineStr"/>
+      <c r="AU23" s="3" t="inlineStr"/>
+      <c r="AV23" s="3" t="inlineStr"/>
+      <c r="AW23" s="3" t="inlineStr"/>
+      <c r="AX23" s="3" t="inlineStr"/>
+      <c r="AY23" s="3" t="inlineStr"/>
+      <c r="AZ23" s="3" t="inlineStr"/>
+      <c r="BA23" s="3" t="inlineStr"/>
+      <c r="BB23" s="3" t="inlineStr">
         <is>
           <t>DUK</t>
         </is>
       </c>
-      <c r="BC23" s="2" t="inlineStr">
+      <c r="BC23" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD23" s="2" t="inlineStr"/>
-      <c r="BE23" s="2" t="inlineStr">
+      <c r="BD23" s="3" t="inlineStr"/>
+      <c r="BE23" s="3" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF23" s="2" t="inlineStr"/>
-      <c r="BG23" s="2" t="inlineStr">
+      <c r="BF23" s="3" t="inlineStr"/>
+      <c r="BG23" s="3" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH23" s="2" t="inlineStr"/>
+      <c r="BH23" s="3" t="inlineStr"/>
+      <c r="BI23" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ23" s="3" t="inlineStr"/>
+      <c r="BK23" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL23" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -4787,184 +5063,216 @@
         </is>
       </c>
       <c r="BH24" s="3" t="inlineStr"/>
+      <c r="BI24" s="3" t="inlineStr"/>
+      <c r="BJ24" s="3" t="inlineStr"/>
+      <c r="BK24" s="3" t="inlineStr"/>
+      <c r="BL24" s="3" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>UBER</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t>Uber Technologies, Inc. Common Stock</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E25" s="3" t="inlineStr">
         <is>
           <t>2026-10-08T03:47:56+08:00</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F25" s="3" t="inlineStr">
         <is>
           <t>Uber class action alleges company enrolled users in Uber One without consent</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr"/>
-      <c r="M25" s="2" t="inlineStr">
+      <c r="G25" s="3" t="inlineStr"/>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t>'-0.669</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="inlineStr"/>
+      <c r="Q25" s="3" t="inlineStr"/>
+      <c r="R25" s="3" t="inlineStr"/>
+      <c r="S25" s="3" t="inlineStr"/>
+      <c r="T25" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U25" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPQTF5YmpWOXI5bmRMdy1Gd1l0cXZSODJoT3Q3STJYUkxQRV9qYm9JSEpUWk9hODQzYWdDeGczdk1XeGxlaXZNSU9naFVqMGFMZEcyVXlqV1ZmXzJnSE9TeEFMZ0VxXzZCZzBCQ2QtSWxLOERGYXZiRGRZcGhMNzViTC1oSld4WmQ0cjQ4d3JzOXZ0Z2IwVjhYOTRkUVFwRXd5X2xsaUxfNWZWd0JTeTQxTDdRSzQxSTNQcDFObFl0VQ?oc=5</t>
+        </is>
+      </c>
+      <c r="V25" s="3" t="inlineStr">
+        <is>
+          <t>Claim Depot</t>
+        </is>
+      </c>
+      <c r="W25" s="3" t="inlineStr"/>
+      <c r="X25" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y25" s="3" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z25" s="3" t="inlineStr">
+        <is>
+          <t>class action</t>
+        </is>
+      </c>
+      <c r="AA25" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB25" s="3" t="inlineStr">
+        <is>
+          <t>70a9f8d39d4343049d8218d472b31990</t>
+        </is>
+      </c>
+      <c r="AC25" s="3" t="inlineStr">
+        <is>
+          <t>4e08db63479dad56e0723932</t>
+        </is>
+      </c>
+      <c r="AD25" s="3" t="inlineStr">
+        <is>
+          <t>a47ec3a8e00258e537cfdb3e</t>
+        </is>
+      </c>
+      <c r="AE25" s="3" t="inlineStr">
+        <is>
+          <t>UBER-MAJOR_LITIGATION-001</t>
+        </is>
+      </c>
+      <c r="AF25" s="3" t="inlineStr"/>
+      <c r="AG25" s="3" t="inlineStr"/>
+      <c r="AH25" s="3" t="inlineStr"/>
+      <c r="AI25" s="3" t="inlineStr"/>
+      <c r="AJ25" s="3" t="inlineStr"/>
+      <c r="AK25" s="3" t="inlineStr"/>
+      <c r="AL25" s="3" t="inlineStr"/>
+      <c r="AM25" s="3" t="inlineStr"/>
+      <c r="AN25" s="3" t="inlineStr"/>
+      <c r="AO25" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>'-0.669</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr"/>
-      <c r="Q25" s="2" t="inlineStr"/>
-      <c r="R25" s="2" t="inlineStr"/>
-      <c r="S25" s="2" t="inlineStr"/>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPQTF5YmpWOXI5bmRMdy1Gd1l0cXZSODJoT3Q3STJYUkxQRV9qYm9JSEpUWk9hODQzYWdDeGczdk1XeGxlaXZNSU9naFVqMGFMZEcyVXlqV1ZmXzJnSE9TeEFMZ0VxXzZCZzBCQ2QtSWxLOERGYXZiRGRZcGhMNzViTC1oSld4WmQ0cjQ4d3JzOXZ0Z2IwVjhYOTRkUVFwRXd5X2xsaUxfNWZWd0JTeTQxTDdRSzQxSTNQcDFObFl0VQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>Claim Depot</t>
-        </is>
-      </c>
-      <c r="W25" s="2" t="inlineStr"/>
-      <c r="X25" s="2" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y25" s="2" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z25" s="2" t="inlineStr">
-        <is>
-          <t>class action</t>
-        </is>
-      </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB25" s="2" t="inlineStr"/>
-      <c r="AC25" s="2" t="inlineStr">
-        <is>
-          <t>4e08db63479dad56e0723932</t>
-        </is>
-      </c>
-      <c r="AD25" s="2" t="inlineStr">
-        <is>
-          <t>a47ec3a8e00258e537cfdb3e</t>
-        </is>
-      </c>
-      <c r="AE25" s="2" t="inlineStr">
-        <is>
-          <t>UBER-MAJOR_LITIGATION-001</t>
-        </is>
-      </c>
-      <c r="AF25" s="2" t="inlineStr"/>
-      <c r="AG25" s="2" t="inlineStr"/>
-      <c r="AH25" s="2" t="inlineStr"/>
-      <c r="AI25" s="2" t="inlineStr"/>
-      <c r="AJ25" s="2" t="inlineStr"/>
-      <c r="AK25" s="2" t="inlineStr"/>
-      <c r="AL25" s="2" t="inlineStr"/>
-      <c r="AM25" s="2" t="inlineStr"/>
-      <c r="AN25" s="2" t="inlineStr"/>
-      <c r="AO25" s="2" t="inlineStr"/>
-      <c r="AP25" s="2" t="inlineStr"/>
-      <c r="AQ25" s="2" t="inlineStr"/>
-      <c r="AR25" s="2" t="inlineStr"/>
-      <c r="AS25" s="2" t="inlineStr"/>
-      <c r="AT25" s="2" t="inlineStr"/>
-      <c r="AU25" s="2" t="inlineStr"/>
-      <c r="AV25" s="2" t="inlineStr"/>
-      <c r="AW25" s="2" t="inlineStr">
+      <c r="AP25" s="3" t="inlineStr"/>
+      <c r="AQ25" s="3" t="inlineStr"/>
+      <c r="AR25" s="3" t="inlineStr"/>
+      <c r="AS25" s="3" t="inlineStr"/>
+      <c r="AT25" s="3" t="inlineStr"/>
+      <c r="AU25" s="3" t="inlineStr"/>
+      <c r="AV25" s="3" t="inlineStr"/>
+      <c r="AW25" s="3" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX25" s="2" t="inlineStr"/>
-      <c r="AY25" s="2" t="inlineStr"/>
-      <c r="AZ25" s="2" t="inlineStr"/>
-      <c r="BA25" s="2" t="inlineStr"/>
-      <c r="BB25" s="2" t="inlineStr">
+      <c r="AX25" s="3" t="inlineStr"/>
+      <c r="AY25" s="3" t="inlineStr"/>
+      <c r="AZ25" s="3" t="inlineStr"/>
+      <c r="BA25" s="3" t="inlineStr"/>
+      <c r="BB25" s="3" t="inlineStr">
         <is>
           <t>UBER</t>
         </is>
       </c>
-      <c r="BC25" s="2" t="inlineStr">
+      <c r="BC25" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD25" s="2" t="inlineStr"/>
-      <c r="BE25" s="2" t="inlineStr">
+      <c r="BD25" s="3" t="inlineStr"/>
+      <c r="BE25" s="3" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF25" s="2" t="inlineStr">
+      <c r="BF25" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG25" s="2" t="inlineStr">
+      <c r="BG25" s="3" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH25" s="2" t="inlineStr"/>
+      <c r="BH25" s="3" t="inlineStr"/>
+      <c r="BI25" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ25" s="3" t="inlineStr"/>
+      <c r="BK25" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL25" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -5135,6 +5443,10 @@
         </is>
       </c>
       <c r="BH26" s="3" t="inlineStr"/>
+      <c r="BI26" s="3" t="inlineStr"/>
+      <c r="BJ26" s="3" t="inlineStr"/>
+      <c r="BK26" s="3" t="inlineStr"/>
+      <c r="BL26" s="3" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -5313,184 +5625,208 @@
       </c>
       <c r="BG27" s="4" t="inlineStr"/>
       <c r="BH27" s="4" t="inlineStr"/>
+      <c r="BI27" s="4" t="inlineStr"/>
+      <c r="BJ27" s="4" t="inlineStr"/>
+      <c r="BK27" s="4" t="inlineStr"/>
+      <c r="BL27" s="4" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr"/>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr"/>
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t>Marriott International</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E28" s="3" t="inlineStr">
         <is>
           <t>2026-10-08T01:16:51+08:00</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F28" s="3" t="inlineStr">
         <is>
           <t>消息人士稱，Priceline因發布誤導性酒店廣告將面臨美國聯邦貿易委員會（FTC）的處罰</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>監管調查</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
+      <c r="G28" s="3" t="inlineStr"/>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="inlineStr">
+        <is>
+          <t>0.069</t>
+        </is>
+      </c>
+      <c r="P28" s="3" t="inlineStr"/>
+      <c r="Q28" s="3" t="inlineStr"/>
+      <c r="R28" s="3" t="inlineStr"/>
+      <c r="S28" s="3" t="inlineStr"/>
+      <c r="T28" s="3" t="inlineStr">
+        <is>
+          <t>主體證據不足</t>
+        </is>
+      </c>
+      <c r="U28" s="3" t="inlineStr">
+        <is>
+          <t>https://tw.tradingview.com/symbols/NASDAQ-MAR/news/</t>
+        </is>
+      </c>
+      <c r="V28" s="3" t="inlineStr">
+        <is>
+          <t>TradingView</t>
+        </is>
+      </c>
+      <c r="W28" s="3" t="inlineStr"/>
+      <c r="X28" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y28" s="3" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z28" s="3" t="inlineStr">
+        <is>
+          <t>FTC</t>
+        </is>
+      </c>
+      <c r="AA28" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB28" s="3" t="inlineStr">
+        <is>
+          <t>82054bd659ec4beaa9ae509bcdd846f4</t>
+        </is>
+      </c>
+      <c r="AC28" s="3" t="inlineStr">
+        <is>
+          <t>3fa2144c2654b305167099fd</t>
+        </is>
+      </c>
+      <c r="AD28" s="3" t="inlineStr">
+        <is>
+          <t>06a16fc3d0d85d6619b772bf</t>
+        </is>
+      </c>
+      <c r="AE28" s="3" t="inlineStr">
+        <is>
+          <t>MAR-REGULATORY_INVESTIGATION-001</t>
+        </is>
+      </c>
+      <c r="AF28" s="3" t="inlineStr"/>
+      <c r="AG28" s="3" t="inlineStr"/>
+      <c r="AH28" s="3" t="inlineStr"/>
+      <c r="AI28" s="3" t="inlineStr"/>
+      <c r="AJ28" s="3" t="inlineStr"/>
+      <c r="AK28" s="3" t="inlineStr"/>
+      <c r="AL28" s="3" t="inlineStr"/>
+      <c r="AM28" s="3" t="inlineStr"/>
+      <c r="AN28" s="3" t="inlineStr"/>
+      <c r="AO28" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0.069</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr"/>
-      <c r="Q28" s="2" t="inlineStr"/>
-      <c r="R28" s="2" t="inlineStr"/>
-      <c r="S28" s="2" t="inlineStr"/>
-      <c r="T28" s="2" t="inlineStr">
+      <c r="AP28" s="3" t="inlineStr"/>
+      <c r="AQ28" s="3" t="inlineStr"/>
+      <c r="AR28" s="3" t="inlineStr"/>
+      <c r="AS28" s="3" t="inlineStr"/>
+      <c r="AT28" s="3" t="inlineStr"/>
+      <c r="AU28" s="3" t="inlineStr"/>
+      <c r="AV28" s="3" t="inlineStr"/>
+      <c r="AW28" s="3" t="inlineStr"/>
+      <c r="AX28" s="3" t="inlineStr"/>
+      <c r="AY28" s="3" t="inlineStr"/>
+      <c r="AZ28" s="3" t="inlineStr"/>
+      <c r="BA28" s="3" t="inlineStr"/>
+      <c r="BB28" s="3" t="inlineStr">
+        <is>
+          <t>MAR</t>
+        </is>
+      </c>
+      <c r="BC28" s="3" t="inlineStr">
         <is>
           <t>主體證據不足</t>
         </is>
       </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>https://tw.tradingview.com/symbols/NASDAQ-MAR/news/</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="W28" s="2" t="inlineStr"/>
-      <c r="X28" s="2" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y28" s="2" t="inlineStr">
-        <is>
-          <t>REGULATORY_INVESTIGATION</t>
-        </is>
-      </c>
-      <c r="Z28" s="2" t="inlineStr">
-        <is>
-          <t>FTC</t>
-        </is>
-      </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB28" s="2" t="inlineStr"/>
-      <c r="AC28" s="2" t="inlineStr">
-        <is>
-          <t>3fa2144c2654b305167099fd</t>
-        </is>
-      </c>
-      <c r="AD28" s="2" t="inlineStr">
-        <is>
-          <t>06a16fc3d0d85d6619b772bf</t>
-        </is>
-      </c>
-      <c r="AE28" s="2" t="inlineStr">
-        <is>
-          <t>MAR-REGULATORY_INVESTIGATION-001</t>
-        </is>
-      </c>
-      <c r="AF28" s="2" t="inlineStr"/>
-      <c r="AG28" s="2" t="inlineStr"/>
-      <c r="AH28" s="2" t="inlineStr"/>
-      <c r="AI28" s="2" t="inlineStr"/>
-      <c r="AJ28" s="2" t="inlineStr"/>
-      <c r="AK28" s="2" t="inlineStr"/>
-      <c r="AL28" s="2" t="inlineStr"/>
-      <c r="AM28" s="2" t="inlineStr"/>
-      <c r="AN28" s="2" t="inlineStr"/>
-      <c r="AO28" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP28" s="2" t="inlineStr"/>
-      <c r="AQ28" s="2" t="inlineStr"/>
-      <c r="AR28" s="2" t="inlineStr"/>
-      <c r="AS28" s="2" t="inlineStr"/>
-      <c r="AT28" s="2" t="inlineStr"/>
-      <c r="AU28" s="2" t="inlineStr"/>
-      <c r="AV28" s="2" t="inlineStr"/>
-      <c r="AW28" s="2" t="inlineStr"/>
-      <c r="AX28" s="2" t="inlineStr"/>
-      <c r="AY28" s="2" t="inlineStr"/>
-      <c r="AZ28" s="2" t="inlineStr"/>
-      <c r="BA28" s="2" t="inlineStr"/>
-      <c r="BB28" s="2" t="inlineStr">
+      <c r="BD28" s="3" t="inlineStr">
         <is>
           <t>MAR</t>
         </is>
       </c>
-      <c r="BC28" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD28" s="2" t="inlineStr">
-        <is>
-          <t>MAR</t>
-        </is>
-      </c>
-      <c r="BE28" s="2" t="inlineStr">
+      <c r="BE28" s="3" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
-      <c r="BF28" s="2" t="inlineStr">
+      <c r="BF28" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
-      <c r="BG28" s="2" t="inlineStr"/>
-      <c r="BH28" s="2" t="inlineStr"/>
+      <c r="BG28" s="3" t="inlineStr"/>
+      <c r="BH28" s="3" t="inlineStr"/>
+      <c r="BI28" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ28" s="3" t="inlineStr"/>
+      <c r="BK28" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL28" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5503,7 +5839,11 @@
           <t>US</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr"/>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>BKNG</t>
+        </is>
+      </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Booking Holdings</t>
@@ -5537,17 +5877,17 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>待人工覆核</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -5600,7 +5940,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB29" s="2" t="inlineStr"/>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>56d54296786f4ef487a877d308e2b310</t>
+        </is>
+      </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
           <t>6c24a6b651101bbd050a5c0b</t>
@@ -5627,7 +5971,7 @@
       <c r="AN29" s="2" t="inlineStr"/>
       <c r="AO29" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP29" s="2" t="inlineStr"/>
@@ -5669,357 +6013,421 @@
       </c>
       <c r="BG29" s="2" t="inlineStr"/>
       <c r="BH29" s="2" t="inlineStr"/>
+      <c r="BI29" s="2" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="BJ29" s="2" t="inlineStr"/>
+      <c r="BK29" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL29" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr"/>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr"/>
+      <c r="D30" s="3" t="inlineStr">
         <is>
           <t>Expedia Group</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E30" s="3" t="inlineStr">
         <is>
           <t>2026-10-08T01:16:51+08:00</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F30" s="3" t="inlineStr">
         <is>
           <t>消息人士稱，Priceline因發布誤導性酒店廣告將面臨美國聯邦貿易委員會（FTC）的處罰</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>監管調查</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
+      <c r="G30" s="3" t="inlineStr"/>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O30" s="3" t="inlineStr">
+        <is>
+          <t>0.069</t>
+        </is>
+      </c>
+      <c r="P30" s="3" t="inlineStr"/>
+      <c r="Q30" s="3" t="inlineStr"/>
+      <c r="R30" s="3" t="inlineStr"/>
+      <c r="S30" s="3" t="inlineStr"/>
+      <c r="T30" s="3" t="inlineStr">
+        <is>
+          <t>主體證據不足</t>
+        </is>
+      </c>
+      <c r="U30" s="3" t="inlineStr">
+        <is>
+          <t>https://tw.tradingview.com/symbols/NASDAQ-EXPE/news/</t>
+        </is>
+      </c>
+      <c r="V30" s="3" t="inlineStr">
+        <is>
+          <t>TradingView</t>
+        </is>
+      </c>
+      <c r="W30" s="3" t="inlineStr"/>
+      <c r="X30" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y30" s="3" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z30" s="3" t="inlineStr">
+        <is>
+          <t>FTC</t>
+        </is>
+      </c>
+      <c r="AA30" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB30" s="3" t="inlineStr">
+        <is>
+          <t>6e91b014ef184d1ca4d5248f37cd7a78</t>
+        </is>
+      </c>
+      <c r="AC30" s="3" t="inlineStr">
+        <is>
+          <t>d25efedb84fdd99d661c0c8d</t>
+        </is>
+      </c>
+      <c r="AD30" s="3" t="inlineStr">
+        <is>
+          <t>e8fa0af2431213fe919a445f</t>
+        </is>
+      </c>
+      <c r="AE30" s="3" t="inlineStr">
+        <is>
+          <t>EXPE-REGULATORY_INVESTIGATION-001</t>
+        </is>
+      </c>
+      <c r="AF30" s="3" t="inlineStr"/>
+      <c r="AG30" s="3" t="inlineStr"/>
+      <c r="AH30" s="3" t="inlineStr"/>
+      <c r="AI30" s="3" t="inlineStr"/>
+      <c r="AJ30" s="3" t="inlineStr"/>
+      <c r="AK30" s="3" t="inlineStr"/>
+      <c r="AL30" s="3" t="inlineStr"/>
+      <c r="AM30" s="3" t="inlineStr"/>
+      <c r="AN30" s="3" t="inlineStr"/>
+      <c r="AO30" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>0.069</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr"/>
-      <c r="Q30" s="2" t="inlineStr"/>
-      <c r="R30" s="2" t="inlineStr"/>
-      <c r="S30" s="2" t="inlineStr"/>
-      <c r="T30" s="2" t="inlineStr">
+      <c r="AP30" s="3" t="inlineStr"/>
+      <c r="AQ30" s="3" t="inlineStr"/>
+      <c r="AR30" s="3" t="inlineStr"/>
+      <c r="AS30" s="3" t="inlineStr"/>
+      <c r="AT30" s="3" t="inlineStr"/>
+      <c r="AU30" s="3" t="inlineStr"/>
+      <c r="AV30" s="3" t="inlineStr"/>
+      <c r="AW30" s="3" t="inlineStr"/>
+      <c r="AX30" s="3" t="inlineStr"/>
+      <c r="AY30" s="3" t="inlineStr"/>
+      <c r="AZ30" s="3" t="inlineStr"/>
+      <c r="BA30" s="3" t="inlineStr"/>
+      <c r="BB30" s="3" t="inlineStr">
+        <is>
+          <t>EXPE</t>
+        </is>
+      </c>
+      <c r="BC30" s="3" t="inlineStr">
         <is>
           <t>主體證據不足</t>
         </is>
       </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>https://tw.tradingview.com/symbols/NASDAQ-EXPE/news/</t>
-        </is>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="W30" s="2" t="inlineStr"/>
-      <c r="X30" s="2" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y30" s="2" t="inlineStr">
-        <is>
-          <t>REGULATORY_INVESTIGATION</t>
-        </is>
-      </c>
-      <c r="Z30" s="2" t="inlineStr">
-        <is>
-          <t>FTC</t>
-        </is>
-      </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB30" s="2" t="inlineStr"/>
-      <c r="AC30" s="2" t="inlineStr">
-        <is>
-          <t>d25efedb84fdd99d661c0c8d</t>
-        </is>
-      </c>
-      <c r="AD30" s="2" t="inlineStr">
-        <is>
-          <t>e8fa0af2431213fe919a445f</t>
-        </is>
-      </c>
-      <c r="AE30" s="2" t="inlineStr">
-        <is>
-          <t>EXPE-REGULATORY_INVESTIGATION-001</t>
-        </is>
-      </c>
-      <c r="AF30" s="2" t="inlineStr"/>
-      <c r="AG30" s="2" t="inlineStr"/>
-      <c r="AH30" s="2" t="inlineStr"/>
-      <c r="AI30" s="2" t="inlineStr"/>
-      <c r="AJ30" s="2" t="inlineStr"/>
-      <c r="AK30" s="2" t="inlineStr"/>
-      <c r="AL30" s="2" t="inlineStr"/>
-      <c r="AM30" s="2" t="inlineStr"/>
-      <c r="AN30" s="2" t="inlineStr"/>
-      <c r="AO30" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP30" s="2" t="inlineStr"/>
-      <c r="AQ30" s="2" t="inlineStr"/>
-      <c r="AR30" s="2" t="inlineStr"/>
-      <c r="AS30" s="2" t="inlineStr"/>
-      <c r="AT30" s="2" t="inlineStr"/>
-      <c r="AU30" s="2" t="inlineStr"/>
-      <c r="AV30" s="2" t="inlineStr"/>
-      <c r="AW30" s="2" t="inlineStr"/>
-      <c r="AX30" s="2" t="inlineStr"/>
-      <c r="AY30" s="2" t="inlineStr"/>
-      <c r="AZ30" s="2" t="inlineStr"/>
-      <c r="BA30" s="2" t="inlineStr"/>
-      <c r="BB30" s="2" t="inlineStr">
+      <c r="BD30" s="3" t="inlineStr">
         <is>
           <t>EXPE</t>
         </is>
       </c>
-      <c r="BC30" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD30" s="2" t="inlineStr">
-        <is>
-          <t>EXPE</t>
-        </is>
-      </c>
-      <c r="BE30" s="2" t="inlineStr">
+      <c r="BE30" s="3" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
-      <c r="BF30" s="2" t="inlineStr">
+      <c r="BF30" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
-      <c r="BG30" s="2" t="inlineStr"/>
-      <c r="BH30" s="2" t="inlineStr"/>
+      <c r="BG30" s="3" t="inlineStr"/>
+      <c r="BH30" s="3" t="inlineStr"/>
+      <c r="BI30" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ30" s="3" t="inlineStr"/>
+      <c r="BK30" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL30" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>XOM</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>ExxonMobil</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E31" s="3" t="inlineStr">
         <is>
           <t>2026-10-08T00:48:21+08:00</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F31" s="3" t="inlineStr">
         <is>
           <t>Weil Wins Dismissal of Plastics Class Action for ExxonMobil</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr"/>
-      <c r="M31" s="2" t="inlineStr">
+      <c r="G31" s="3" t="inlineStr"/>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O31" s="3" t="inlineStr">
+        <is>
+          <t>'-0.734</t>
+        </is>
+      </c>
+      <c r="P31" s="3" t="inlineStr"/>
+      <c r="Q31" s="3" t="inlineStr"/>
+      <c r="R31" s="3" t="inlineStr"/>
+      <c r="S31" s="3" t="inlineStr"/>
+      <c r="T31" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U31" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPZmVQN0llTEJsUWQxMXF4ZWQ1MXAyOGZXUzdEc0hkcUMyTEVZZF9tMjZIZkFwY0h4dDZrVFhEd0RxWW5lZWkweGN4NnhaT2pabkl5MFNyd3pUdnJLZzNwbVRwZjg0V2JGa1NwLVp5UXBBNHhYcmt3ODhiSzR5RklVX0VoMU1WTVlXQU9FQUJEejk2SzQ?oc=5</t>
+        </is>
+      </c>
+      <c r="V31" s="3" t="inlineStr">
+        <is>
+          <t>Weil</t>
+        </is>
+      </c>
+      <c r="W31" s="3" t="inlineStr"/>
+      <c r="X31" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y31" s="3" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z31" s="3" t="inlineStr">
+        <is>
+          <t>class action</t>
+        </is>
+      </c>
+      <c r="AA31" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB31" s="3" t="inlineStr">
+        <is>
+          <t>80124e58c931444cb79dc99b815feb9b</t>
+        </is>
+      </c>
+      <c r="AC31" s="3" t="inlineStr">
+        <is>
+          <t>6168931c1522728631b435be</t>
+        </is>
+      </c>
+      <c r="AD31" s="3" t="inlineStr">
+        <is>
+          <t>a56141ede6d0d4ab2b1ad0df</t>
+        </is>
+      </c>
+      <c r="AE31" s="3" t="inlineStr">
+        <is>
+          <t>XOM-MAJOR_LITIGATION-001</t>
+        </is>
+      </c>
+      <c r="AF31" s="3" t="inlineStr"/>
+      <c r="AG31" s="3" t="inlineStr"/>
+      <c r="AH31" s="3" t="inlineStr"/>
+      <c r="AI31" s="3" t="inlineStr"/>
+      <c r="AJ31" s="3" t="inlineStr"/>
+      <c r="AK31" s="3" t="inlineStr"/>
+      <c r="AL31" s="3" t="inlineStr"/>
+      <c r="AM31" s="3" t="inlineStr"/>
+      <c r="AN31" s="3" t="inlineStr"/>
+      <c r="AO31" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>'-0.734</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="inlineStr"/>
-      <c r="Q31" s="2" t="inlineStr"/>
-      <c r="R31" s="2" t="inlineStr"/>
-      <c r="S31" s="2" t="inlineStr"/>
-      <c r="T31" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U31" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPZmVQN0llTEJsUWQxMXF4ZWQ1MXAyOGZXUzdEc0hkcUMyTEVZZF9tMjZIZkFwY0h4dDZrVFhEd0RxWW5lZWkweGN4NnhaT2pabkl5MFNyd3pUdnJLZzNwbVRwZjg0V2JGa1NwLVp5UXBBNHhYcmt3ODhiSzR5RklVX0VoMU1WTVlXQU9FQUJEejk2SzQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V31" s="2" t="inlineStr">
-        <is>
-          <t>Weil</t>
-        </is>
-      </c>
-      <c r="W31" s="2" t="inlineStr"/>
-      <c r="X31" s="2" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y31" s="2" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z31" s="2" t="inlineStr">
-        <is>
-          <t>class action</t>
-        </is>
-      </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB31" s="2" t="inlineStr"/>
-      <c r="AC31" s="2" t="inlineStr">
-        <is>
-          <t>6168931c1522728631b435be</t>
-        </is>
-      </c>
-      <c r="AD31" s="2" t="inlineStr">
-        <is>
-          <t>a56141ede6d0d4ab2b1ad0df</t>
-        </is>
-      </c>
-      <c r="AE31" s="2" t="inlineStr">
-        <is>
-          <t>XOM-MAJOR_LITIGATION-001</t>
-        </is>
-      </c>
-      <c r="AF31" s="2" t="inlineStr"/>
-      <c r="AG31" s="2" t="inlineStr"/>
-      <c r="AH31" s="2" t="inlineStr"/>
-      <c r="AI31" s="2" t="inlineStr"/>
-      <c r="AJ31" s="2" t="inlineStr"/>
-      <c r="AK31" s="2" t="inlineStr"/>
-      <c r="AL31" s="2" t="inlineStr"/>
-      <c r="AM31" s="2" t="inlineStr"/>
-      <c r="AN31" s="2" t="inlineStr"/>
-      <c r="AO31" s="2" t="inlineStr"/>
-      <c r="AP31" s="2" t="inlineStr"/>
-      <c r="AQ31" s="2" t="inlineStr"/>
-      <c r="AR31" s="2" t="inlineStr"/>
-      <c r="AS31" s="2" t="inlineStr"/>
-      <c r="AT31" s="2" t="inlineStr"/>
-      <c r="AU31" s="2" t="inlineStr"/>
-      <c r="AV31" s="2" t="inlineStr"/>
-      <c r="AW31" s="2" t="inlineStr"/>
-      <c r="AX31" s="2" t="inlineStr"/>
-      <c r="AY31" s="2" t="inlineStr"/>
-      <c r="AZ31" s="2" t="inlineStr"/>
-      <c r="BA31" s="2" t="inlineStr"/>
-      <c r="BB31" s="2" t="inlineStr">
+      <c r="AP31" s="3" t="inlineStr"/>
+      <c r="AQ31" s="3" t="inlineStr"/>
+      <c r="AR31" s="3" t="inlineStr"/>
+      <c r="AS31" s="3" t="inlineStr"/>
+      <c r="AT31" s="3" t="inlineStr"/>
+      <c r="AU31" s="3" t="inlineStr"/>
+      <c r="AV31" s="3" t="inlineStr"/>
+      <c r="AW31" s="3" t="inlineStr"/>
+      <c r="AX31" s="3" t="inlineStr"/>
+      <c r="AY31" s="3" t="inlineStr"/>
+      <c r="AZ31" s="3" t="inlineStr"/>
+      <c r="BA31" s="3" t="inlineStr"/>
+      <c r="BB31" s="3" t="inlineStr">
         <is>
           <t>XOM</t>
         </is>
       </c>
-      <c r="BC31" s="2" t="inlineStr">
+      <c r="BC31" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD31" s="2" t="inlineStr"/>
-      <c r="BE31" s="2" t="inlineStr">
+      <c r="BD31" s="3" t="inlineStr"/>
+      <c r="BE31" s="3" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF31" s="2" t="inlineStr"/>
-      <c r="BG31" s="2" t="inlineStr">
+      <c r="BF31" s="3" t="inlineStr"/>
+      <c r="BG31" s="3" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH31" s="2" t="inlineStr"/>
+      <c r="BH31" s="3" t="inlineStr"/>
+      <c r="BI31" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ31" s="3" t="inlineStr"/>
+      <c r="BK31" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL31" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH31"/>
+  <autoFilter ref="A1:BL31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6030,7 +6438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH19"/>
+  <dimension ref="A1:BL9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6093,6 +6501,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6396,6 +6808,26 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -6408,7 +6840,11 @@
           <t>US</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr"/>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Ford Motor Company</t>
@@ -6442,17 +6878,17 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>待人工覆核</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -6505,7 +6941,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>64c2c3d7374141a3bc32ffe3c8e5db76</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
           <t>298c3610ce9944a092126e67</t>
@@ -6532,7 +6972,7 @@
       <c r="AN2" s="2" t="inlineStr"/>
       <c r="AO2" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP2" s="2" t="inlineStr"/>
@@ -6574,184 +7014,204 @@
       </c>
       <c r="BG2" s="2" t="inlineStr"/>
       <c r="BH2" s="2" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="BJ2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>AT&amp;T Inc.</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-08T21:09:00+08:00</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Payments could come soon in $177M AT&amp;T settlement: How much will you receive?</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>BLDR</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Builders FirstSource, Inc. Common Stock</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08T21:07:46+08:00</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Truist cuts Builders FirstSource stock price target on margin pressure</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr"/>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>營運惡化</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="L3" s="4" t="inlineStr"/>
+      <c r="M3" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="N3" s="4" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>0.055</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr"/>
-      <c r="Q3" s="2" t="inlineStr"/>
-      <c r="R3" s="2" t="inlineStr"/>
-      <c r="S3" s="2" t="inlineStr"/>
-      <c r="T3" s="2" t="inlineStr">
+      <c r="O3" s="4" t="inlineStr">
+        <is>
+          <t>'-0.557</t>
+        </is>
+      </c>
+      <c r="P3" s="4" t="inlineStr"/>
+      <c r="Q3" s="4" t="inlineStr"/>
+      <c r="R3" s="4" t="inlineStr"/>
+      <c r="S3" s="4" t="inlineStr"/>
+      <c r="T3" s="4" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U3" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxNTGhVaHM1VlNJcTFEOGh4WHg1MU91c3NZam9rWUU5UHd0Rk1ZR2dWQ1Y0VmxEX2VaWkNPQTl2RW42UzB1blZmMk1lb3VCRXhwdDJKbmlCQW1ZV3E2RGdldlRFRWdUYWFfUV9PMWEtdndubkxPc1lTTjNxN0RUOURwMG5VcmVYOFBadnJobm1oaEJ5X1lQbDQxZ1E4WlZzOGJ4QmlTc3E5c3gyREowUkIyedIBtgFBVV95cUxNa1VaelBiUnRPZ3JVR0Z1d3REdDNtTHV5ajlFNHUtcWpxaDJRbzNKdnRqWEh2UlM3NTlqS01VcEI1T2hlUFBxTmV6RXNQeFRMb3NKc0NyUHptdzZSeXpqUG9MWU1aZU1SaWZTZFFndGZ5Y0FsU2ktSXVsX2JKb2FCN0RzT294ODdBdGFZU3JwMFhQOU5wNmNkTlplc2dmeTlwZUJ6U3dUYmU4RWs5bTZhSUxUNlBjZw?oc=5</t>
-        </is>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>The Hill</t>
-        </is>
-      </c>
-      <c r="W3" s="2" t="inlineStr"/>
-      <c r="X3" s="2" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y3" s="2" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z3" s="2" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA3" s="2" t="inlineStr">
+      <c r="U3" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOWF9VTTdVd3IzLXFrUG91amtWd0VQX2hRT2R2MlVGempDU2hPb2ZRcVpqUGd5Q1hTNlVweHJKYkswWVJUd05pTkpvWmZQQW9JNE9IWDZxREEybk1mWXFFM3VfMnB6cWYxRjN1d1dGeHFNLTNvRkhRWUZpMXI3eWgtZDlReGJEQ0hVVnV5VWZzeE5QM3NJeU5BZDVtamRDNkpobnpiNWtEQmNENGphbW0zQnIwdnVWVTVVcjNsRnR3LWkwVllSQmtabVpB?oc=5</t>
+        </is>
+      </c>
+      <c r="V3" s="4" t="inlineStr">
+        <is>
+          <t>Investing.com</t>
+        </is>
+      </c>
+      <c r="W3" s="4" t="inlineStr"/>
+      <c r="X3" s="4" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y3" s="4" t="inlineStr">
+        <is>
+          <t>OPERATING_DETERIORATION</t>
+        </is>
+      </c>
+      <c r="Z3" s="4" t="inlineStr">
+        <is>
+          <t>margin pressure</t>
+        </is>
+      </c>
+      <c r="AA3" s="4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB3" s="2" t="inlineStr"/>
-      <c r="AC3" s="2" t="inlineStr">
-        <is>
-          <t>0257b77fa3158891dc098ada</t>
-        </is>
-      </c>
-      <c r="AD3" s="2" t="inlineStr">
-        <is>
-          <t>cd0647af0a2d18ec95909417</t>
-        </is>
-      </c>
-      <c r="AE3" s="2" t="inlineStr">
-        <is>
-          <t>T-REGULATORY_PENALTY-001</t>
-        </is>
-      </c>
-      <c r="AF3" s="2" t="inlineStr"/>
-      <c r="AG3" s="2" t="inlineStr"/>
-      <c r="AH3" s="2" t="inlineStr"/>
-      <c r="AI3" s="2" t="inlineStr"/>
-      <c r="AJ3" s="2" t="inlineStr"/>
-      <c r="AK3" s="2" t="inlineStr"/>
-      <c r="AL3" s="2" t="inlineStr"/>
-      <c r="AM3" s="2" t="inlineStr"/>
-      <c r="AN3" s="2" t="inlineStr"/>
-      <c r="AO3" s="2" t="inlineStr"/>
-      <c r="AP3" s="2" t="inlineStr"/>
-      <c r="AQ3" s="2" t="inlineStr"/>
-      <c r="AR3" s="2" t="inlineStr"/>
-      <c r="AS3" s="2" t="inlineStr"/>
-      <c r="AT3" s="2" t="inlineStr"/>
-      <c r="AU3" s="2" t="inlineStr"/>
-      <c r="AV3" s="2" t="inlineStr"/>
-      <c r="AW3" s="2" t="inlineStr">
+      <c r="AB3" s="4" t="inlineStr"/>
+      <c r="AC3" s="4" t="inlineStr">
+        <is>
+          <t>efa885a37c192ced1cafd9fe</t>
+        </is>
+      </c>
+      <c r="AD3" s="4" t="inlineStr">
+        <is>
+          <t>54889863e846041115bc2a16</t>
+        </is>
+      </c>
+      <c r="AE3" s="4" t="inlineStr">
+        <is>
+          <t>BLDR-OPERATING_DETERIORATION-001</t>
+        </is>
+      </c>
+      <c r="AF3" s="4" t="inlineStr"/>
+      <c r="AG3" s="4" t="inlineStr"/>
+      <c r="AH3" s="4" t="inlineStr"/>
+      <c r="AI3" s="4" t="inlineStr"/>
+      <c r="AJ3" s="4" t="inlineStr"/>
+      <c r="AK3" s="4" t="inlineStr"/>
+      <c r="AL3" s="4" t="inlineStr"/>
+      <c r="AM3" s="4" t="inlineStr"/>
+      <c r="AN3" s="4" t="inlineStr"/>
+      <c r="AO3" s="4" t="inlineStr"/>
+      <c r="AP3" s="4" t="inlineStr"/>
+      <c r="AQ3" s="4" t="inlineStr"/>
+      <c r="AR3" s="4" t="inlineStr"/>
+      <c r="AS3" s="4" t="inlineStr"/>
+      <c r="AT3" s="4" t="inlineStr"/>
+      <c r="AU3" s="4" t="inlineStr"/>
+      <c r="AV3" s="4" t="inlineStr"/>
+      <c r="AW3" s="4" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX3" s="2" t="inlineStr"/>
-      <c r="AY3" s="2" t="inlineStr"/>
-      <c r="AZ3" s="2" t="inlineStr"/>
-      <c r="BA3" s="2" t="inlineStr"/>
-      <c r="BB3" s="2" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="BC3" s="2" t="inlineStr">
+      <c r="AX3" s="4" t="inlineStr"/>
+      <c r="AY3" s="4" t="inlineStr"/>
+      <c r="AZ3" s="4" t="inlineStr"/>
+      <c r="BA3" s="4" t="inlineStr"/>
+      <c r="BB3" s="4" t="inlineStr">
+        <is>
+          <t>BLDR</t>
+        </is>
+      </c>
+      <c r="BC3" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD3" s="2" t="inlineStr"/>
-      <c r="BE3" s="2" t="inlineStr">
+      <c r="BD3" s="4" t="inlineStr"/>
+      <c r="BE3" s="4" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF3" s="2" t="inlineStr">
+      <c r="BF3" s="4" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG3" s="2" t="inlineStr">
+      <c r="BG3" s="4" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH3" s="2" t="inlineStr"/>
+      <c r="BH3" s="4" t="inlineStr"/>
+      <c r="BI3" s="4" t="inlineStr"/>
+      <c r="BJ3" s="4" t="inlineStr"/>
+      <c r="BK3" s="4" t="inlineStr"/>
+      <c r="BL3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -6766,22 +7226,22 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>BLDR</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Builders FirstSource, Inc. Common Stock</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T21:07:46+08:00</t>
+          <t>2026-10-08T20:21:33+08:00</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>Truist cuts Builders FirstSource stock price target on margin pressure</t>
+          <t>Amazon confirms job cuts impacting hundreds of employees in retail unit</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr"/>
@@ -6792,7 +7252,7 @@
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>營運惡化</t>
+          <t>裁員或人力縮減</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -6818,7 +7278,7 @@
       </c>
       <c r="O4" s="4" t="inlineStr">
         <is>
-          <t>'-0.557</t>
+          <t>'-0.952</t>
         </is>
       </c>
       <c r="P4" s="4" t="inlineStr"/>
@@ -6832,12 +7292,12 @@
       </c>
       <c r="U4" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOWF9VTTdVd3IzLXFrUG91amtWd0VQX2hRT2R2MlVGempDU2hPb2ZRcVpqUGd5Q1hTNlVweHJKYkswWVJUd05pTkpvWmZQQW9JNE9IWDZxREEybk1mWXFFM3VfMnB6cWYxRjN1d1dGeHFNLTNvRkhRWUZpMXI3eWgtZDlReGJEQ0hVVnV5VWZzeE5QM3NJeU5BZDVtamRDNkpobnpiNWtEQmNENGphbW0zQnIwdnVWVTVVcjNsRnR3LWkwVllSQmtabVpB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQdlBIbVRER3NIV25XUFpXSzdwcWo5cTBMMGpOSEJCRHpVQ3pyNl8wcXg1RTBNSzdIQTk2S0VERDZBZDZROThuOTNLU2VsMzJZWWhOR1Nqd3VldUgyWS1XNFdvR1FIbXBVcWNkU0RwNEVHck5SUFA3Q21Md2pXRDUtdnV2SGdfRVNOSmNZTEN2eGc3RU91ZTVROEJudDU2a2tuZDFodA?oc=5</t>
         </is>
       </c>
       <c r="V4" s="4" t="inlineStr">
         <is>
-          <t>Investing.com</t>
+          <t>GeekWire</t>
         </is>
       </c>
       <c r="W4" s="4" t="inlineStr"/>
@@ -6848,12 +7308,12 @@
       </c>
       <c r="Y4" s="4" t="inlineStr">
         <is>
-          <t>OPERATING_DETERIORATION</t>
+          <t>WORKFORCE_REDUCTION</t>
         </is>
       </c>
       <c r="Z4" s="4" t="inlineStr">
         <is>
-          <t>margin pressure</t>
+          <t>job cuts</t>
         </is>
       </c>
       <c r="AA4" s="4" t="inlineStr">
@@ -6864,17 +7324,17 @@
       <c r="AB4" s="4" t="inlineStr"/>
       <c r="AC4" s="4" t="inlineStr">
         <is>
-          <t>efa885a37c192ced1cafd9fe</t>
+          <t>4e87e63d42d1b5cd17bf65ef</t>
         </is>
       </c>
       <c r="AD4" s="4" t="inlineStr">
         <is>
-          <t>54889863e846041115bc2a16</t>
+          <t>0a44da94d725c599c3494cee</t>
         </is>
       </c>
       <c r="AE4" s="4" t="inlineStr">
         <is>
-          <t>BLDR-OPERATING_DETERIORATION-001</t>
+          <t>AMZN-WORKFORCE_REDUCTION-001</t>
         </is>
       </c>
       <c r="AF4" s="4" t="inlineStr"/>
@@ -6894,18 +7354,14 @@
       <c r="AT4" s="4" t="inlineStr"/>
       <c r="AU4" s="4" t="inlineStr"/>
       <c r="AV4" s="4" t="inlineStr"/>
-      <c r="AW4" s="4" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
+      <c r="AW4" s="4" t="inlineStr"/>
       <c r="AX4" s="4" t="inlineStr"/>
       <c r="AY4" s="4" t="inlineStr"/>
       <c r="AZ4" s="4" t="inlineStr"/>
       <c r="BA4" s="4" t="inlineStr"/>
       <c r="BB4" s="4" t="inlineStr">
         <is>
-          <t>BLDR</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="BC4" s="4" t="inlineStr">
@@ -6916,20 +7372,20 @@
       <c r="BD4" s="4" t="inlineStr"/>
       <c r="BE4" s="4" t="inlineStr">
         <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF4" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
+          <t>公司清單</t>
+        </is>
+      </c>
+      <c r="BF4" s="4" t="inlineStr"/>
       <c r="BG4" s="4" t="inlineStr">
         <is>
-          <t>交易所目前名單</t>
+          <t>公司清單／交易所參照</t>
         </is>
       </c>
       <c r="BH4" s="4" t="inlineStr"/>
+      <c r="BI4" s="4" t="inlineStr"/>
+      <c r="BJ4" s="4" t="inlineStr"/>
+      <c r="BK4" s="4" t="inlineStr"/>
+      <c r="BL4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -6954,12 +7410,12 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T20:21:33+08:00</t>
+          <t>2026-10-08T19:35:31+08:00</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>Amazon confirms job cuts impacting hundreds of employees in retail unit</t>
+          <t>Amazon makes fresh job cuts, mainly in retail division</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr"/>
@@ -6996,7 +7452,7 @@
       </c>
       <c r="O5" s="4" t="inlineStr">
         <is>
-          <t>'-0.952</t>
+          <t>'-0.909</t>
         </is>
       </c>
       <c r="P5" s="4" t="inlineStr"/>
@@ -7010,12 +7466,12 @@
       </c>
       <c r="U5" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQdlBIbVRER3NIV25XUFpXSzdwcWo5cTBMMGpOSEJCRHpVQ3pyNl8wcXg1RTBNSzdIQTk2S0VERDZBZDZROThuOTNLU2VsMzJZWWhOR1Nqd3VldUgyWS1XNFdvR1FIbXBVcWNkU0RwNEVHck5SUFA3Q21Md2pXRDUtdnV2SGdfRVNOSmNZTEN2eGc3RU91ZTVROEJudDU2a2tuZDFodA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxOMXBaTUxRTVRaaEh2ajRtZWxDekFLVElmbi1oVEw1eFJyUDg4NG5TNGxTZGw1eUFSTWhTbHVERXU2R2p1YlBFRnZhcUFXSG9vQWhPcVFxN21jdDJaMFRLY0lSU0x0YUtBREl3UXBYaVFXZmNtNmdfVGhkUmt5bnZJOTg3eTBOdjlUdTNaRTlFSGQ5YTdLcjVwWnVkLUREN2dLSkhoaEhlMHQ0U2YwWWc?oc=5</t>
         </is>
       </c>
       <c r="V5" s="4" t="inlineStr">
         <is>
-          <t>GeekWire</t>
+          <t>Reuters</t>
         </is>
       </c>
       <c r="W5" s="4" t="inlineStr"/>
@@ -7042,12 +7498,12 @@
       <c r="AB5" s="4" t="inlineStr"/>
       <c r="AC5" s="4" t="inlineStr">
         <is>
-          <t>4e87e63d42d1b5cd17bf65ef</t>
+          <t>a2db2c67030d1a9d23e43a8b</t>
         </is>
       </c>
       <c r="AD5" s="4" t="inlineStr">
         <is>
-          <t>0a44da94d725c599c3494cee</t>
+          <t>10c7c686523aa28cfbe010d3</t>
         </is>
       </c>
       <c r="AE5" s="4" t="inlineStr">
@@ -7100,176 +7556,192 @@
         </is>
       </c>
       <c r="BH5" s="4" t="inlineStr"/>
+      <c r="BI5" s="4" t="inlineStr"/>
+      <c r="BJ5" s="4" t="inlineStr"/>
+      <c r="BK5" s="4" t="inlineStr"/>
+      <c r="BL5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>XOM</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>ExxonMobil</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-08T20:10:56+08:00</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Update: ExxonMobil Director Vote Prompts US SEC Investigation Into Climate Action 100+; Regulator Pursues No Action Against Group</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>監管調查</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>FDX</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>FedEx Corporation Common Stock</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08T15:00:00+08:00</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>PGA TOUR Studios launches 'Tee Sheet presented by FedEx,' new weekly FedExCup Playoffs preview show</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>裁員或人力縮減</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="L6" s="4" t="inlineStr"/>
+      <c r="M6" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N6" s="4" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>'-0.02</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr"/>
-      <c r="Q6" s="2" t="inlineStr"/>
-      <c r="R6" s="2" t="inlineStr"/>
-      <c r="S6" s="2" t="inlineStr"/>
-      <c r="T6" s="2" t="inlineStr">
+      <c r="O6" s="4" t="inlineStr">
+        <is>
+          <t>0.017</t>
+        </is>
+      </c>
+      <c r="P6" s="4" t="inlineStr"/>
+      <c r="Q6" s="4" t="inlineStr"/>
+      <c r="R6" s="4" t="inlineStr"/>
+      <c r="S6" s="4" t="inlineStr"/>
+      <c r="T6" s="4" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOWHN6U2Vwdl9tNGFVRHFjS0Z1cG5ocXk0bTNOQ2lSS1hPU3h4am1wSHdnTXVjM0RRVVZac21CdEVvd3BXbXIwbGtoT245RWlZOURPMGkzcGhudC1iTkJHaDdLeGpPRTNId1IzUjZYUXVmVFVMWkJYZ2tBOGpZRHpwVlAxc01WQnVDZVVKUVc1VDVPVXVQUHkw?oc=5</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr"/>
-      <c r="X6" s="2" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y6" s="2" t="inlineStr">
-        <is>
-          <t>REGULATORY_INVESTIGATION</t>
-        </is>
-      </c>
-      <c r="Z6" s="2" t="inlineStr">
-        <is>
-          <t>SEC investigation</t>
-        </is>
-      </c>
-      <c r="AA6" s="2" t="inlineStr">
+      <c r="U6" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqgJBVV95cUxNRjhJcmZtSldNOFRiVHFyOXpUaXNCNWhKcGx3SHg0THFxVUFhRDREQm5oTXpOS1BVcU9GT3BMWW1NVWJJbG81eEI1WktfVlJvcEh3VXY0YUxsS2t2bGRCUDdjbDJoVktnd3FuRFItc2lZWTdQVzNWTl9mUmdnV2ZtMzctYXg5UjlhVUxkY21POF9YaUpzTzRHVnVQQldIZU00d2Z5RmZfbC1LY3c0RjRWM2dkbkJmNjRjMlZvVkxSWkFFQ0JMSWdkM1FKcmdOQTdzd1ZudGxNUEZGai1GdnA5Zm4xYmJRXzFOTlNBTUR2T3h2M1AxSnRRYlZGWVhkS002dkpwVENPdzFkeFltUmZUUm9OdVBTZXJ1Si1aa3owbXdNZXZhU3dLdVZR?oc=5</t>
+        </is>
+      </c>
+      <c r="V6" s="4" t="inlineStr">
+        <is>
+          <t>PGA Tour</t>
+        </is>
+      </c>
+      <c r="W6" s="4" t="inlineStr"/>
+      <c r="X6" s="4" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y6" s="4" t="inlineStr">
+        <is>
+          <t>WORKFORCE_REDUCTION</t>
+        </is>
+      </c>
+      <c r="Z6" s="4" t="inlineStr">
+        <is>
+          <t>layoff；layoffs</t>
+        </is>
+      </c>
+      <c r="AA6" s="4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB6" s="2" t="inlineStr"/>
-      <c r="AC6" s="2" t="inlineStr">
-        <is>
-          <t>933ef7caf63052209e76d5c9</t>
-        </is>
-      </c>
-      <c r="AD6" s="2" t="inlineStr">
-        <is>
-          <t>b18ab0e7b0df2c6140112fef</t>
-        </is>
-      </c>
-      <c r="AE6" s="2" t="inlineStr">
-        <is>
-          <t>XOM-REGULATORY_INVESTIGATION-001</t>
-        </is>
-      </c>
-      <c r="AF6" s="2" t="inlineStr"/>
-      <c r="AG6" s="2" t="inlineStr"/>
-      <c r="AH6" s="2" t="inlineStr"/>
-      <c r="AI6" s="2" t="inlineStr"/>
-      <c r="AJ6" s="2" t="inlineStr"/>
-      <c r="AK6" s="2" t="inlineStr"/>
-      <c r="AL6" s="2" t="inlineStr"/>
-      <c r="AM6" s="2" t="inlineStr"/>
-      <c r="AN6" s="2" t="inlineStr"/>
-      <c r="AO6" s="2" t="inlineStr"/>
-      <c r="AP6" s="2" t="inlineStr"/>
-      <c r="AQ6" s="2" t="inlineStr"/>
-      <c r="AR6" s="2" t="inlineStr"/>
-      <c r="AS6" s="2" t="inlineStr"/>
-      <c r="AT6" s="2" t="inlineStr"/>
-      <c r="AU6" s="2" t="inlineStr"/>
-      <c r="AV6" s="2" t="inlineStr"/>
-      <c r="AW6" s="2" t="inlineStr"/>
-      <c r="AX6" s="2" t="inlineStr"/>
-      <c r="AY6" s="2" t="inlineStr"/>
-      <c r="AZ6" s="2" t="inlineStr"/>
-      <c r="BA6" s="2" t="inlineStr"/>
-      <c r="BB6" s="2" t="inlineStr">
-        <is>
-          <t>XOM</t>
-        </is>
-      </c>
-      <c r="BC6" s="2" t="inlineStr">
+      <c r="AB6" s="4" t="inlineStr"/>
+      <c r="AC6" s="4" t="inlineStr">
+        <is>
+          <t>92096d9447cbe4262464271c</t>
+        </is>
+      </c>
+      <c r="AD6" s="4" t="inlineStr">
+        <is>
+          <t>6beb18eca6edec9226578611</t>
+        </is>
+      </c>
+      <c r="AE6" s="4" t="inlineStr">
+        <is>
+          <t>FDX-WORKFORCE_REDUCTION-001</t>
+        </is>
+      </c>
+      <c r="AF6" s="4" t="inlineStr"/>
+      <c r="AG6" s="4" t="inlineStr"/>
+      <c r="AH6" s="4" t="inlineStr"/>
+      <c r="AI6" s="4" t="inlineStr"/>
+      <c r="AJ6" s="4" t="inlineStr"/>
+      <c r="AK6" s="4" t="inlineStr"/>
+      <c r="AL6" s="4" t="inlineStr"/>
+      <c r="AM6" s="4" t="inlineStr"/>
+      <c r="AN6" s="4" t="inlineStr"/>
+      <c r="AO6" s="4" t="inlineStr"/>
+      <c r="AP6" s="4" t="inlineStr"/>
+      <c r="AQ6" s="4" t="inlineStr"/>
+      <c r="AR6" s="4" t="inlineStr"/>
+      <c r="AS6" s="4" t="inlineStr"/>
+      <c r="AT6" s="4" t="inlineStr"/>
+      <c r="AU6" s="4" t="inlineStr"/>
+      <c r="AV6" s="4" t="inlineStr"/>
+      <c r="AW6" s="4" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
+      <c r="AX6" s="4" t="inlineStr"/>
+      <c r="AY6" s="4" t="inlineStr"/>
+      <c r="AZ6" s="4" t="inlineStr"/>
+      <c r="BA6" s="4" t="inlineStr"/>
+      <c r="BB6" s="4" t="inlineStr">
+        <is>
+          <t>FDX</t>
+        </is>
+      </c>
+      <c r="BC6" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD6" s="2" t="inlineStr"/>
-      <c r="BE6" s="2" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF6" s="2" t="inlineStr"/>
-      <c r="BG6" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH6" s="2" t="inlineStr"/>
+      <c r="BD6" s="4" t="inlineStr"/>
+      <c r="BE6" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF6" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.957209+00:00</t>
+        </is>
+      </c>
+      <c r="BG6" s="4" t="inlineStr">
+        <is>
+          <t>交易所目前名單</t>
+        </is>
+      </c>
+      <c r="BH6" s="4" t="inlineStr"/>
+      <c r="BI6" s="4" t="inlineStr"/>
+      <c r="BJ6" s="4" t="inlineStr"/>
+      <c r="BK6" s="4" t="inlineStr"/>
+      <c r="BL6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -7284,22 +7756,22 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T19:35:31+08:00</t>
+          <t>2026-10-08T13:00:16+08:00</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Amazon makes fresh job cuts, mainly in retail division</t>
+          <t>Goldman Sachs Ensnared in EY Data Breach Earlier This Year</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr"/>
@@ -7310,7 +7782,7 @@
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>裁員或人力縮減</t>
+          <t>資料外洩</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -7336,7 +7808,7 @@
       </c>
       <c r="O7" s="4" t="inlineStr">
         <is>
-          <t>'-0.909</t>
+          <t>'-0.847</t>
         </is>
       </c>
       <c r="P7" s="4" t="inlineStr"/>
@@ -7350,28 +7822,28 @@
       </c>
       <c r="U7" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxOMXBaTUxRTVRaaEh2ajRtZWxDekFLVElmbi1oVEw1eFJyUDg4NG5TNGxTZGw1eUFSTWhTbHVERXU2R2p1YlBFRnZhcUFXSG9vQWhPcVFxN21jdDJaMFRLY0lSU0x0YUtBREl3UXBYaVFXZmNtNmdfVGhkUmt5bnZJOTg3eTBOdjlUdTNaRTlFSGQ5YTdLcjVwWnVkLUREN2dLSkhoaEhlMHQ0U2YwWWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE5Lc0NBNzJDeVdESGJSVWZhaFgtRnhJOC1MQm1GU3hLaFh1VnJhMk9ubFZfX2F6MnJaeUowMk5BQzF4MmZSS1UwczY5aVNWeVpwMXhmZ3YyZXh6dFVwSHpzNE90TXNQS1ZrRDdEY0ZvTGxiSTQ?oc=5</t>
         </is>
       </c>
       <c r="V7" s="4" t="inlineStr">
         <is>
-          <t>Reuters</t>
+          <t>Claims Journal</t>
         </is>
       </c>
       <c r="W7" s="4" t="inlineStr"/>
       <c r="X7" s="4" t="inlineStr">
         <is>
-          <t>OPERATIONS</t>
+          <t>CYBER</t>
         </is>
       </c>
       <c r="Y7" s="4" t="inlineStr">
         <is>
-          <t>WORKFORCE_REDUCTION</t>
+          <t>DATA_BREACH</t>
         </is>
       </c>
       <c r="Z7" s="4" t="inlineStr">
         <is>
-          <t>job cuts</t>
+          <t>data breach</t>
         </is>
       </c>
       <c r="AA7" s="4" t="inlineStr">
@@ -7382,17 +7854,17 @@
       <c r="AB7" s="4" t="inlineStr"/>
       <c r="AC7" s="4" t="inlineStr">
         <is>
-          <t>a2db2c67030d1a9d23e43a8b</t>
+          <t>86f75917141aafc70be3cb5d</t>
         </is>
       </c>
       <c r="AD7" s="4" t="inlineStr">
         <is>
-          <t>10c7c686523aa28cfbe010d3</t>
+          <t>0c48ccb7c65f57c24ba2ac79</t>
         </is>
       </c>
       <c r="AE7" s="4" t="inlineStr">
         <is>
-          <t>AMZN-WORKFORCE_REDUCTION-001</t>
+          <t>GS-DATA_BREACH-001</t>
         </is>
       </c>
       <c r="AF7" s="4" t="inlineStr"/>
@@ -7419,7 +7891,7 @@
       <c r="BA7" s="4" t="inlineStr"/>
       <c r="BB7" s="4" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="BC7" s="4" t="inlineStr">
@@ -7440,2105 +7912,397 @@
         </is>
       </c>
       <c r="BH7" s="4" t="inlineStr"/>
+      <c r="BI7" s="4" t="inlineStr"/>
+      <c r="BJ7" s="4" t="inlineStr"/>
+      <c r="BK7" s="4" t="inlineStr"/>
+      <c r="BL7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>XOM</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>ExxonMobil</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-08T18:29:34+08:00</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>ExxonMobil Director Vote Prompts US SEC Investigation Into Climate Action 100+; Regulator Pursues No Action Against Group</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>監管調查</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr"/>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Constellation Brands</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08T03:14:03+08:00</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Modelo owner Constellation is getting creative to bring back beer drinkers as overall demand weakens</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>營運惡化</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>待人工覆核</t>
+        </is>
+      </c>
+      <c r="M8" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="N8" s="4" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>'-0.069</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr"/>
-      <c r="Q8" s="2" t="inlineStr"/>
-      <c r="R8" s="2" t="inlineStr"/>
-      <c r="S8" s="2" t="inlineStr"/>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQam9qUlRFMDNUX1duNG40dDlEWTBpeHZwRXpVWFlTRjdwXzF2RzRSRFRXRmEwOTlPUE9DQ3lLQ0NjYnl0aTMydmtTWXBoUW1QenBqS0pkWFZOS29xSkNacGJlMkp6Wl90ZWlOeWVMU3ZoSWFsY0t1OFlkbGJLbktybzgwb3AzZ0tCNV9yVkljSndNSTdmMTdR?oc=5</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr"/>
-      <c r="X8" s="2" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y8" s="2" t="inlineStr">
-        <is>
-          <t>REGULATORY_INVESTIGATION</t>
-        </is>
-      </c>
-      <c r="Z8" s="2" t="inlineStr">
-        <is>
-          <t>SEC investigation</t>
-        </is>
-      </c>
-      <c r="AA8" s="2" t="inlineStr">
+      <c r="O8" s="4" t="inlineStr">
+        <is>
+          <t>0.294</t>
+        </is>
+      </c>
+      <c r="P8" s="4" t="inlineStr"/>
+      <c r="Q8" s="4" t="inlineStr"/>
+      <c r="R8" s="4" t="inlineStr"/>
+      <c r="S8" s="4" t="inlineStr"/>
+      <c r="T8" s="4" t="inlineStr">
+        <is>
+          <t>主體證據不足</t>
+        </is>
+      </c>
+      <c r="U8" s="4" t="inlineStr">
+        <is>
+          <t>https://www.cnbc.com/2026/10/07/constellation-brands-earnings-beer-demand.html</t>
+        </is>
+      </c>
+      <c r="V8" s="4" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="W8" s="4" t="inlineStr"/>
+      <c r="X8" s="4" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y8" s="4" t="inlineStr">
+        <is>
+          <t>OPERATING_DETERIORATION</t>
+        </is>
+      </c>
+      <c r="Z8" s="4" t="inlineStr">
+        <is>
+          <t>demand weakens</t>
+        </is>
+      </c>
+      <c r="AA8" s="4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB8" s="2" t="inlineStr"/>
-      <c r="AC8" s="2" t="inlineStr">
-        <is>
-          <t>52e928852f367f84def58be5</t>
-        </is>
-      </c>
-      <c r="AD8" s="2" t="inlineStr">
-        <is>
-          <t>a853d138cb477793c8bdce64</t>
-        </is>
-      </c>
-      <c r="AE8" s="2" t="inlineStr">
-        <is>
-          <t>XOM-REGULATORY_INVESTIGATION-001</t>
-        </is>
-      </c>
-      <c r="AF8" s="2" t="inlineStr"/>
-      <c r="AG8" s="2" t="inlineStr"/>
-      <c r="AH8" s="2" t="inlineStr"/>
-      <c r="AI8" s="2" t="inlineStr"/>
-      <c r="AJ8" s="2" t="inlineStr"/>
-      <c r="AK8" s="2" t="inlineStr"/>
-      <c r="AL8" s="2" t="inlineStr"/>
-      <c r="AM8" s="2" t="inlineStr"/>
-      <c r="AN8" s="2" t="inlineStr"/>
-      <c r="AO8" s="2" t="inlineStr"/>
-      <c r="AP8" s="2" t="inlineStr"/>
-      <c r="AQ8" s="2" t="inlineStr"/>
-      <c r="AR8" s="2" t="inlineStr"/>
-      <c r="AS8" s="2" t="inlineStr"/>
-      <c r="AT8" s="2" t="inlineStr"/>
-      <c r="AU8" s="2" t="inlineStr"/>
-      <c r="AV8" s="2" t="inlineStr"/>
-      <c r="AW8" s="2" t="inlineStr"/>
-      <c r="AX8" s="2" t="inlineStr"/>
-      <c r="AY8" s="2" t="inlineStr"/>
-      <c r="AZ8" s="2" t="inlineStr"/>
-      <c r="BA8" s="2" t="inlineStr"/>
-      <c r="BB8" s="2" t="inlineStr">
-        <is>
-          <t>XOM</t>
-        </is>
-      </c>
-      <c r="BC8" s="2" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD8" s="2" t="inlineStr"/>
-      <c r="BE8" s="2" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF8" s="2" t="inlineStr"/>
-      <c r="BG8" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH8" s="2" t="inlineStr"/>
+      <c r="AB8" s="4" t="inlineStr"/>
+      <c r="AC8" s="4" t="inlineStr">
+        <is>
+          <t>8d8850558267dbf8d0d2266f</t>
+        </is>
+      </c>
+      <c r="AD8" s="4" t="inlineStr">
+        <is>
+          <t>1f8743088a62046a79eb1e82</t>
+        </is>
+      </c>
+      <c r="AE8" s="4" t="inlineStr">
+        <is>
+          <t>STZ-OPERATING_DETERIORATION-001</t>
+        </is>
+      </c>
+      <c r="AF8" s="4" t="inlineStr"/>
+      <c r="AG8" s="4" t="inlineStr"/>
+      <c r="AH8" s="4" t="inlineStr"/>
+      <c r="AI8" s="4" t="inlineStr"/>
+      <c r="AJ8" s="4" t="inlineStr"/>
+      <c r="AK8" s="4" t="inlineStr"/>
+      <c r="AL8" s="4" t="inlineStr"/>
+      <c r="AM8" s="4" t="inlineStr"/>
+      <c r="AN8" s="4" t="inlineStr"/>
+      <c r="AO8" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AP8" s="4" t="inlineStr"/>
+      <c r="AQ8" s="4" t="inlineStr"/>
+      <c r="AR8" s="4" t="inlineStr"/>
+      <c r="AS8" s="4" t="inlineStr"/>
+      <c r="AT8" s="4" t="inlineStr"/>
+      <c r="AU8" s="4" t="inlineStr"/>
+      <c r="AV8" s="4" t="inlineStr"/>
+      <c r="AW8" s="4" t="inlineStr"/>
+      <c r="AX8" s="4" t="inlineStr"/>
+      <c r="AY8" s="4" t="inlineStr"/>
+      <c r="AZ8" s="4" t="inlineStr"/>
+      <c r="BA8" s="4" t="inlineStr"/>
+      <c r="BB8" s="4" t="inlineStr">
+        <is>
+          <t>STZ</t>
+        </is>
+      </c>
+      <c r="BC8" s="4" t="inlineStr">
+        <is>
+          <t>主體證據不足</t>
+        </is>
+      </c>
+      <c r="BD8" s="4" t="inlineStr">
+        <is>
+          <t>STZ</t>
+        </is>
+      </c>
+      <c r="BE8" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF8" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.957209+00:00</t>
+        </is>
+      </c>
+      <c r="BG8" s="4" t="inlineStr"/>
+      <c r="BH8" s="4" t="inlineStr"/>
+      <c r="BI8" s="4" t="inlineStr"/>
+      <c r="BJ8" s="4" t="inlineStr"/>
+      <c r="BK8" s="4" t="inlineStr"/>
+      <c r="BL8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>FDX</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>FedEx Corporation Common Stock</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-08T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>PGA TOUR Studios launches 'Tee Sheet presented by FedEx,' new weekly FedExCup Playoffs preview show</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr"/>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K9" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L9" s="4" t="inlineStr"/>
-      <c r="M9" s="4" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>BKNG</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Booking Holdings</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08T01:16:51+08:00</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>消息人士稱，Priceline因發布誤導性酒店廣告將面臨美國聯邦貿易委員會（FTC）的處罰</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>監管調查</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>0.069</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="2" t="inlineStr"/>
+      <c r="R9" s="2" t="inlineStr"/>
+      <c r="S9" s="2" t="inlineStr"/>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>主體證據不足</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>https://tw.tradingview.com/symbols/NASDAQ-BKNG/news/</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>TradingView</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr"/>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t>REGULATORY_INVESTIGATION</t>
+        </is>
+      </c>
+      <c r="Z9" s="2" t="inlineStr">
+        <is>
+          <t>FTC</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>56d54296786f4ef487a877d308e2b310</t>
+        </is>
+      </c>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>6c24a6b651101bbd050a5c0b</t>
+        </is>
+      </c>
+      <c r="AD9" s="2" t="inlineStr">
+        <is>
+          <t>26926663a032f19c53fb3dcc</t>
+        </is>
+      </c>
+      <c r="AE9" s="2" t="inlineStr">
+        <is>
+          <t>BKNG-REGULATORY_INVESTIGATION-001</t>
+        </is>
+      </c>
+      <c r="AF9" s="2" t="inlineStr"/>
+      <c r="AG9" s="2" t="inlineStr"/>
+      <c r="AH9" s="2" t="inlineStr"/>
+      <c r="AI9" s="2" t="inlineStr"/>
+      <c r="AJ9" s="2" t="inlineStr"/>
+      <c r="AK9" s="2" t="inlineStr"/>
+      <c r="AL9" s="2" t="inlineStr"/>
+      <c r="AM9" s="2" t="inlineStr"/>
+      <c r="AN9" s="2" t="inlineStr"/>
+      <c r="AO9" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N9" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O9" s="4" t="inlineStr">
-        <is>
-          <t>0.017</t>
-        </is>
-      </c>
-      <c r="P9" s="4" t="inlineStr"/>
-      <c r="Q9" s="4" t="inlineStr"/>
-      <c r="R9" s="4" t="inlineStr"/>
-      <c r="S9" s="4" t="inlineStr"/>
-      <c r="T9" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U9" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiqgJBVV95cUxNRjhJcmZtSldNOFRiVHFyOXpUaXNCNWhKcGx3SHg0THFxVUFhRDREQm5oTXpOS1BVcU9GT3BMWW1NVWJJbG81eEI1WktfVlJvcEh3VXY0YUxsS2t2bGRCUDdjbDJoVktnd3FuRFItc2lZWTdQVzNWTl9mUmdnV2ZtMzctYXg5UjlhVUxkY21POF9YaUpzTzRHVnVQQldIZU00d2Z5RmZfbC1LY3c0RjRWM2dkbkJmNjRjMlZvVkxSWkFFQ0JMSWdkM1FKcmdOQTdzd1ZudGxNUEZGai1GdnA5Zm4xYmJRXzFOTlNBTUR2T3h2M1AxSnRRYlZGWVhkS002dkpwVENPdzFkeFltUmZUUm9OdVBTZXJ1Si1aa3owbXdNZXZhU3dLdVZR?oc=5</t>
-        </is>
-      </c>
-      <c r="V9" s="4" t="inlineStr">
-        <is>
-          <t>PGA Tour</t>
-        </is>
-      </c>
-      <c r="W9" s="4" t="inlineStr"/>
-      <c r="X9" s="4" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y9" s="4" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z9" s="4" t="inlineStr">
-        <is>
-          <t>layoff；layoffs</t>
-        </is>
-      </c>
-      <c r="AA9" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="4" t="inlineStr"/>
-      <c r="AC9" s="4" t="inlineStr">
-        <is>
-          <t>92096d9447cbe4262464271c</t>
-        </is>
-      </c>
-      <c r="AD9" s="4" t="inlineStr">
-        <is>
-          <t>6beb18eca6edec9226578611</t>
-        </is>
-      </c>
-      <c r="AE9" s="4" t="inlineStr">
-        <is>
-          <t>FDX-WORKFORCE_REDUCTION-001</t>
-        </is>
-      </c>
-      <c r="AF9" s="4" t="inlineStr"/>
-      <c r="AG9" s="4" t="inlineStr"/>
-      <c r="AH9" s="4" t="inlineStr"/>
-      <c r="AI9" s="4" t="inlineStr"/>
-      <c r="AJ9" s="4" t="inlineStr"/>
-      <c r="AK9" s="4" t="inlineStr"/>
-      <c r="AL9" s="4" t="inlineStr"/>
-      <c r="AM9" s="4" t="inlineStr"/>
-      <c r="AN9" s="4" t="inlineStr"/>
-      <c r="AO9" s="4" t="inlineStr"/>
-      <c r="AP9" s="4" t="inlineStr"/>
-      <c r="AQ9" s="4" t="inlineStr"/>
-      <c r="AR9" s="4" t="inlineStr"/>
-      <c r="AS9" s="4" t="inlineStr"/>
-      <c r="AT9" s="4" t="inlineStr"/>
-      <c r="AU9" s="4" t="inlineStr"/>
-      <c r="AV9" s="4" t="inlineStr"/>
-      <c r="AW9" s="4" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX9" s="4" t="inlineStr"/>
-      <c r="AY9" s="4" t="inlineStr"/>
-      <c r="AZ9" s="4" t="inlineStr"/>
-      <c r="BA9" s="4" t="inlineStr"/>
-      <c r="BB9" s="4" t="inlineStr">
-        <is>
-          <t>FDX</t>
-        </is>
-      </c>
-      <c r="BC9" s="4" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD9" s="4" t="inlineStr"/>
-      <c r="BE9" s="4" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF9" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG9" s="4" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH9" s="4" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>GS</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>Goldman Sachs</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-08T13:00:16+08:00</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>Goldman Sachs Ensnared in EY Data Breach Earlier This Year</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr"/>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>資料外洩</t>
-        </is>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K10" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L10" s="4" t="inlineStr"/>
-      <c r="M10" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N10" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O10" s="4" t="inlineStr">
-        <is>
-          <t>'-0.847</t>
-        </is>
-      </c>
-      <c r="P10" s="4" t="inlineStr"/>
-      <c r="Q10" s="4" t="inlineStr"/>
-      <c r="R10" s="4" t="inlineStr"/>
-      <c r="S10" s="4" t="inlineStr"/>
-      <c r="T10" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U10" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE5Lc0NBNzJDeVdESGJSVWZhaFgtRnhJOC1MQm1GU3hLaFh1VnJhMk9ubFZfX2F6MnJaeUowMk5BQzF4MmZSS1UwczY5aVNWeVpwMXhmZ3YyZXh6dFVwSHpzNE90TXNQS1ZrRDdEY0ZvTGxiSTQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V10" s="4" t="inlineStr">
-        <is>
-          <t>Claims Journal</t>
-        </is>
-      </c>
-      <c r="W10" s="4" t="inlineStr"/>
-      <c r="X10" s="4" t="inlineStr">
-        <is>
-          <t>CYBER</t>
-        </is>
-      </c>
-      <c r="Y10" s="4" t="inlineStr">
-        <is>
-          <t>DATA_BREACH</t>
-        </is>
-      </c>
-      <c r="Z10" s="4" t="inlineStr">
-        <is>
-          <t>data breach</t>
-        </is>
-      </c>
-      <c r="AA10" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="4" t="inlineStr"/>
-      <c r="AC10" s="4" t="inlineStr">
-        <is>
-          <t>86f75917141aafc70be3cb5d</t>
-        </is>
-      </c>
-      <c r="AD10" s="4" t="inlineStr">
-        <is>
-          <t>0c48ccb7c65f57c24ba2ac79</t>
-        </is>
-      </c>
-      <c r="AE10" s="4" t="inlineStr">
-        <is>
-          <t>GS-DATA_BREACH-001</t>
-        </is>
-      </c>
-      <c r="AF10" s="4" t="inlineStr"/>
-      <c r="AG10" s="4" t="inlineStr"/>
-      <c r="AH10" s="4" t="inlineStr"/>
-      <c r="AI10" s="4" t="inlineStr"/>
-      <c r="AJ10" s="4" t="inlineStr"/>
-      <c r="AK10" s="4" t="inlineStr"/>
-      <c r="AL10" s="4" t="inlineStr"/>
-      <c r="AM10" s="4" t="inlineStr"/>
-      <c r="AN10" s="4" t="inlineStr"/>
-      <c r="AO10" s="4" t="inlineStr"/>
-      <c r="AP10" s="4" t="inlineStr"/>
-      <c r="AQ10" s="4" t="inlineStr"/>
-      <c r="AR10" s="4" t="inlineStr"/>
-      <c r="AS10" s="4" t="inlineStr"/>
-      <c r="AT10" s="4" t="inlineStr"/>
-      <c r="AU10" s="4" t="inlineStr"/>
-      <c r="AV10" s="4" t="inlineStr"/>
-      <c r="AW10" s="4" t="inlineStr"/>
-      <c r="AX10" s="4" t="inlineStr"/>
-      <c r="AY10" s="4" t="inlineStr"/>
-      <c r="AZ10" s="4" t="inlineStr"/>
-      <c r="BA10" s="4" t="inlineStr"/>
-      <c r="BB10" s="4" t="inlineStr">
-        <is>
-          <t>GS</t>
-        </is>
-      </c>
-      <c r="BC10" s="4" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD10" s="4" t="inlineStr"/>
-      <c r="BE10" s="4" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF10" s="4" t="inlineStr"/>
-      <c r="BG10" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH10" s="4" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>DUK</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Duke Energy</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-08T07:44:03+08:00</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Duke Energy Reaches Settlement Requiring Data Centers To Pay Upfront Grid Connection Costs In N.C.</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>'-0.904</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr"/>
-      <c r="Q11" s="2" t="inlineStr"/>
-      <c r="R11" s="2" t="inlineStr"/>
-      <c r="S11" s="2" t="inlineStr"/>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQSlN2VkVfS3hUVU5EQmh6N2JCa0cwS1FJYUxoWmFqM0JTeWNTLU9VbEtOa083eTd3b3FVOWdaNFUtRFBkVkhWZGo1V2VfR3JhYzlILVNQZHRPNXppT0NaMGJUV0I3TVViMUNkRDdVakdnU0ZMcUtCUzM1Ums0WFhCZzhDSEUzU0ZsOXF1UndvTWcxNmQxVFJBYjJWRWFTQQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr"/>
-      <c r="X11" s="2" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y11" s="2" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z11" s="2" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
-      <c r="AC11" s="2" t="inlineStr">
-        <is>
-          <t>489ddfc61d708d0afe70f27e</t>
-        </is>
-      </c>
-      <c r="AD11" s="2" t="inlineStr">
-        <is>
-          <t>055c89085873416a44a38958</t>
-        </is>
-      </c>
-      <c r="AE11" s="2" t="inlineStr">
-        <is>
-          <t>DUK-REGULATORY_PENALTY-001</t>
-        </is>
-      </c>
-      <c r="AF11" s="2" t="inlineStr"/>
-      <c r="AG11" s="2" t="inlineStr"/>
-      <c r="AH11" s="2" t="inlineStr"/>
-      <c r="AI11" s="2" t="inlineStr"/>
-      <c r="AJ11" s="2" t="inlineStr"/>
-      <c r="AK11" s="2" t="inlineStr"/>
-      <c r="AL11" s="2" t="inlineStr"/>
-      <c r="AM11" s="2" t="inlineStr"/>
-      <c r="AN11" s="2" t="inlineStr"/>
-      <c r="AO11" s="2" t="inlineStr"/>
-      <c r="AP11" s="2" t="inlineStr"/>
-      <c r="AQ11" s="2" t="inlineStr"/>
-      <c r="AR11" s="2" t="inlineStr"/>
-      <c r="AS11" s="2" t="inlineStr"/>
-      <c r="AT11" s="2" t="inlineStr"/>
-      <c r="AU11" s="2" t="inlineStr"/>
-      <c r="AV11" s="2" t="inlineStr"/>
-      <c r="AW11" s="2" t="inlineStr"/>
-      <c r="AX11" s="2" t="inlineStr"/>
-      <c r="AY11" s="2" t="inlineStr"/>
-      <c r="AZ11" s="2" t="inlineStr"/>
-      <c r="BA11" s="2" t="inlineStr"/>
-      <c r="BB11" s="2" t="inlineStr">
-        <is>
-          <t>DUK</t>
-        </is>
-      </c>
-      <c r="BC11" s="2" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD11" s="2" t="inlineStr"/>
-      <c r="BE11" s="2" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF11" s="2" t="inlineStr"/>
-      <c r="BG11" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH11" s="2" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>CMS</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>CMS Energy Corporation Common Stock</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-08T05:01:21+08:00</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Nursing home takes fight over CMS penalty authority to Supreme Court</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>'-0.484</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr"/>
-      <c r="Q12" s="2" t="inlineStr"/>
-      <c r="R12" s="2" t="inlineStr"/>
-      <c r="S12" s="2" t="inlineStr"/>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPamcyWWVnQ09CSXJmMWQ0ZjJxXzZNd01fT3pET20yLXpPS09LZWRqMmdEWUdFWklhZHlXYm1JNFFpUUVvME4tWmQyUHVZZXlqYkZuQWJic1BQSWktLUpTX1RtVkVLUy1qV2o3Zmk5Z3ZsekhXTUFWdi14WWU0OUs3dDdVcGc5WnNwMU5WWVozMGJFUFRNdUNxMlFZWHFWWVdVeVE?oc=5</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>McKnight's Long-Term Care News</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr"/>
-      <c r="X12" s="2" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y12" s="2" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z12" s="2" t="inlineStr">
-        <is>
-          <t>penalty</t>
-        </is>
-      </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB12" s="2" t="inlineStr"/>
-      <c r="AC12" s="2" t="inlineStr">
-        <is>
-          <t>658a733daaf57ab96f019658</t>
-        </is>
-      </c>
-      <c r="AD12" s="2" t="inlineStr">
-        <is>
-          <t>0a40d2da69a8540dbe451850</t>
-        </is>
-      </c>
-      <c r="AE12" s="2" t="inlineStr">
-        <is>
-          <t>CMS-REGULATORY_PENALTY-001</t>
-        </is>
-      </c>
-      <c r="AF12" s="2" t="inlineStr"/>
-      <c r="AG12" s="2" t="inlineStr"/>
-      <c r="AH12" s="2" t="inlineStr"/>
-      <c r="AI12" s="2" t="inlineStr"/>
-      <c r="AJ12" s="2" t="inlineStr"/>
-      <c r="AK12" s="2" t="inlineStr"/>
-      <c r="AL12" s="2" t="inlineStr"/>
-      <c r="AM12" s="2" t="inlineStr"/>
-      <c r="AN12" s="2" t="inlineStr"/>
-      <c r="AO12" s="2" t="inlineStr"/>
-      <c r="AP12" s="2" t="inlineStr"/>
-      <c r="AQ12" s="2" t="inlineStr"/>
-      <c r="AR12" s="2" t="inlineStr"/>
-      <c r="AS12" s="2" t="inlineStr"/>
-      <c r="AT12" s="2" t="inlineStr"/>
-      <c r="AU12" s="2" t="inlineStr"/>
-      <c r="AV12" s="2" t="inlineStr"/>
-      <c r="AW12" s="2" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX12" s="2" t="inlineStr"/>
-      <c r="AY12" s="2" t="inlineStr"/>
-      <c r="AZ12" s="2" t="inlineStr"/>
-      <c r="BA12" s="2" t="inlineStr"/>
-      <c r="BB12" s="2" t="inlineStr">
-        <is>
-          <t>CMS</t>
-        </is>
-      </c>
-      <c r="BC12" s="2" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD12" s="2" t="inlineStr"/>
-      <c r="BE12" s="2" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF12" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG12" s="2" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>DUK</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Duke Energy</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-08T04:13:03+08:00</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Duke Energy, NC Public Staff Reach Settlement on Data Center Costs</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr"/>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>'-0.87</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr"/>
-      <c r="Q13" s="2" t="inlineStr"/>
-      <c r="R13" s="2" t="inlineStr"/>
-      <c r="S13" s="2" t="inlineStr"/>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPY0NlM1pNMDZnZlR2bjliMmdxX0hwRng0OEV5elcxR3VyX3h1d213T3NoeWdkdjVLMG9UTmJRR0dCeUdmcjVSZmpRLUtqSTM2Qk5TbTYzU1RPRnNyTTVYRl9vMHhvUXgzU092QUcxR19RcjdnRUtZa1N2YXNPMW44R0Q5dFJad3gxRzZDQ1h1eDA?oc=5</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Unite.AI</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr"/>
-      <c r="X13" s="2" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y13" s="2" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z13" s="2" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB13" s="2" t="inlineStr"/>
-      <c r="AC13" s="2" t="inlineStr">
-        <is>
-          <t>18411cab75cb71cb78f93e94</t>
-        </is>
-      </c>
-      <c r="AD13" s="2" t="inlineStr">
-        <is>
-          <t>9b059848cb04eeb5f0c3f583</t>
-        </is>
-      </c>
-      <c r="AE13" s="2" t="inlineStr">
-        <is>
-          <t>DUK-REGULATORY_PENALTY-001</t>
-        </is>
-      </c>
-      <c r="AF13" s="2" t="inlineStr"/>
-      <c r="AG13" s="2" t="inlineStr"/>
-      <c r="AH13" s="2" t="inlineStr"/>
-      <c r="AI13" s="2" t="inlineStr"/>
-      <c r="AJ13" s="2" t="inlineStr"/>
-      <c r="AK13" s="2" t="inlineStr"/>
-      <c r="AL13" s="2" t="inlineStr"/>
-      <c r="AM13" s="2" t="inlineStr"/>
-      <c r="AN13" s="2" t="inlineStr"/>
-      <c r="AO13" s="2" t="inlineStr"/>
-      <c r="AP13" s="2" t="inlineStr"/>
-      <c r="AQ13" s="2" t="inlineStr"/>
-      <c r="AR13" s="2" t="inlineStr"/>
-      <c r="AS13" s="2" t="inlineStr"/>
-      <c r="AT13" s="2" t="inlineStr"/>
-      <c r="AU13" s="2" t="inlineStr"/>
-      <c r="AV13" s="2" t="inlineStr"/>
-      <c r="AW13" s="2" t="inlineStr"/>
-      <c r="AX13" s="2" t="inlineStr"/>
-      <c r="AY13" s="2" t="inlineStr"/>
-      <c r="AZ13" s="2" t="inlineStr"/>
-      <c r="BA13" s="2" t="inlineStr"/>
-      <c r="BB13" s="2" t="inlineStr">
-        <is>
-          <t>DUK</t>
-        </is>
-      </c>
-      <c r="BC13" s="2" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD13" s="2" t="inlineStr"/>
-      <c r="BE13" s="2" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF13" s="2" t="inlineStr"/>
-      <c r="BG13" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH13" s="2" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>UBER</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Uber Technologies, Inc. Common Stock</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-08T03:47:56+08:00</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Uber class action alleges company enrolled users in Uber One without consent</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr"/>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>'-0.669</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr"/>
-      <c r="Q14" s="2" t="inlineStr"/>
-      <c r="R14" s="2" t="inlineStr"/>
-      <c r="S14" s="2" t="inlineStr"/>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPQTF5YmpWOXI5bmRMdy1Gd1l0cXZSODJoT3Q3STJYUkxQRV9qYm9JSEpUWk9hODQzYWdDeGczdk1XeGxlaXZNSU9naFVqMGFMZEcyVXlqV1ZmXzJnSE9TeEFMZ0VxXzZCZzBCQ2QtSWxLOERGYXZiRGRZcGhMNzViTC1oSld4WmQ0cjQ4d3JzOXZ0Z2IwVjhYOTRkUVFwRXd5X2xsaUxfNWZWd0JTeTQxTDdRSzQxSTNQcDFObFl0VQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Claim Depot</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr"/>
-      <c r="X14" s="2" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y14" s="2" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z14" s="2" t="inlineStr">
-        <is>
-          <t>class action</t>
-        </is>
-      </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB14" s="2" t="inlineStr"/>
-      <c r="AC14" s="2" t="inlineStr">
-        <is>
-          <t>4e08db63479dad56e0723932</t>
-        </is>
-      </c>
-      <c r="AD14" s="2" t="inlineStr">
-        <is>
-          <t>a47ec3a8e00258e537cfdb3e</t>
-        </is>
-      </c>
-      <c r="AE14" s="2" t="inlineStr">
-        <is>
-          <t>UBER-MAJOR_LITIGATION-001</t>
-        </is>
-      </c>
-      <c r="AF14" s="2" t="inlineStr"/>
-      <c r="AG14" s="2" t="inlineStr"/>
-      <c r="AH14" s="2" t="inlineStr"/>
-      <c r="AI14" s="2" t="inlineStr"/>
-      <c r="AJ14" s="2" t="inlineStr"/>
-      <c r="AK14" s="2" t="inlineStr"/>
-      <c r="AL14" s="2" t="inlineStr"/>
-      <c r="AM14" s="2" t="inlineStr"/>
-      <c r="AN14" s="2" t="inlineStr"/>
-      <c r="AO14" s="2" t="inlineStr"/>
-      <c r="AP14" s="2" t="inlineStr"/>
-      <c r="AQ14" s="2" t="inlineStr"/>
-      <c r="AR14" s="2" t="inlineStr"/>
-      <c r="AS14" s="2" t="inlineStr"/>
-      <c r="AT14" s="2" t="inlineStr"/>
-      <c r="AU14" s="2" t="inlineStr"/>
-      <c r="AV14" s="2" t="inlineStr"/>
-      <c r="AW14" s="2" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX14" s="2" t="inlineStr"/>
-      <c r="AY14" s="2" t="inlineStr"/>
-      <c r="AZ14" s="2" t="inlineStr"/>
-      <c r="BA14" s="2" t="inlineStr"/>
-      <c r="BB14" s="2" t="inlineStr">
-        <is>
-          <t>UBER</t>
-        </is>
-      </c>
-      <c r="BC14" s="2" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD14" s="2" t="inlineStr"/>
-      <c r="BE14" s="2" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF14" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG14" s="2" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH14" s="2" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr"/>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>Constellation Brands</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-08T03:14:03+08:00</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>Modelo owner Constellation is getting creative to bring back beer drinkers as overall demand weakens</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr"/>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I15" s="4" t="inlineStr">
-        <is>
-          <t>營運惡化</t>
-        </is>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K15" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L15" s="4" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M15" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N15" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O15" s="4" t="inlineStr">
-        <is>
-          <t>0.294</t>
-        </is>
-      </c>
-      <c r="P15" s="4" t="inlineStr"/>
-      <c r="Q15" s="4" t="inlineStr"/>
-      <c r="R15" s="4" t="inlineStr"/>
-      <c r="S15" s="4" t="inlineStr"/>
-      <c r="T15" s="4" t="inlineStr">
+      <c r="AP9" s="2" t="inlineStr"/>
+      <c r="AQ9" s="2" t="inlineStr"/>
+      <c r="AR9" s="2" t="inlineStr"/>
+      <c r="AS9" s="2" t="inlineStr"/>
+      <c r="AT9" s="2" t="inlineStr"/>
+      <c r="AU9" s="2" t="inlineStr"/>
+      <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" s="2" t="inlineStr"/>
+      <c r="AX9" s="2" t="inlineStr"/>
+      <c r="AY9" s="2" t="inlineStr"/>
+      <c r="AZ9" s="2" t="inlineStr"/>
+      <c r="BA9" s="2" t="inlineStr"/>
+      <c r="BB9" s="2" t="inlineStr">
+        <is>
+          <t>BKNG</t>
+        </is>
+      </c>
+      <c r="BC9" s="2" t="inlineStr">
         <is>
           <t>主體證據不足</t>
         </is>
       </c>
-      <c r="U15" s="4" t="inlineStr">
-        <is>
-          <t>https://www.cnbc.com/2026/10/07/constellation-brands-earnings-beer-demand.html</t>
-        </is>
-      </c>
-      <c r="V15" s="4" t="inlineStr">
-        <is>
-          <t>CNBC</t>
-        </is>
-      </c>
-      <c r="W15" s="4" t="inlineStr"/>
-      <c r="X15" s="4" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y15" s="4" t="inlineStr">
-        <is>
-          <t>OPERATING_DETERIORATION</t>
-        </is>
-      </c>
-      <c r="Z15" s="4" t="inlineStr">
-        <is>
-          <t>demand weakens</t>
-        </is>
-      </c>
-      <c r="AA15" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB15" s="4" t="inlineStr"/>
-      <c r="AC15" s="4" t="inlineStr">
-        <is>
-          <t>8d8850558267dbf8d0d2266f</t>
-        </is>
-      </c>
-      <c r="AD15" s="4" t="inlineStr">
-        <is>
-          <t>1f8743088a62046a79eb1e82</t>
-        </is>
-      </c>
-      <c r="AE15" s="4" t="inlineStr">
-        <is>
-          <t>STZ-OPERATING_DETERIORATION-001</t>
-        </is>
-      </c>
-      <c r="AF15" s="4" t="inlineStr"/>
-      <c r="AG15" s="4" t="inlineStr"/>
-      <c r="AH15" s="4" t="inlineStr"/>
-      <c r="AI15" s="4" t="inlineStr"/>
-      <c r="AJ15" s="4" t="inlineStr"/>
-      <c r="AK15" s="4" t="inlineStr"/>
-      <c r="AL15" s="4" t="inlineStr"/>
-      <c r="AM15" s="4" t="inlineStr"/>
-      <c r="AN15" s="4" t="inlineStr"/>
-      <c r="AO15" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP15" s="4" t="inlineStr"/>
-      <c r="AQ15" s="4" t="inlineStr"/>
-      <c r="AR15" s="4" t="inlineStr"/>
-      <c r="AS15" s="4" t="inlineStr"/>
-      <c r="AT15" s="4" t="inlineStr"/>
-      <c r="AU15" s="4" t="inlineStr"/>
-      <c r="AV15" s="4" t="inlineStr"/>
-      <c r="AW15" s="4" t="inlineStr"/>
-      <c r="AX15" s="4" t="inlineStr"/>
-      <c r="AY15" s="4" t="inlineStr"/>
-      <c r="AZ15" s="4" t="inlineStr"/>
-      <c r="BA15" s="4" t="inlineStr"/>
-      <c r="BB15" s="4" t="inlineStr">
-        <is>
-          <t>STZ</t>
-        </is>
-      </c>
-      <c r="BC15" s="4" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD15" s="4" t="inlineStr">
-        <is>
-          <t>STZ</t>
-        </is>
-      </c>
-      <c r="BE15" s="4" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF15" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG15" s="4" t="inlineStr"/>
-      <c r="BH15" s="4" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr"/>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Marriott International</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-08T01:16:51+08:00</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>消息人士稱，Priceline因發布誤導性酒店廣告將面臨美國聯邦貿易委員會（FTC）的處罰</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>監管調查</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0.069</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr"/>
-      <c r="Q16" s="2" t="inlineStr"/>
-      <c r="R16" s="2" t="inlineStr"/>
-      <c r="S16" s="2" t="inlineStr"/>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>https://tw.tradingview.com/symbols/NASDAQ-MAR/news/</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr"/>
-      <c r="X16" s="2" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y16" s="2" t="inlineStr">
-        <is>
-          <t>REGULATORY_INVESTIGATION</t>
-        </is>
-      </c>
-      <c r="Z16" s="2" t="inlineStr">
-        <is>
-          <t>FTC</t>
-        </is>
-      </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB16" s="2" t="inlineStr"/>
-      <c r="AC16" s="2" t="inlineStr">
-        <is>
-          <t>3fa2144c2654b305167099fd</t>
-        </is>
-      </c>
-      <c r="AD16" s="2" t="inlineStr">
-        <is>
-          <t>06a16fc3d0d85d6619b772bf</t>
-        </is>
-      </c>
-      <c r="AE16" s="2" t="inlineStr">
-        <is>
-          <t>MAR-REGULATORY_INVESTIGATION-001</t>
-        </is>
-      </c>
-      <c r="AF16" s="2" t="inlineStr"/>
-      <c r="AG16" s="2" t="inlineStr"/>
-      <c r="AH16" s="2" t="inlineStr"/>
-      <c r="AI16" s="2" t="inlineStr"/>
-      <c r="AJ16" s="2" t="inlineStr"/>
-      <c r="AK16" s="2" t="inlineStr"/>
-      <c r="AL16" s="2" t="inlineStr"/>
-      <c r="AM16" s="2" t="inlineStr"/>
-      <c r="AN16" s="2" t="inlineStr"/>
-      <c r="AO16" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP16" s="2" t="inlineStr"/>
-      <c r="AQ16" s="2" t="inlineStr"/>
-      <c r="AR16" s="2" t="inlineStr"/>
-      <c r="AS16" s="2" t="inlineStr"/>
-      <c r="AT16" s="2" t="inlineStr"/>
-      <c r="AU16" s="2" t="inlineStr"/>
-      <c r="AV16" s="2" t="inlineStr"/>
-      <c r="AW16" s="2" t="inlineStr"/>
-      <c r="AX16" s="2" t="inlineStr"/>
-      <c r="AY16" s="2" t="inlineStr"/>
-      <c r="AZ16" s="2" t="inlineStr"/>
-      <c r="BA16" s="2" t="inlineStr"/>
-      <c r="BB16" s="2" t="inlineStr">
-        <is>
-          <t>MAR</t>
-        </is>
-      </c>
-      <c r="BC16" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD16" s="2" t="inlineStr">
-        <is>
-          <t>MAR</t>
-        </is>
-      </c>
-      <c r="BE16" s="2" t="inlineStr">
+      <c r="BD9" s="2" t="inlineStr">
+        <is>
+          <t>BKNG</t>
+        </is>
+      </c>
+      <c r="BE9" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
-      <c r="BF16" s="2" t="inlineStr">
+      <c r="BF9" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
-      <c r="BG16" s="2" t="inlineStr"/>
-      <c r="BH16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr"/>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Booking Holdings</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-08T01:16:51+08:00</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>消息人士稱，Priceline因發布誤導性酒店廣告將面臨美國聯邦貿易委員會（FTC）的處罰</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>監管調查</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>0.069</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr"/>
-      <c r="Q17" s="2" t="inlineStr"/>
-      <c r="R17" s="2" t="inlineStr"/>
-      <c r="S17" s="2" t="inlineStr"/>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>https://tw.tradingview.com/symbols/NASDAQ-BKNG/news/</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr"/>
-      <c r="X17" s="2" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y17" s="2" t="inlineStr">
-        <is>
-          <t>REGULATORY_INVESTIGATION</t>
-        </is>
-      </c>
-      <c r="Z17" s="2" t="inlineStr">
-        <is>
-          <t>FTC</t>
-        </is>
-      </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB17" s="2" t="inlineStr"/>
-      <c r="AC17" s="2" t="inlineStr">
-        <is>
-          <t>6c24a6b651101bbd050a5c0b</t>
-        </is>
-      </c>
-      <c r="AD17" s="2" t="inlineStr">
-        <is>
-          <t>26926663a032f19c53fb3dcc</t>
-        </is>
-      </c>
-      <c r="AE17" s="2" t="inlineStr">
-        <is>
-          <t>BKNG-REGULATORY_INVESTIGATION-001</t>
-        </is>
-      </c>
-      <c r="AF17" s="2" t="inlineStr"/>
-      <c r="AG17" s="2" t="inlineStr"/>
-      <c r="AH17" s="2" t="inlineStr"/>
-      <c r="AI17" s="2" t="inlineStr"/>
-      <c r="AJ17" s="2" t="inlineStr"/>
-      <c r="AK17" s="2" t="inlineStr"/>
-      <c r="AL17" s="2" t="inlineStr"/>
-      <c r="AM17" s="2" t="inlineStr"/>
-      <c r="AN17" s="2" t="inlineStr"/>
-      <c r="AO17" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP17" s="2" t="inlineStr"/>
-      <c r="AQ17" s="2" t="inlineStr"/>
-      <c r="AR17" s="2" t="inlineStr"/>
-      <c r="AS17" s="2" t="inlineStr"/>
-      <c r="AT17" s="2" t="inlineStr"/>
-      <c r="AU17" s="2" t="inlineStr"/>
-      <c r="AV17" s="2" t="inlineStr"/>
-      <c r="AW17" s="2" t="inlineStr"/>
-      <c r="AX17" s="2" t="inlineStr"/>
-      <c r="AY17" s="2" t="inlineStr"/>
-      <c r="AZ17" s="2" t="inlineStr"/>
-      <c r="BA17" s="2" t="inlineStr"/>
-      <c r="BB17" s="2" t="inlineStr">
-        <is>
-          <t>BKNG</t>
-        </is>
-      </c>
-      <c r="BC17" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD17" s="2" t="inlineStr">
-        <is>
-          <t>BKNG</t>
-        </is>
-      </c>
-      <c r="BE17" s="2" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF17" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG17" s="2" t="inlineStr"/>
-      <c r="BH17" s="2" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr"/>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Expedia Group</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-08T01:16:51+08:00</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>消息人士稱，Priceline因發布誤導性酒店廣告將面臨美國聯邦貿易委員會（FTC）的處罰</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>監管調查</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>0.069</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr"/>
-      <c r="Q18" s="2" t="inlineStr"/>
-      <c r="R18" s="2" t="inlineStr"/>
-      <c r="S18" s="2" t="inlineStr"/>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>https://tw.tradingview.com/symbols/NASDAQ-EXPE/news/</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr"/>
-      <c r="X18" s="2" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y18" s="2" t="inlineStr">
-        <is>
-          <t>REGULATORY_INVESTIGATION</t>
-        </is>
-      </c>
-      <c r="Z18" s="2" t="inlineStr">
-        <is>
-          <t>FTC</t>
-        </is>
-      </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB18" s="2" t="inlineStr"/>
-      <c r="AC18" s="2" t="inlineStr">
-        <is>
-          <t>d25efedb84fdd99d661c0c8d</t>
-        </is>
-      </c>
-      <c r="AD18" s="2" t="inlineStr">
-        <is>
-          <t>e8fa0af2431213fe919a445f</t>
-        </is>
-      </c>
-      <c r="AE18" s="2" t="inlineStr">
-        <is>
-          <t>EXPE-REGULATORY_INVESTIGATION-001</t>
-        </is>
-      </c>
-      <c r="AF18" s="2" t="inlineStr"/>
-      <c r="AG18" s="2" t="inlineStr"/>
-      <c r="AH18" s="2" t="inlineStr"/>
-      <c r="AI18" s="2" t="inlineStr"/>
-      <c r="AJ18" s="2" t="inlineStr"/>
-      <c r="AK18" s="2" t="inlineStr"/>
-      <c r="AL18" s="2" t="inlineStr"/>
-      <c r="AM18" s="2" t="inlineStr"/>
-      <c r="AN18" s="2" t="inlineStr"/>
-      <c r="AO18" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP18" s="2" t="inlineStr"/>
-      <c r="AQ18" s="2" t="inlineStr"/>
-      <c r="AR18" s="2" t="inlineStr"/>
-      <c r="AS18" s="2" t="inlineStr"/>
-      <c r="AT18" s="2" t="inlineStr"/>
-      <c r="AU18" s="2" t="inlineStr"/>
-      <c r="AV18" s="2" t="inlineStr"/>
-      <c r="AW18" s="2" t="inlineStr"/>
-      <c r="AX18" s="2" t="inlineStr"/>
-      <c r="AY18" s="2" t="inlineStr"/>
-      <c r="AZ18" s="2" t="inlineStr"/>
-      <c r="BA18" s="2" t="inlineStr"/>
-      <c r="BB18" s="2" t="inlineStr">
-        <is>
-          <t>EXPE</t>
-        </is>
-      </c>
-      <c r="BC18" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD18" s="2" t="inlineStr">
-        <is>
-          <t>EXPE</t>
-        </is>
-      </c>
-      <c r="BE18" s="2" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF18" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG18" s="2" t="inlineStr"/>
-      <c r="BH18" s="2" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>XOM</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>ExxonMobil</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-08T00:48:21+08:00</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>Weil Wins Dismissal of Plastics Class Action for ExxonMobil</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr"/>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>'-0.734</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr"/>
-      <c r="Q19" s="2" t="inlineStr"/>
-      <c r="R19" s="2" t="inlineStr"/>
-      <c r="S19" s="2" t="inlineStr"/>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPZmVQN0llTEJsUWQxMXF4ZWQ1MXAyOGZXUzdEc0hkcUMyTEVZZF9tMjZIZkFwY0h4dDZrVFhEd0RxWW5lZWkweGN4NnhaT2pabkl5MFNyd3pUdnJLZzNwbVRwZjg0V2JGa1NwLVp5UXBBNHhYcmt3ODhiSzR5RklVX0VoMU1WTVlXQU9FQUJEejk2SzQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Weil</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr"/>
-      <c r="X19" s="2" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y19" s="2" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z19" s="2" t="inlineStr">
-        <is>
-          <t>class action</t>
-        </is>
-      </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB19" s="2" t="inlineStr"/>
-      <c r="AC19" s="2" t="inlineStr">
-        <is>
-          <t>6168931c1522728631b435be</t>
-        </is>
-      </c>
-      <c r="AD19" s="2" t="inlineStr">
-        <is>
-          <t>a56141ede6d0d4ab2b1ad0df</t>
-        </is>
-      </c>
-      <c r="AE19" s="2" t="inlineStr">
-        <is>
-          <t>XOM-MAJOR_LITIGATION-001</t>
-        </is>
-      </c>
-      <c r="AF19" s="2" t="inlineStr"/>
-      <c r="AG19" s="2" t="inlineStr"/>
-      <c r="AH19" s="2" t="inlineStr"/>
-      <c r="AI19" s="2" t="inlineStr"/>
-      <c r="AJ19" s="2" t="inlineStr"/>
-      <c r="AK19" s="2" t="inlineStr"/>
-      <c r="AL19" s="2" t="inlineStr"/>
-      <c r="AM19" s="2" t="inlineStr"/>
-      <c r="AN19" s="2" t="inlineStr"/>
-      <c r="AO19" s="2" t="inlineStr"/>
-      <c r="AP19" s="2" t="inlineStr"/>
-      <c r="AQ19" s="2" t="inlineStr"/>
-      <c r="AR19" s="2" t="inlineStr"/>
-      <c r="AS19" s="2" t="inlineStr"/>
-      <c r="AT19" s="2" t="inlineStr"/>
-      <c r="AU19" s="2" t="inlineStr"/>
-      <c r="AV19" s="2" t="inlineStr"/>
-      <c r="AW19" s="2" t="inlineStr"/>
-      <c r="AX19" s="2" t="inlineStr"/>
-      <c r="AY19" s="2" t="inlineStr"/>
-      <c r="AZ19" s="2" t="inlineStr"/>
-      <c r="BA19" s="2" t="inlineStr"/>
-      <c r="BB19" s="2" t="inlineStr">
-        <is>
-          <t>XOM</t>
-        </is>
-      </c>
-      <c r="BC19" s="2" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD19" s="2" t="inlineStr"/>
-      <c r="BE19" s="2" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF19" s="2" t="inlineStr"/>
-      <c r="BG19" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH19" s="2" t="inlineStr"/>
+      <c r="BG9" s="2" t="inlineStr"/>
+      <c r="BH9" s="2" t="inlineStr"/>
+      <c r="BI9" s="2" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="BJ9" s="2" t="inlineStr"/>
+      <c r="BK9" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH19"/>
+  <autoFilter ref="A1:BL9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9549,7 +8313,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH6"/>
+  <dimension ref="A1:BL2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -9612,6 +8376,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9915,899 +8683,211 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr"/>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Ford Motor Company</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-08T21:56:22+08:00</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>英國法院駁回了針對汽車製造商的柴油車尾氣排放訴訟中的上訴許可申請</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr"/>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>Constellation Brands</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08T03:14:03+08:00</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>Modelo owner Constellation is getting creative to bring back beer drinkers as overall demand weakens</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr"/>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>營運惡化</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
+        </is>
+      </c>
+      <c r="K2" s="4" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="L2" s="4" t="inlineStr">
         <is>
           <t>待人工覆核</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="M2" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="N2" s="4" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>0.101</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr"/>
-      <c r="S2" s="2" t="inlineStr"/>
-      <c r="T2" s="2" t="inlineStr">
+      <c r="O2" s="4" t="inlineStr">
+        <is>
+          <t>0.294</t>
+        </is>
+      </c>
+      <c r="P2" s="4" t="inlineStr"/>
+      <c r="Q2" s="4" t="inlineStr"/>
+      <c r="R2" s="4" t="inlineStr"/>
+      <c r="S2" s="4" t="inlineStr"/>
+      <c r="T2" s="4" t="inlineStr">
         <is>
           <t>主體證據不足</t>
         </is>
       </c>
-      <c r="U2" s="2" t="inlineStr">
-        <is>
-          <t>https://tw.tradingview.com/symbols/NYSE-F/news/</t>
-        </is>
-      </c>
-      <c r="V2" s="2" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="W2" s="2" t="inlineStr"/>
-      <c r="X2" s="2" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y2" s="2" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z2" s="2" t="inlineStr">
-        <is>
-          <t>訴訟</t>
-        </is>
-      </c>
-      <c r="AA2" s="2" t="inlineStr">
+      <c r="U2" s="4" t="inlineStr">
+        <is>
+          <t>https://www.cnbc.com/2026/10/07/constellation-brands-earnings-beer-demand.html</t>
+        </is>
+      </c>
+      <c r="V2" s="4" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="W2" s="4" t="inlineStr"/>
+      <c r="X2" s="4" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y2" s="4" t="inlineStr">
+        <is>
+          <t>OPERATING_DETERIORATION</t>
+        </is>
+      </c>
+      <c r="Z2" s="4" t="inlineStr">
+        <is>
+          <t>demand weakens</t>
+        </is>
+      </c>
+      <c r="AA2" s="4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr"/>
-      <c r="AC2" s="2" t="inlineStr">
-        <is>
-          <t>298c3610ce9944a092126e67</t>
-        </is>
-      </c>
-      <c r="AD2" s="2" t="inlineStr">
-        <is>
-          <t>381d3368c6c9f41ce74590e9</t>
-        </is>
-      </c>
-      <c r="AE2" s="2" t="inlineStr">
-        <is>
-          <t>F-MAJOR_LITIGATION-001</t>
-        </is>
-      </c>
-      <c r="AF2" s="2" t="inlineStr"/>
-      <c r="AG2" s="2" t="inlineStr"/>
-      <c r="AH2" s="2" t="inlineStr"/>
-      <c r="AI2" s="2" t="inlineStr"/>
-      <c r="AJ2" s="2" t="inlineStr"/>
-      <c r="AK2" s="2" t="inlineStr"/>
-      <c r="AL2" s="2" t="inlineStr"/>
-      <c r="AM2" s="2" t="inlineStr"/>
-      <c r="AN2" s="2" t="inlineStr"/>
-      <c r="AO2" s="2" t="inlineStr">
+      <c r="AB2" s="4" t="inlineStr"/>
+      <c r="AC2" s="4" t="inlineStr">
+        <is>
+          <t>8d8850558267dbf8d0d2266f</t>
+        </is>
+      </c>
+      <c r="AD2" s="4" t="inlineStr">
+        <is>
+          <t>1f8743088a62046a79eb1e82</t>
+        </is>
+      </c>
+      <c r="AE2" s="4" t="inlineStr">
+        <is>
+          <t>STZ-OPERATING_DETERIORATION-001</t>
+        </is>
+      </c>
+      <c r="AF2" s="4" t="inlineStr"/>
+      <c r="AG2" s="4" t="inlineStr"/>
+      <c r="AH2" s="4" t="inlineStr"/>
+      <c r="AI2" s="4" t="inlineStr"/>
+      <c r="AJ2" s="4" t="inlineStr"/>
+      <c r="AK2" s="4" t="inlineStr"/>
+      <c r="AL2" s="4" t="inlineStr"/>
+      <c r="AM2" s="4" t="inlineStr"/>
+      <c r="AN2" s="4" t="inlineStr"/>
+      <c r="AO2" s="4" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AP2" s="2" t="inlineStr"/>
-      <c r="AQ2" s="2" t="inlineStr"/>
-      <c r="AR2" s="2" t="inlineStr"/>
-      <c r="AS2" s="2" t="inlineStr"/>
-      <c r="AT2" s="2" t="inlineStr"/>
-      <c r="AU2" s="2" t="inlineStr"/>
-      <c r="AV2" s="2" t="inlineStr"/>
-      <c r="AW2" s="2" t="inlineStr"/>
-      <c r="AX2" s="2" t="inlineStr"/>
-      <c r="AY2" s="2" t="inlineStr"/>
-      <c r="AZ2" s="2" t="inlineStr"/>
-      <c r="BA2" s="2" t="inlineStr"/>
-      <c r="BB2" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="BC2" s="2" t="inlineStr">
+      <c r="AP2" s="4" t="inlineStr"/>
+      <c r="AQ2" s="4" t="inlineStr"/>
+      <c r="AR2" s="4" t="inlineStr"/>
+      <c r="AS2" s="4" t="inlineStr"/>
+      <c r="AT2" s="4" t="inlineStr"/>
+      <c r="AU2" s="4" t="inlineStr"/>
+      <c r="AV2" s="4" t="inlineStr"/>
+      <c r="AW2" s="4" t="inlineStr"/>
+      <c r="AX2" s="4" t="inlineStr"/>
+      <c r="AY2" s="4" t="inlineStr"/>
+      <c r="AZ2" s="4" t="inlineStr"/>
+      <c r="BA2" s="4" t="inlineStr"/>
+      <c r="BB2" s="4" t="inlineStr">
+        <is>
+          <t>STZ</t>
+        </is>
+      </c>
+      <c r="BC2" s="4" t="inlineStr">
         <is>
           <t>主體證據不足</t>
         </is>
       </c>
-      <c r="BD2" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="BE2" s="2" t="inlineStr">
+      <c r="BD2" s="4" t="inlineStr">
+        <is>
+          <t>STZ</t>
+        </is>
+      </c>
+      <c r="BE2" s="4" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF2" s="2" t="inlineStr">
+      <c r="BF2" s="4" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG2" s="2" t="inlineStr"/>
-      <c r="BH2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr"/>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>Constellation Brands</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-08T03:14:03+08:00</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>Modelo owner Constellation is getting creative to bring back beer drinkers as overall demand weakens</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr"/>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>營運惡化</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M3" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N3" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O3" s="4" t="inlineStr">
-        <is>
-          <t>0.294</t>
-        </is>
-      </c>
-      <c r="P3" s="4" t="inlineStr"/>
-      <c r="Q3" s="4" t="inlineStr"/>
-      <c r="R3" s="4" t="inlineStr"/>
-      <c r="S3" s="4" t="inlineStr"/>
-      <c r="T3" s="4" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U3" s="4" t="inlineStr">
-        <is>
-          <t>https://www.cnbc.com/2026/10/07/constellation-brands-earnings-beer-demand.html</t>
-        </is>
-      </c>
-      <c r="V3" s="4" t="inlineStr">
-        <is>
-          <t>CNBC</t>
-        </is>
-      </c>
-      <c r="W3" s="4" t="inlineStr"/>
-      <c r="X3" s="4" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y3" s="4" t="inlineStr">
-        <is>
-          <t>OPERATING_DETERIORATION</t>
-        </is>
-      </c>
-      <c r="Z3" s="4" t="inlineStr">
-        <is>
-          <t>demand weakens</t>
-        </is>
-      </c>
-      <c r="AA3" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="4" t="inlineStr"/>
-      <c r="AC3" s="4" t="inlineStr">
-        <is>
-          <t>8d8850558267dbf8d0d2266f</t>
-        </is>
-      </c>
-      <c r="AD3" s="4" t="inlineStr">
-        <is>
-          <t>1f8743088a62046a79eb1e82</t>
-        </is>
-      </c>
-      <c r="AE3" s="4" t="inlineStr">
-        <is>
-          <t>STZ-OPERATING_DETERIORATION-001</t>
-        </is>
-      </c>
-      <c r="AF3" s="4" t="inlineStr"/>
-      <c r="AG3" s="4" t="inlineStr"/>
-      <c r="AH3" s="4" t="inlineStr"/>
-      <c r="AI3" s="4" t="inlineStr"/>
-      <c r="AJ3" s="4" t="inlineStr"/>
-      <c r="AK3" s="4" t="inlineStr"/>
-      <c r="AL3" s="4" t="inlineStr"/>
-      <c r="AM3" s="4" t="inlineStr"/>
-      <c r="AN3" s="4" t="inlineStr"/>
-      <c r="AO3" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP3" s="4" t="inlineStr"/>
-      <c r="AQ3" s="4" t="inlineStr"/>
-      <c r="AR3" s="4" t="inlineStr"/>
-      <c r="AS3" s="4" t="inlineStr"/>
-      <c r="AT3" s="4" t="inlineStr"/>
-      <c r="AU3" s="4" t="inlineStr"/>
-      <c r="AV3" s="4" t="inlineStr"/>
-      <c r="AW3" s="4" t="inlineStr"/>
-      <c r="AX3" s="4" t="inlineStr"/>
-      <c r="AY3" s="4" t="inlineStr"/>
-      <c r="AZ3" s="4" t="inlineStr"/>
-      <c r="BA3" s="4" t="inlineStr"/>
-      <c r="BB3" s="4" t="inlineStr">
-        <is>
-          <t>STZ</t>
-        </is>
-      </c>
-      <c r="BC3" s="4" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD3" s="4" t="inlineStr">
-        <is>
-          <t>STZ</t>
-        </is>
-      </c>
-      <c r="BE3" s="4" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF3" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG3" s="4" t="inlineStr"/>
-      <c r="BH3" s="4" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr"/>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Marriott International</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-08T01:16:51+08:00</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>消息人士稱，Priceline因發布誤導性酒店廣告將面臨美國聯邦貿易委員會（FTC）的處罰</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>監管調查</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0.069</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr"/>
-      <c r="Q4" s="2" t="inlineStr"/>
-      <c r="R4" s="2" t="inlineStr"/>
-      <c r="S4" s="2" t="inlineStr"/>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>https://tw.tradingview.com/symbols/NASDAQ-MAR/news/</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr"/>
-      <c r="X4" s="2" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y4" s="2" t="inlineStr">
-        <is>
-          <t>REGULATORY_INVESTIGATION</t>
-        </is>
-      </c>
-      <c r="Z4" s="2" t="inlineStr">
-        <is>
-          <t>FTC</t>
-        </is>
-      </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
-      <c r="AC4" s="2" t="inlineStr">
-        <is>
-          <t>3fa2144c2654b305167099fd</t>
-        </is>
-      </c>
-      <c r="AD4" s="2" t="inlineStr">
-        <is>
-          <t>06a16fc3d0d85d6619b772bf</t>
-        </is>
-      </c>
-      <c r="AE4" s="2" t="inlineStr">
-        <is>
-          <t>MAR-REGULATORY_INVESTIGATION-001</t>
-        </is>
-      </c>
-      <c r="AF4" s="2" t="inlineStr"/>
-      <c r="AG4" s="2" t="inlineStr"/>
-      <c r="AH4" s="2" t="inlineStr"/>
-      <c r="AI4" s="2" t="inlineStr"/>
-      <c r="AJ4" s="2" t="inlineStr"/>
-      <c r="AK4" s="2" t="inlineStr"/>
-      <c r="AL4" s="2" t="inlineStr"/>
-      <c r="AM4" s="2" t="inlineStr"/>
-      <c r="AN4" s="2" t="inlineStr"/>
-      <c r="AO4" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP4" s="2" t="inlineStr"/>
-      <c r="AQ4" s="2" t="inlineStr"/>
-      <c r="AR4" s="2" t="inlineStr"/>
-      <c r="AS4" s="2" t="inlineStr"/>
-      <c r="AT4" s="2" t="inlineStr"/>
-      <c r="AU4" s="2" t="inlineStr"/>
-      <c r="AV4" s="2" t="inlineStr"/>
-      <c r="AW4" s="2" t="inlineStr"/>
-      <c r="AX4" s="2" t="inlineStr"/>
-      <c r="AY4" s="2" t="inlineStr"/>
-      <c r="AZ4" s="2" t="inlineStr"/>
-      <c r="BA4" s="2" t="inlineStr"/>
-      <c r="BB4" s="2" t="inlineStr">
-        <is>
-          <t>MAR</t>
-        </is>
-      </c>
-      <c r="BC4" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD4" s="2" t="inlineStr">
-        <is>
-          <t>MAR</t>
-        </is>
-      </c>
-      <c r="BE4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF4" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG4" s="2" t="inlineStr"/>
-      <c r="BH4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr"/>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Booking Holdings</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-08T01:16:51+08:00</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>消息人士稱，Priceline因發布誤導性酒店廣告將面臨美國聯邦貿易委員會（FTC）的處罰</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>監管調查</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0.069</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr"/>
-      <c r="Q5" s="2" t="inlineStr"/>
-      <c r="R5" s="2" t="inlineStr"/>
-      <c r="S5" s="2" t="inlineStr"/>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>https://tw.tradingview.com/symbols/NASDAQ-BKNG/news/</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr"/>
-      <c r="X5" s="2" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y5" s="2" t="inlineStr">
-        <is>
-          <t>REGULATORY_INVESTIGATION</t>
-        </is>
-      </c>
-      <c r="Z5" s="2" t="inlineStr">
-        <is>
-          <t>FTC</t>
-        </is>
-      </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr"/>
-      <c r="AC5" s="2" t="inlineStr">
-        <is>
-          <t>6c24a6b651101bbd050a5c0b</t>
-        </is>
-      </c>
-      <c r="AD5" s="2" t="inlineStr">
-        <is>
-          <t>26926663a032f19c53fb3dcc</t>
-        </is>
-      </c>
-      <c r="AE5" s="2" t="inlineStr">
-        <is>
-          <t>BKNG-REGULATORY_INVESTIGATION-001</t>
-        </is>
-      </c>
-      <c r="AF5" s="2" t="inlineStr"/>
-      <c r="AG5" s="2" t="inlineStr"/>
-      <c r="AH5" s="2" t="inlineStr"/>
-      <c r="AI5" s="2" t="inlineStr"/>
-      <c r="AJ5" s="2" t="inlineStr"/>
-      <c r="AK5" s="2" t="inlineStr"/>
-      <c r="AL5" s="2" t="inlineStr"/>
-      <c r="AM5" s="2" t="inlineStr"/>
-      <c r="AN5" s="2" t="inlineStr"/>
-      <c r="AO5" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP5" s="2" t="inlineStr"/>
-      <c r="AQ5" s="2" t="inlineStr"/>
-      <c r="AR5" s="2" t="inlineStr"/>
-      <c r="AS5" s="2" t="inlineStr"/>
-      <c r="AT5" s="2" t="inlineStr"/>
-      <c r="AU5" s="2" t="inlineStr"/>
-      <c r="AV5" s="2" t="inlineStr"/>
-      <c r="AW5" s="2" t="inlineStr"/>
-      <c r="AX5" s="2" t="inlineStr"/>
-      <c r="AY5" s="2" t="inlineStr"/>
-      <c r="AZ5" s="2" t="inlineStr"/>
-      <c r="BA5" s="2" t="inlineStr"/>
-      <c r="BB5" s="2" t="inlineStr">
-        <is>
-          <t>BKNG</t>
-        </is>
-      </c>
-      <c r="BC5" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD5" s="2" t="inlineStr">
-        <is>
-          <t>BKNG</t>
-        </is>
-      </c>
-      <c r="BE5" s="2" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG5" s="2" t="inlineStr"/>
-      <c r="BH5" s="2" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr"/>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Expedia Group</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-08T01:16:51+08:00</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>消息人士稱，Priceline因發布誤導性酒店廣告將面臨美國聯邦貿易委員會（FTC）的處罰</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>監管調查</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>0.069</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr"/>
-      <c r="Q6" s="2" t="inlineStr"/>
-      <c r="R6" s="2" t="inlineStr"/>
-      <c r="S6" s="2" t="inlineStr"/>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>https://tw.tradingview.com/symbols/NASDAQ-EXPE/news/</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr"/>
-      <c r="X6" s="2" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y6" s="2" t="inlineStr">
-        <is>
-          <t>REGULATORY_INVESTIGATION</t>
-        </is>
-      </c>
-      <c r="Z6" s="2" t="inlineStr">
-        <is>
-          <t>FTC</t>
-        </is>
-      </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" s="2" t="inlineStr"/>
-      <c r="AC6" s="2" t="inlineStr">
-        <is>
-          <t>d25efedb84fdd99d661c0c8d</t>
-        </is>
-      </c>
-      <c r="AD6" s="2" t="inlineStr">
-        <is>
-          <t>e8fa0af2431213fe919a445f</t>
-        </is>
-      </c>
-      <c r="AE6" s="2" t="inlineStr">
-        <is>
-          <t>EXPE-REGULATORY_INVESTIGATION-001</t>
-        </is>
-      </c>
-      <c r="AF6" s="2" t="inlineStr"/>
-      <c r="AG6" s="2" t="inlineStr"/>
-      <c r="AH6" s="2" t="inlineStr"/>
-      <c r="AI6" s="2" t="inlineStr"/>
-      <c r="AJ6" s="2" t="inlineStr"/>
-      <c r="AK6" s="2" t="inlineStr"/>
-      <c r="AL6" s="2" t="inlineStr"/>
-      <c r="AM6" s="2" t="inlineStr"/>
-      <c r="AN6" s="2" t="inlineStr"/>
-      <c r="AO6" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP6" s="2" t="inlineStr"/>
-      <c r="AQ6" s="2" t="inlineStr"/>
-      <c r="AR6" s="2" t="inlineStr"/>
-      <c r="AS6" s="2" t="inlineStr"/>
-      <c r="AT6" s="2" t="inlineStr"/>
-      <c r="AU6" s="2" t="inlineStr"/>
-      <c r="AV6" s="2" t="inlineStr"/>
-      <c r="AW6" s="2" t="inlineStr"/>
-      <c r="AX6" s="2" t="inlineStr"/>
-      <c r="AY6" s="2" t="inlineStr"/>
-      <c r="AZ6" s="2" t="inlineStr"/>
-      <c r="BA6" s="2" t="inlineStr"/>
-      <c r="BB6" s="2" t="inlineStr">
-        <is>
-          <t>EXPE</t>
-        </is>
-      </c>
-      <c r="BC6" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD6" s="2" t="inlineStr">
-        <is>
-          <t>EXPE</t>
-        </is>
-      </c>
-      <c r="BE6" s="2" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF6" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG6" s="2" t="inlineStr"/>
-      <c r="BH6" s="2" t="inlineStr"/>
+      <c r="BG2" s="4" t="inlineStr"/>
+      <c r="BH2" s="4" t="inlineStr"/>
+      <c r="BI2" s="4" t="inlineStr"/>
+      <c r="BJ2" s="4" t="inlineStr"/>
+      <c r="BK2" s="4" t="inlineStr"/>
+      <c r="BL2" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH6"/>
+  <autoFilter ref="A1:BL2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10818,7 +8898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH1"/>
+  <dimension ref="A1:BL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -10881,6 +8961,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11184,9 +9268,29 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH1"/>
+  <autoFilter ref="A1:BL1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11197,7 +9301,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA5"/>
+  <dimension ref="A1:AA8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -11247,134 +9351,134 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>start</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>end</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>methods</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>ai</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>started_at</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>finished_at</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>llm_calls</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>cache_reused</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>selected_company_count</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>collected</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>rows</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>errors</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>stages</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>quota_reserved</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>重複合併</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>sources</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>rows</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>changed</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>missing_publication_time</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>ticker_statuses</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>llm_calls</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>start</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>end</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>methods</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>ai</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>cache_reused</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>review</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>major</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>selected_company_count</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>collected</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>errors</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>stages</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>quota_reserved</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>重複合併</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>ticker-audit-20261024-081549</t>
+          <t>daily-2026-10-26</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>ticker-audit</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -11384,46 +9488,80 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-24T08:15:49.296780+08:00</t>
+          <t>2026-10-25T08:20:00+08:00</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-24T08:15:49.296790+08:00</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="G2" s="3" t="n">
-        <v>1691</v>
-      </c>
-      <c r="H2" s="3" t="n">
-        <v>257</v>
-      </c>
-      <c r="I2" s="3" t="n">
+          <t>2026-10-26T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T08:23:38.366332+08:00</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T08:40:53.776257+08:00</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="L2" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>{'已核對': 1429, '主體證據不足': 218, '人工確認': 20, '市場／多公司或主體待辨識': 10, '公司名稱／股票代號歧義': 7, '公司代號待核對': 4, '非本市場上市主體': 2, '非上市機構': 1}</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="3" t="inlineStr"/>
-      <c r="M2" s="3" t="inlineStr"/>
-      <c r="N2" s="3" t="inlineStr"/>
-      <c r="O2" s="3" t="inlineStr"/>
-      <c r="P2" s="3" t="inlineStr"/>
-      <c r="Q2" s="3" t="inlineStr"/>
-      <c r="R2" s="3" t="inlineStr"/>
-      <c r="S2" s="3" t="inlineStr"/>
-      <c r="T2" s="3" t="inlineStr"/>
-      <c r="U2" s="3" t="inlineStr"/>
-      <c r="V2" s="3" t="inlineStr"/>
-      <c r="W2" s="3" t="inlineStr"/>
+      <c r="M2" s="3" t="n">
+        <v>1926</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="P2" s="3" t="n">
+        <v>503</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>1976</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>1961</v>
+      </c>
+      <c r="S2" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T2" s="3" t="inlineStr">
+        <is>
+          <t>['方法一 16 筆', '方法二 1958 筆；公司 503 家（非輪替）', '市場事件搜尋 2 筆', 'FinBERT 完成 1976 筆']</t>
+        </is>
+      </c>
+      <c r="U2" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="V2" s="3" t="n">
+        <v>1961</v>
+      </c>
+      <c r="W2" s="3" t="n">
+        <v>15</v>
+      </c>
       <c r="X2" s="3" t="inlineStr"/>
       <c r="Y2" s="3" t="inlineStr"/>
       <c r="Z2" s="3" t="inlineStr"/>
@@ -11432,12 +9570,12 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
+          <t>daily-2026-10-25</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -11447,90 +9585,94 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-24T00:26:34.299718+08:00</t>
+          <t>2026-10-24T08:20:00+08:00</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-24T00:32:11.776786+08:00</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="3" t="n">
-        <v>51</v>
-      </c>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr"/>
-      <c r="J3" s="3" t="inlineStr"/>
+          <t>2026-10-25T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:23:17.137147+08:00</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:40:12.120180+08:00</t>
+        </is>
+      </c>
       <c r="K3" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-22T00:26:32.508450+08:00</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:26:32.508450+08:00</t>
-        </is>
-      </c>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O3" s="3" t="inlineStr"/>
-      <c r="P3" s="3" t="b">
-        <v>1</v>
+        <v>35</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="3" t="n">
+        <v>2032</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="P3" s="3" t="n">
+        <v>503</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>34</v>
+        <v>2089</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" s="3" t="n">
-        <v>48</v>
-      </c>
-      <c r="T3" s="3" t="n">
-        <v>17</v>
+        <v>2067</v>
+      </c>
+      <c r="S3" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T3" s="3" t="inlineStr">
+        <is>
+          <t>['方法一 26 筆', '方法二 2059 筆；公司 503 家（非輪替）', '市場事件搜尋 6 筆', 'FinBERT 完成 2089 筆']</t>
+        </is>
       </c>
       <c r="U3" s="3" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="V3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X3" s="3" t="inlineStr">
-        <is>
-          <t>['沿用已擷取資料；不重新抓取']</t>
-        </is>
-      </c>
-      <c r="Y3" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="Z3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>2067</v>
+      </c>
+      <c r="W3" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="X3" s="3" t="inlineStr"/>
+      <c r="Y3" s="3" t="inlineStr"/>
+      <c r="Z3" s="3" t="inlineStr"/>
+      <c r="AA3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+          <t>daily-2026-10-24</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -11540,94 +9682,94 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-24T00:20:47.845317+08:00</t>
+          <t>2026-10-23T08:20:00+08:00</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-24T00:21:20.302846+08:00</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr"/>
-      <c r="G4" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr"/>
-      <c r="J4" s="3" t="inlineStr"/>
+          <t>2026-10-24T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T12:44:09.884829+08:00</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T13:04:34.984103+08:00</t>
+        </is>
+      </c>
       <c r="K4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>方法一|方法二</t>
-        </is>
-      </c>
-      <c r="P4" s="3" t="b">
-        <v>1</v>
+        <v>35</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>3760</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>503</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>2</v>
+        <v>3802</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="S4" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="T4" s="3" t="n">
-        <v>2</v>
+        <v>3825</v>
+      </c>
+      <c r="S4" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T4" s="3" t="inlineStr">
+        <is>
+          <t>['方法一 158 筆', '方法二 3638 筆；公司 503 家（非輪替）', '市場事件搜尋 8 筆', 'FinBERT 完成 3802 筆']</t>
+        </is>
       </c>
       <c r="U4" s="3" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="W4" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X4" s="3" t="inlineStr">
-        <is>
-          <t>['方法一 6 筆', '方法二 12 筆；公司 1 家（非輪替）', 'FinBERT 完成 18 筆']</t>
-        </is>
-      </c>
-      <c r="Y4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z4" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA4" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>3793</v>
+      </c>
+      <c r="W4" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="X4" s="3" t="inlineStr"/>
+      <c r="Y4" s="3" t="inlineStr"/>
+      <c r="Z4" s="3" t="inlineStr"/>
+      <c r="AA4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>ticker-audit-20261024-081549</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>ticker-audit</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -11635,89 +9777,342 @@
           <t>success</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:19:11.949238+08:00</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:19:18.833437+08:00</t>
-        </is>
-      </c>
+      <c r="D5" s="3" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr"/>
       <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="n">
-        <v>33</v>
-      </c>
+      <c r="G5" s="3" t="inlineStr"/>
       <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr"/>
-      <c r="J5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:15:49.296780+08:00</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:15:49.296790+08:00</t>
+        </is>
+      </c>
       <c r="K5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="N5" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>方法一|方法二</t>
-        </is>
-      </c>
-      <c r="P5" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="3" t="n">
-        <v>33</v>
-      </c>
+      <c r="L5" s="3" t="inlineStr"/>
+      <c r="M5" s="3" t="inlineStr"/>
+      <c r="N5" s="3" t="inlineStr"/>
+      <c r="O5" s="3" t="inlineStr"/>
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" s="3" t="inlineStr"/>
       <c r="R5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="T5" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="U5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X5" s="3" t="inlineStr">
-        <is>
-          <t>['沿用已擷取資料；不重新抓取']</t>
-        </is>
+        <v>1691</v>
+      </c>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="inlineStr"/>
+      <c r="V5" s="3" t="inlineStr"/>
+      <c r="W5" s="3" t="inlineStr"/>
+      <c r="X5" s="3" t="n">
+        <v>19</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>1</v>
+        <v>257</v>
       </c>
       <c r="Z5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AA5" s="3" t="n">
+      <c r="AA5" s="3" t="inlineStr">
+        <is>
+          <t>{'已核對': 1429, '主體證據不足': 218, '人工確認': 20, '市場／多公司或主體待辨識': 10, '公司名稱／股票代號歧義': 7, '公司代號待核對': 4, '非本市場上市主體': 2, '非上市機構': 1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22T00:26:32.508450+08:00</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:26:32.508450+08:00</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:26:34.299718+08:00</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:32:11.776786+08:00</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="M6" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="N6" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="S6" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T6" s="3" t="inlineStr">
+        <is>
+          <t>['沿用已擷取資料；不重新抓取']</t>
+        </is>
+      </c>
+      <c r="U6" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="V6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="3" t="inlineStr"/>
+      <c r="Y6" s="3" t="inlineStr"/>
+      <c r="Z6" s="3" t="inlineStr"/>
+      <c r="AA6" s="3" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:20:47.845317+08:00</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:21:20.302846+08:00</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="P7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="S7" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T7" s="3" t="inlineStr">
+        <is>
+          <t>['方法一 6 筆', '方法二 12 筆；公司 1 家（非輪替）', 'FinBERT 完成 18 筆']</t>
+        </is>
+      </c>
+      <c r="U7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="W7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" s="3" t="inlineStr"/>
+      <c r="Y7" s="3" t="inlineStr"/>
+      <c r="Z7" s="3" t="inlineStr"/>
+      <c r="AA7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:19:11.949238+08:00</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:19:18.833437+08:00</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="P8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="S8" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T8" s="3" t="inlineStr">
+        <is>
+          <t>['沿用已擷取資料；不重新抓取']</t>
+        </is>
+      </c>
+      <c r="U8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" s="3" t="inlineStr"/>
+      <c r="Y8" s="3" t="inlineStr"/>
+      <c r="Z8" s="3" t="inlineStr"/>
+      <c r="AA8" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA5"/>
+  <autoFilter ref="A1:AA8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/news_daily/2026-10-08.xlsx
+++ b/news_daily/2026-10-08.xlsx
@@ -15,8 +15,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$8</definedName>
   </definedNames>
@@ -1485,13 +1485,17 @@
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L5" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N5" s="4" t="inlineStr">
@@ -1544,7 +1548,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB5" s="4" t="inlineStr"/>
+      <c r="AB5" s="4" t="inlineStr">
+        <is>
+          <t>e0d58a2fec804f30905a2e82e28d1fb6</t>
+        </is>
+      </c>
       <c r="AC5" s="4" t="inlineStr">
         <is>
           <t>efa885a37c192ced1cafd9fe</t>
@@ -1569,7 +1577,11 @@
       <c r="AL5" s="4" t="inlineStr"/>
       <c r="AM5" s="4" t="inlineStr"/>
       <c r="AN5" s="4" t="inlineStr"/>
-      <c r="AO5" s="4" t="inlineStr"/>
+      <c r="AO5" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP5" s="4" t="inlineStr"/>
       <c r="AQ5" s="4" t="inlineStr"/>
       <c r="AR5" s="4" t="inlineStr"/>
@@ -1615,8 +1627,16 @@
       <c r="BH5" s="4" t="inlineStr"/>
       <c r="BI5" s="4" t="inlineStr"/>
       <c r="BJ5" s="4" t="inlineStr"/>
-      <c r="BK5" s="4" t="inlineStr"/>
-      <c r="BL5" s="4" t="inlineStr"/>
+      <c r="BK5" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL5" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -1667,13 +1687,17 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L6" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N6" s="4" t="inlineStr">
@@ -1726,7 +1750,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB6" s="4" t="inlineStr"/>
+      <c r="AB6" s="4" t="inlineStr">
+        <is>
+          <t>93c0768c6fd241e08d3ec3b55927507c</t>
+        </is>
+      </c>
       <c r="AC6" s="4" t="inlineStr">
         <is>
           <t>4e87e63d42d1b5cd17bf65ef</t>
@@ -1751,7 +1779,11 @@
       <c r="AL6" s="4" t="inlineStr"/>
       <c r="AM6" s="4" t="inlineStr"/>
       <c r="AN6" s="4" t="inlineStr"/>
-      <c r="AO6" s="4" t="inlineStr"/>
+      <c r="AO6" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP6" s="4" t="inlineStr"/>
       <c r="AQ6" s="4" t="inlineStr"/>
       <c r="AR6" s="4" t="inlineStr"/>
@@ -1789,8 +1821,16 @@
       <c r="BH6" s="4" t="inlineStr"/>
       <c r="BI6" s="4" t="inlineStr"/>
       <c r="BJ6" s="4" t="inlineStr"/>
-      <c r="BK6" s="4" t="inlineStr"/>
-      <c r="BL6" s="4" t="inlineStr"/>
+      <c r="BK6" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL6" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -2221,13 +2261,17 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L9" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N9" s="4" t="inlineStr">
@@ -2280,7 +2324,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB9" s="4" t="inlineStr"/>
+      <c r="AB9" s="4" t="inlineStr">
+        <is>
+          <t>e9fad3dbaa5946c4b6b561148df168bb</t>
+        </is>
+      </c>
       <c r="AC9" s="4" t="inlineStr">
         <is>
           <t>a2db2c67030d1a9d23e43a8b</t>
@@ -2305,7 +2353,11 @@
       <c r="AL9" s="4" t="inlineStr"/>
       <c r="AM9" s="4" t="inlineStr"/>
       <c r="AN9" s="4" t="inlineStr"/>
-      <c r="AO9" s="4" t="inlineStr"/>
+      <c r="AO9" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP9" s="4" t="inlineStr"/>
       <c r="AQ9" s="4" t="inlineStr"/>
       <c r="AR9" s="4" t="inlineStr"/>
@@ -2343,8 +2395,16 @@
       <c r="BH9" s="4" t="inlineStr"/>
       <c r="BI9" s="4" t="inlineStr"/>
       <c r="BJ9" s="4" t="inlineStr"/>
-      <c r="BK9" s="4" t="inlineStr"/>
-      <c r="BL9" s="4" t="inlineStr"/>
+      <c r="BK9" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL9" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -3415,186 +3475,210 @@
       <c r="BL15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>FDX</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>FedEx Corporation Common Stock</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>2026-10-08T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>PGA TOUR Studios launches 'Tee Sheet presented by FedEx,' new weekly FedExCup Playoffs preview show</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr"/>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I16" s="4" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K16" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L16" s="4" t="inlineStr"/>
-      <c r="M16" s="4" t="inlineStr">
+      <c r="G16" s="3" t="inlineStr"/>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>0.017</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr"/>
+      <c r="Q16" s="3" t="inlineStr"/>
+      <c r="R16" s="3" t="inlineStr"/>
+      <c r="S16" s="3" t="inlineStr"/>
+      <c r="T16" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqgJBVV95cUxNRjhJcmZtSldNOFRiVHFyOXpUaXNCNWhKcGx3SHg0THFxVUFhRDREQm5oTXpOS1BVcU9GT3BMWW1NVWJJbG81eEI1WktfVlJvcEh3VXY0YUxsS2t2bGRCUDdjbDJoVktnd3FuRFItc2lZWTdQVzNWTl9mUmdnV2ZtMzctYXg5UjlhVUxkY21POF9YaUpzTzRHVnVQQldIZU00d2Z5RmZfbC1LY3c0RjRWM2dkbkJmNjRjMlZvVkxSWkFFQ0JMSWdkM1FKcmdOQTdzd1ZudGxNUEZGai1GdnA5Zm4xYmJRXzFOTlNBTUR2T3h2M1AxSnRRYlZGWVhkS002dkpwVENPdzFkeFltUmZUUm9OdVBTZXJ1Si1aa3owbXdNZXZhU3dLdVZR?oc=5</t>
+        </is>
+      </c>
+      <c r="V16" s="3" t="inlineStr">
+        <is>
+          <t>PGA Tour</t>
+        </is>
+      </c>
+      <c r="W16" s="3" t="inlineStr"/>
+      <c r="X16" s="3" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y16" s="3" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z16" s="3" t="inlineStr">
+        <is>
+          <t>layoff；layoffs</t>
+        </is>
+      </c>
+      <c r="AA16" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB16" s="3" t="inlineStr">
+        <is>
+          <t>dbb8be508e314e338ea805d58305b0b6</t>
+        </is>
+      </c>
+      <c r="AC16" s="3" t="inlineStr">
+        <is>
+          <t>92096d9447cbe4262464271c</t>
+        </is>
+      </c>
+      <c r="AD16" s="3" t="inlineStr">
+        <is>
+          <t>6beb18eca6edec9226578611</t>
+        </is>
+      </c>
+      <c r="AE16" s="3" t="inlineStr">
+        <is>
+          <t>FDX-WORKFORCE_REDUCTION-001</t>
+        </is>
+      </c>
+      <c r="AF16" s="3" t="inlineStr"/>
+      <c r="AG16" s="3" t="inlineStr"/>
+      <c r="AH16" s="3" t="inlineStr"/>
+      <c r="AI16" s="3" t="inlineStr"/>
+      <c r="AJ16" s="3" t="inlineStr"/>
+      <c r="AK16" s="3" t="inlineStr"/>
+      <c r="AL16" s="3" t="inlineStr"/>
+      <c r="AM16" s="3" t="inlineStr"/>
+      <c r="AN16" s="3" t="inlineStr"/>
+      <c r="AO16" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N16" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O16" s="4" t="inlineStr">
-        <is>
-          <t>0.017</t>
-        </is>
-      </c>
-      <c r="P16" s="4" t="inlineStr"/>
-      <c r="Q16" s="4" t="inlineStr"/>
-      <c r="R16" s="4" t="inlineStr"/>
-      <c r="S16" s="4" t="inlineStr"/>
-      <c r="T16" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U16" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiqgJBVV95cUxNRjhJcmZtSldNOFRiVHFyOXpUaXNCNWhKcGx3SHg0THFxVUFhRDREQm5oTXpOS1BVcU9GT3BMWW1NVWJJbG81eEI1WktfVlJvcEh3VXY0YUxsS2t2bGRCUDdjbDJoVktnd3FuRFItc2lZWTdQVzNWTl9mUmdnV2ZtMzctYXg5UjlhVUxkY21POF9YaUpzTzRHVnVQQldIZU00d2Z5RmZfbC1LY3c0RjRWM2dkbkJmNjRjMlZvVkxSWkFFQ0JMSWdkM1FKcmdOQTdzd1ZudGxNUEZGai1GdnA5Zm4xYmJRXzFOTlNBTUR2T3h2M1AxSnRRYlZGWVhkS002dkpwVENPdzFkeFltUmZUUm9OdVBTZXJ1Si1aa3owbXdNZXZhU3dLdVZR?oc=5</t>
-        </is>
-      </c>
-      <c r="V16" s="4" t="inlineStr">
-        <is>
-          <t>PGA Tour</t>
-        </is>
-      </c>
-      <c r="W16" s="4" t="inlineStr"/>
-      <c r="X16" s="4" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y16" s="4" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z16" s="4" t="inlineStr">
-        <is>
-          <t>layoff；layoffs</t>
-        </is>
-      </c>
-      <c r="AA16" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB16" s="4" t="inlineStr"/>
-      <c r="AC16" s="4" t="inlineStr">
-        <is>
-          <t>92096d9447cbe4262464271c</t>
-        </is>
-      </c>
-      <c r="AD16" s="4" t="inlineStr">
-        <is>
-          <t>6beb18eca6edec9226578611</t>
-        </is>
-      </c>
-      <c r="AE16" s="4" t="inlineStr">
-        <is>
-          <t>FDX-WORKFORCE_REDUCTION-001</t>
-        </is>
-      </c>
-      <c r="AF16" s="4" t="inlineStr"/>
-      <c r="AG16" s="4" t="inlineStr"/>
-      <c r="AH16" s="4" t="inlineStr"/>
-      <c r="AI16" s="4" t="inlineStr"/>
-      <c r="AJ16" s="4" t="inlineStr"/>
-      <c r="AK16" s="4" t="inlineStr"/>
-      <c r="AL16" s="4" t="inlineStr"/>
-      <c r="AM16" s="4" t="inlineStr"/>
-      <c r="AN16" s="4" t="inlineStr"/>
-      <c r="AO16" s="4" t="inlineStr"/>
-      <c r="AP16" s="4" t="inlineStr"/>
-      <c r="AQ16" s="4" t="inlineStr"/>
-      <c r="AR16" s="4" t="inlineStr"/>
-      <c r="AS16" s="4" t="inlineStr"/>
-      <c r="AT16" s="4" t="inlineStr"/>
-      <c r="AU16" s="4" t="inlineStr"/>
-      <c r="AV16" s="4" t="inlineStr"/>
-      <c r="AW16" s="4" t="inlineStr">
+      <c r="AP16" s="3" t="inlineStr"/>
+      <c r="AQ16" s="3" t="inlineStr"/>
+      <c r="AR16" s="3" t="inlineStr"/>
+      <c r="AS16" s="3" t="inlineStr"/>
+      <c r="AT16" s="3" t="inlineStr"/>
+      <c r="AU16" s="3" t="inlineStr"/>
+      <c r="AV16" s="3" t="inlineStr"/>
+      <c r="AW16" s="3" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX16" s="4" t="inlineStr"/>
-      <c r="AY16" s="4" t="inlineStr"/>
-      <c r="AZ16" s="4" t="inlineStr"/>
-      <c r="BA16" s="4" t="inlineStr"/>
-      <c r="BB16" s="4" t="inlineStr">
+      <c r="AX16" s="3" t="inlineStr"/>
+      <c r="AY16" s="3" t="inlineStr"/>
+      <c r="AZ16" s="3" t="inlineStr"/>
+      <c r="BA16" s="3" t="inlineStr"/>
+      <c r="BB16" s="3" t="inlineStr">
         <is>
           <t>FDX</t>
         </is>
       </c>
-      <c r="BC16" s="4" t="inlineStr">
+      <c r="BC16" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD16" s="4" t="inlineStr"/>
-      <c r="BE16" s="4" t="inlineStr">
+      <c r="BD16" s="3" t="inlineStr"/>
+      <c r="BE16" s="3" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF16" s="4" t="inlineStr">
+      <c r="BF16" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG16" s="4" t="inlineStr">
+      <c r="BG16" s="3" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH16" s="4" t="inlineStr"/>
-      <c r="BI16" s="4" t="inlineStr"/>
-      <c r="BJ16" s="4" t="inlineStr"/>
-      <c r="BK16" s="4" t="inlineStr"/>
-      <c r="BL16" s="4" t="inlineStr"/>
+      <c r="BH16" s="3" t="inlineStr"/>
+      <c r="BI16" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ16" s="3" t="inlineStr"/>
+      <c r="BK16" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL16" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -3645,13 +3729,17 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L17" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N17" s="4" t="inlineStr">
@@ -3704,7 +3792,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB17" s="4" t="inlineStr"/>
+      <c r="AB17" s="4" t="inlineStr">
+        <is>
+          <t>55ee4b6dfa034fb78a69bc3c0e41cba6</t>
+        </is>
+      </c>
       <c r="AC17" s="4" t="inlineStr">
         <is>
           <t>86f75917141aafc70be3cb5d</t>
@@ -3729,7 +3821,11 @@
       <c r="AL17" s="4" t="inlineStr"/>
       <c r="AM17" s="4" t="inlineStr"/>
       <c r="AN17" s="4" t="inlineStr"/>
-      <c r="AO17" s="4" t="inlineStr"/>
+      <c r="AO17" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP17" s="4" t="inlineStr"/>
       <c r="AQ17" s="4" t="inlineStr"/>
       <c r="AR17" s="4" t="inlineStr"/>
@@ -3767,8 +3863,16 @@
       <c r="BH17" s="4" t="inlineStr"/>
       <c r="BI17" s="4" t="inlineStr"/>
       <c r="BJ17" s="4" t="inlineStr"/>
-      <c r="BK17" s="4" t="inlineStr"/>
-      <c r="BL17" s="4" t="inlineStr"/>
+      <c r="BK17" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL17" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -5459,7 +5563,11 @@
           <t>US</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr"/>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>STZ</t>
+        </is>
+      </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
           <t>Constellation Brands</t>
@@ -5493,17 +5601,17 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
-          <t>待人工覆核</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
@@ -5556,7 +5664,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB27" s="4" t="inlineStr"/>
+      <c r="AB27" s="4" t="inlineStr">
+        <is>
+          <t>5c34309f53664ad18e70cb8403aa39d6</t>
+        </is>
+      </c>
       <c r="AC27" s="4" t="inlineStr">
         <is>
           <t>8d8850558267dbf8d0d2266f</t>
@@ -5583,7 +5695,7 @@
       <c r="AN27" s="4" t="inlineStr"/>
       <c r="AO27" s="4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP27" s="4" t="inlineStr"/>
@@ -5625,10 +5737,22 @@
       </c>
       <c r="BG27" s="4" t="inlineStr"/>
       <c r="BH27" s="4" t="inlineStr"/>
-      <c r="BI27" s="4" t="inlineStr"/>
+      <c r="BI27" s="4" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
       <c r="BJ27" s="4" t="inlineStr"/>
-      <c r="BK27" s="4" t="inlineStr"/>
-      <c r="BL27" s="4" t="inlineStr"/>
+      <c r="BK27" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL27" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
@@ -6438,7 +6562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL9"/>
+  <dimension ref="A1:BL8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7080,13 +7204,17 @@
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M3" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N3" s="4" t="inlineStr">
@@ -7139,7 +7267,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB3" s="4" t="inlineStr"/>
+      <c r="AB3" s="4" t="inlineStr">
+        <is>
+          <t>e0d58a2fec804f30905a2e82e28d1fb6</t>
+        </is>
+      </c>
       <c r="AC3" s="4" t="inlineStr">
         <is>
           <t>efa885a37c192ced1cafd9fe</t>
@@ -7164,7 +7296,11 @@
       <c r="AL3" s="4" t="inlineStr"/>
       <c r="AM3" s="4" t="inlineStr"/>
       <c r="AN3" s="4" t="inlineStr"/>
-      <c r="AO3" s="4" t="inlineStr"/>
+      <c r="AO3" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP3" s="4" t="inlineStr"/>
       <c r="AQ3" s="4" t="inlineStr"/>
       <c r="AR3" s="4" t="inlineStr"/>
@@ -7210,8 +7346,16 @@
       <c r="BH3" s="4" t="inlineStr"/>
       <c r="BI3" s="4" t="inlineStr"/>
       <c r="BJ3" s="4" t="inlineStr"/>
-      <c r="BK3" s="4" t="inlineStr"/>
-      <c r="BL3" s="4" t="inlineStr"/>
+      <c r="BK3" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL3" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -7262,13 +7406,17 @@
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L4" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M4" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N4" s="4" t="inlineStr">
@@ -7321,7 +7469,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB4" s="4" t="inlineStr"/>
+      <c r="AB4" s="4" t="inlineStr">
+        <is>
+          <t>93c0768c6fd241e08d3ec3b55927507c</t>
+        </is>
+      </c>
       <c r="AC4" s="4" t="inlineStr">
         <is>
           <t>4e87e63d42d1b5cd17bf65ef</t>
@@ -7346,7 +7498,11 @@
       <c r="AL4" s="4" t="inlineStr"/>
       <c r="AM4" s="4" t="inlineStr"/>
       <c r="AN4" s="4" t="inlineStr"/>
-      <c r="AO4" s="4" t="inlineStr"/>
+      <c r="AO4" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP4" s="4" t="inlineStr"/>
       <c r="AQ4" s="4" t="inlineStr"/>
       <c r="AR4" s="4" t="inlineStr"/>
@@ -7384,8 +7540,16 @@
       <c r="BH4" s="4" t="inlineStr"/>
       <c r="BI4" s="4" t="inlineStr"/>
       <c r="BJ4" s="4" t="inlineStr"/>
-      <c r="BK4" s="4" t="inlineStr"/>
-      <c r="BL4" s="4" t="inlineStr"/>
+      <c r="BK4" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL4" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -7436,13 +7600,17 @@
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L5" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N5" s="4" t="inlineStr">
@@ -7495,7 +7663,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB5" s="4" t="inlineStr"/>
+      <c r="AB5" s="4" t="inlineStr">
+        <is>
+          <t>e9fad3dbaa5946c4b6b561148df168bb</t>
+        </is>
+      </c>
       <c r="AC5" s="4" t="inlineStr">
         <is>
           <t>a2db2c67030d1a9d23e43a8b</t>
@@ -7520,7 +7692,11 @@
       <c r="AL5" s="4" t="inlineStr"/>
       <c r="AM5" s="4" t="inlineStr"/>
       <c r="AN5" s="4" t="inlineStr"/>
-      <c r="AO5" s="4" t="inlineStr"/>
+      <c r="AO5" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP5" s="4" t="inlineStr"/>
       <c r="AQ5" s="4" t="inlineStr"/>
       <c r="AR5" s="4" t="inlineStr"/>
@@ -7558,8 +7734,16 @@
       <c r="BH5" s="4" t="inlineStr"/>
       <c r="BI5" s="4" t="inlineStr"/>
       <c r="BJ5" s="4" t="inlineStr"/>
-      <c r="BK5" s="4" t="inlineStr"/>
-      <c r="BL5" s="4" t="inlineStr"/>
+      <c r="BK5" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL5" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -7574,22 +7758,22 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>FDX</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>FedEx Corporation Common Stock</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T15:00:00+08:00</t>
+          <t>2026-10-08T13:00:16+08:00</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>PGA TOUR Studios launches 'Tee Sheet presented by FedEx,' new weekly FedExCup Playoffs preview show</t>
+          <t>Goldman Sachs Ensnared in EY Data Breach Earlier This Year</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr"/>
@@ -7600,7 +7784,7 @@
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>裁員或人力縮減</t>
+          <t>資料外洩</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -7610,13 +7794,17 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L6" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N6" s="4" t="inlineStr">
@@ -7626,7 +7814,7 @@
       </c>
       <c r="O6" s="4" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>'-0.847</t>
         </is>
       </c>
       <c r="P6" s="4" t="inlineStr"/>
@@ -7640,28 +7828,28 @@
       </c>
       <c r="U6" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgJBVV95cUxNRjhJcmZtSldNOFRiVHFyOXpUaXNCNWhKcGx3SHg0THFxVUFhRDREQm5oTXpOS1BVcU9GT3BMWW1NVWJJbG81eEI1WktfVlJvcEh3VXY0YUxsS2t2bGRCUDdjbDJoVktnd3FuRFItc2lZWTdQVzNWTl9mUmdnV2ZtMzctYXg5UjlhVUxkY21POF9YaUpzTzRHVnVQQldIZU00d2Z5RmZfbC1LY3c0RjRWM2dkbkJmNjRjMlZvVkxSWkFFQ0JMSWdkM1FKcmdOQTdzd1ZudGxNUEZGai1GdnA5Zm4xYmJRXzFOTlNBTUR2T3h2M1AxSnRRYlZGWVhkS002dkpwVENPdzFkeFltUmZUUm9OdVBTZXJ1Si1aa3owbXdNZXZhU3dLdVZR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE5Lc0NBNzJDeVdESGJSVWZhaFgtRnhJOC1MQm1GU3hLaFh1VnJhMk9ubFZfX2F6MnJaeUowMk5BQzF4MmZSS1UwczY5aVNWeVpwMXhmZ3YyZXh6dFVwSHpzNE90TXNQS1ZrRDdEY0ZvTGxiSTQ?oc=5</t>
         </is>
       </c>
       <c r="V6" s="4" t="inlineStr">
         <is>
-          <t>PGA Tour</t>
+          <t>Claims Journal</t>
         </is>
       </c>
       <c r="W6" s="4" t="inlineStr"/>
       <c r="X6" s="4" t="inlineStr">
         <is>
-          <t>OPERATIONS</t>
+          <t>CYBER</t>
         </is>
       </c>
       <c r="Y6" s="4" t="inlineStr">
         <is>
-          <t>WORKFORCE_REDUCTION</t>
+          <t>DATA_BREACH</t>
         </is>
       </c>
       <c r="Z6" s="4" t="inlineStr">
         <is>
-          <t>layoff；layoffs</t>
+          <t>data breach</t>
         </is>
       </c>
       <c r="AA6" s="4" t="inlineStr">
@@ -7669,20 +7857,24 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB6" s="4" t="inlineStr"/>
+      <c r="AB6" s="4" t="inlineStr">
+        <is>
+          <t>55ee4b6dfa034fb78a69bc3c0e41cba6</t>
+        </is>
+      </c>
       <c r="AC6" s="4" t="inlineStr">
         <is>
-          <t>92096d9447cbe4262464271c</t>
+          <t>86f75917141aafc70be3cb5d</t>
         </is>
       </c>
       <c r="AD6" s="4" t="inlineStr">
         <is>
-          <t>6beb18eca6edec9226578611</t>
+          <t>0c48ccb7c65f57c24ba2ac79</t>
         </is>
       </c>
       <c r="AE6" s="4" t="inlineStr">
         <is>
-          <t>FDX-WORKFORCE_REDUCTION-001</t>
+          <t>GS-DATA_BREACH-001</t>
         </is>
       </c>
       <c r="AF6" s="4" t="inlineStr"/>
@@ -7694,7 +7886,11 @@
       <c r="AL6" s="4" t="inlineStr"/>
       <c r="AM6" s="4" t="inlineStr"/>
       <c r="AN6" s="4" t="inlineStr"/>
-      <c r="AO6" s="4" t="inlineStr"/>
+      <c r="AO6" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP6" s="4" t="inlineStr"/>
       <c r="AQ6" s="4" t="inlineStr"/>
       <c r="AR6" s="4" t="inlineStr"/>
@@ -7702,18 +7898,14 @@
       <c r="AT6" s="4" t="inlineStr"/>
       <c r="AU6" s="4" t="inlineStr"/>
       <c r="AV6" s="4" t="inlineStr"/>
-      <c r="AW6" s="4" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
+      <c r="AW6" s="4" t="inlineStr"/>
       <c r="AX6" s="4" t="inlineStr"/>
       <c r="AY6" s="4" t="inlineStr"/>
       <c r="AZ6" s="4" t="inlineStr"/>
       <c r="BA6" s="4" t="inlineStr"/>
       <c r="BB6" s="4" t="inlineStr">
         <is>
-          <t>FDX</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="BC6" s="4" t="inlineStr">
@@ -7724,24 +7916,28 @@
       <c r="BD6" s="4" t="inlineStr"/>
       <c r="BE6" s="4" t="inlineStr">
         <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF6" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
+          <t>公司清單</t>
+        </is>
+      </c>
+      <c r="BF6" s="4" t="inlineStr"/>
       <c r="BG6" s="4" t="inlineStr">
         <is>
-          <t>交易所目前名單</t>
+          <t>公司清單／交易所參照</t>
         </is>
       </c>
       <c r="BH6" s="4" t="inlineStr"/>
       <c r="BI6" s="4" t="inlineStr"/>
       <c r="BJ6" s="4" t="inlineStr"/>
-      <c r="BK6" s="4" t="inlineStr"/>
-      <c r="BL6" s="4" t="inlineStr"/>
+      <c r="BK6" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL6" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -7756,22 +7952,22 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>STZ</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Constellation Brands</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T13:00:16+08:00</t>
+          <t>2026-10-08T03:14:03+08:00</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Goldman Sachs Ensnared in EY Data Breach Earlier This Year</t>
+          <t>Modelo owner Constellation is getting creative to bring back beer drinkers as overall demand weakens</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr"/>
@@ -7782,7 +7978,7 @@
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>資料外洩</t>
+          <t>營運惡化</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -7792,13 +7988,17 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L7" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N7" s="4" t="inlineStr">
@@ -7808,7 +8008,7 @@
       </c>
       <c r="O7" s="4" t="inlineStr">
         <is>
-          <t>'-0.847</t>
+          <t>0.294</t>
         </is>
       </c>
       <c r="P7" s="4" t="inlineStr"/>
@@ -7817,33 +8017,33 @@
       <c r="S7" s="4" t="inlineStr"/>
       <c r="T7" s="4" t="inlineStr">
         <is>
-          <t>公司清單／別名核對</t>
+          <t>主體證據不足</t>
         </is>
       </c>
       <c r="U7" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE5Lc0NBNzJDeVdESGJSVWZhaFgtRnhJOC1MQm1GU3hLaFh1VnJhMk9ubFZfX2F6MnJaeUowMk5BQzF4MmZSS1UwczY5aVNWeVpwMXhmZ3YyZXh6dFVwSHpzNE90TXNQS1ZrRDdEY0ZvTGxiSTQ?oc=5</t>
+          <t>https://www.cnbc.com/2026/10/07/constellation-brands-earnings-beer-demand.html</t>
         </is>
       </c>
       <c r="V7" s="4" t="inlineStr">
         <is>
-          <t>Claims Journal</t>
+          <t>CNBC</t>
         </is>
       </c>
       <c r="W7" s="4" t="inlineStr"/>
       <c r="X7" s="4" t="inlineStr">
         <is>
-          <t>CYBER</t>
+          <t>OPERATIONS</t>
         </is>
       </c>
       <c r="Y7" s="4" t="inlineStr">
         <is>
-          <t>DATA_BREACH</t>
+          <t>OPERATING_DETERIORATION</t>
         </is>
       </c>
       <c r="Z7" s="4" t="inlineStr">
         <is>
-          <t>data breach</t>
+          <t>demand weakens</t>
         </is>
       </c>
       <c r="AA7" s="4" t="inlineStr">
@@ -7851,20 +8051,24 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB7" s="4" t="inlineStr"/>
+      <c r="AB7" s="4" t="inlineStr">
+        <is>
+          <t>5c34309f53664ad18e70cb8403aa39d6</t>
+        </is>
+      </c>
       <c r="AC7" s="4" t="inlineStr">
         <is>
-          <t>86f75917141aafc70be3cb5d</t>
+          <t>8d8850558267dbf8d0d2266f</t>
         </is>
       </c>
       <c r="AD7" s="4" t="inlineStr">
         <is>
-          <t>0c48ccb7c65f57c24ba2ac79</t>
+          <t>1f8743088a62046a79eb1e82</t>
         </is>
       </c>
       <c r="AE7" s="4" t="inlineStr">
         <is>
-          <t>GS-DATA_BREACH-001</t>
+          <t>STZ-OPERATING_DETERIORATION-001</t>
         </is>
       </c>
       <c r="AF7" s="4" t="inlineStr"/>
@@ -7876,7 +8080,11 @@
       <c r="AL7" s="4" t="inlineStr"/>
       <c r="AM7" s="4" t="inlineStr"/>
       <c r="AN7" s="4" t="inlineStr"/>
-      <c r="AO7" s="4" t="inlineStr"/>
+      <c r="AO7" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP7" s="4" t="inlineStr"/>
       <c r="AQ7" s="4" t="inlineStr"/>
       <c r="AR7" s="4" t="inlineStr"/>
@@ -7891,418 +8099,252 @@
       <c r="BA7" s="4" t="inlineStr"/>
       <c r="BB7" s="4" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>STZ</t>
         </is>
       </c>
       <c r="BC7" s="4" t="inlineStr">
         <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD7" s="4" t="inlineStr"/>
+          <t>主體證據不足</t>
+        </is>
+      </c>
+      <c r="BD7" s="4" t="inlineStr">
+        <is>
+          <t>STZ</t>
+        </is>
+      </c>
       <c r="BE7" s="4" t="inlineStr">
         <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF7" s="4" t="inlineStr"/>
-      <c r="BG7" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF7" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.957209+00:00</t>
+        </is>
+      </c>
+      <c r="BG7" s="4" t="inlineStr"/>
       <c r="BH7" s="4" t="inlineStr"/>
-      <c r="BI7" s="4" t="inlineStr"/>
+      <c r="BI7" s="4" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
       <c r="BJ7" s="4" t="inlineStr"/>
-      <c r="BK7" s="4" t="inlineStr"/>
-      <c r="BL7" s="4" t="inlineStr"/>
+      <c r="BK7" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL7" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr"/>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>Constellation Brands</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-08T03:14:03+08:00</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>Modelo owner Constellation is getting creative to bring back beer drinkers as overall demand weakens</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr"/>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>營運惡化</t>
-        </is>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K8" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L8" s="4" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M8" s="4" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>BKNG</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Booking Holdings</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08T01:16:51+08:00</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>消息人士稱，Priceline因發布誤導性酒店廣告將面臨美國聯邦貿易委員會（FTC）的處罰</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>監管調查</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>0.069</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr"/>
+      <c r="Q8" s="2" t="inlineStr"/>
+      <c r="R8" s="2" t="inlineStr"/>
+      <c r="S8" s="2" t="inlineStr"/>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>主體證據不足</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>https://tw.tradingview.com/symbols/NASDAQ-BKNG/news/</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>TradingView</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr"/>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr">
+        <is>
+          <t>REGULATORY_INVESTIGATION</t>
+        </is>
+      </c>
+      <c r="Z8" s="2" t="inlineStr">
+        <is>
+          <t>FTC</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>56d54296786f4ef487a877d308e2b310</t>
+        </is>
+      </c>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>6c24a6b651101bbd050a5c0b</t>
+        </is>
+      </c>
+      <c r="AD8" s="2" t="inlineStr">
+        <is>
+          <t>26926663a032f19c53fb3dcc</t>
+        </is>
+      </c>
+      <c r="AE8" s="2" t="inlineStr">
+        <is>
+          <t>BKNG-REGULATORY_INVESTIGATION-001</t>
+        </is>
+      </c>
+      <c r="AF8" s="2" t="inlineStr"/>
+      <c r="AG8" s="2" t="inlineStr"/>
+      <c r="AH8" s="2" t="inlineStr"/>
+      <c r="AI8" s="2" t="inlineStr"/>
+      <c r="AJ8" s="2" t="inlineStr"/>
+      <c r="AK8" s="2" t="inlineStr"/>
+      <c r="AL8" s="2" t="inlineStr"/>
+      <c r="AM8" s="2" t="inlineStr"/>
+      <c r="AN8" s="2" t="inlineStr"/>
+      <c r="AO8" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N8" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O8" s="4" t="inlineStr">
-        <is>
-          <t>0.294</t>
-        </is>
-      </c>
-      <c r="P8" s="4" t="inlineStr"/>
-      <c r="Q8" s="4" t="inlineStr"/>
-      <c r="R8" s="4" t="inlineStr"/>
-      <c r="S8" s="4" t="inlineStr"/>
-      <c r="T8" s="4" t="inlineStr">
+      <c r="AP8" s="2" t="inlineStr"/>
+      <c r="AQ8" s="2" t="inlineStr"/>
+      <c r="AR8" s="2" t="inlineStr"/>
+      <c r="AS8" s="2" t="inlineStr"/>
+      <c r="AT8" s="2" t="inlineStr"/>
+      <c r="AU8" s="2" t="inlineStr"/>
+      <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" s="2" t="inlineStr"/>
+      <c r="AX8" s="2" t="inlineStr"/>
+      <c r="AY8" s="2" t="inlineStr"/>
+      <c r="AZ8" s="2" t="inlineStr"/>
+      <c r="BA8" s="2" t="inlineStr"/>
+      <c r="BB8" s="2" t="inlineStr">
+        <is>
+          <t>BKNG</t>
+        </is>
+      </c>
+      <c r="BC8" s="2" t="inlineStr">
         <is>
           <t>主體證據不足</t>
         </is>
       </c>
-      <c r="U8" s="4" t="inlineStr">
-        <is>
-          <t>https://www.cnbc.com/2026/10/07/constellation-brands-earnings-beer-demand.html</t>
-        </is>
-      </c>
-      <c r="V8" s="4" t="inlineStr">
-        <is>
-          <t>CNBC</t>
-        </is>
-      </c>
-      <c r="W8" s="4" t="inlineStr"/>
-      <c r="X8" s="4" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y8" s="4" t="inlineStr">
-        <is>
-          <t>OPERATING_DETERIORATION</t>
-        </is>
-      </c>
-      <c r="Z8" s="4" t="inlineStr">
-        <is>
-          <t>demand weakens</t>
-        </is>
-      </c>
-      <c r="AA8" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="4" t="inlineStr"/>
-      <c r="AC8" s="4" t="inlineStr">
-        <is>
-          <t>8d8850558267dbf8d0d2266f</t>
-        </is>
-      </c>
-      <c r="AD8" s="4" t="inlineStr">
-        <is>
-          <t>1f8743088a62046a79eb1e82</t>
-        </is>
-      </c>
-      <c r="AE8" s="4" t="inlineStr">
-        <is>
-          <t>STZ-OPERATING_DETERIORATION-001</t>
-        </is>
-      </c>
-      <c r="AF8" s="4" t="inlineStr"/>
-      <c r="AG8" s="4" t="inlineStr"/>
-      <c r="AH8" s="4" t="inlineStr"/>
-      <c r="AI8" s="4" t="inlineStr"/>
-      <c r="AJ8" s="4" t="inlineStr"/>
-      <c r="AK8" s="4" t="inlineStr"/>
-      <c r="AL8" s="4" t="inlineStr"/>
-      <c r="AM8" s="4" t="inlineStr"/>
-      <c r="AN8" s="4" t="inlineStr"/>
-      <c r="AO8" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP8" s="4" t="inlineStr"/>
-      <c r="AQ8" s="4" t="inlineStr"/>
-      <c r="AR8" s="4" t="inlineStr"/>
-      <c r="AS8" s="4" t="inlineStr"/>
-      <c r="AT8" s="4" t="inlineStr"/>
-      <c r="AU8" s="4" t="inlineStr"/>
-      <c r="AV8" s="4" t="inlineStr"/>
-      <c r="AW8" s="4" t="inlineStr"/>
-      <c r="AX8" s="4" t="inlineStr"/>
-      <c r="AY8" s="4" t="inlineStr"/>
-      <c r="AZ8" s="4" t="inlineStr"/>
-      <c r="BA8" s="4" t="inlineStr"/>
-      <c r="BB8" s="4" t="inlineStr">
-        <is>
-          <t>STZ</t>
-        </is>
-      </c>
-      <c r="BC8" s="4" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD8" s="4" t="inlineStr">
-        <is>
-          <t>STZ</t>
-        </is>
-      </c>
-      <c r="BE8" s="4" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF8" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG8" s="4" t="inlineStr"/>
-      <c r="BH8" s="4" t="inlineStr"/>
-      <c r="BI8" s="4" t="inlineStr"/>
-      <c r="BJ8" s="4" t="inlineStr"/>
-      <c r="BK8" s="4" t="inlineStr"/>
-      <c r="BL8" s="4" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="BD8" s="2" t="inlineStr">
         <is>
           <t>BKNG</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Booking Holdings</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-08T01:16:51+08:00</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>消息人士稱，Priceline因發布誤導性酒店廣告將面臨美國聯邦貿易委員會（FTC）的處罰</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>監管調查</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>人工覆核</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>人工覆核</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>0.069</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr"/>
-      <c r="Q9" s="2" t="inlineStr"/>
-      <c r="R9" s="2" t="inlineStr"/>
-      <c r="S9" s="2" t="inlineStr"/>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>https://tw.tradingview.com/symbols/NASDAQ-BKNG/news/</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr"/>
-      <c r="X9" s="2" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y9" s="2" t="inlineStr">
-        <is>
-          <t>REGULATORY_INVESTIGATION</t>
-        </is>
-      </c>
-      <c r="Z9" s="2" t="inlineStr">
-        <is>
-          <t>FTC</t>
-        </is>
-      </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr">
-        <is>
-          <t>56d54296786f4ef487a877d308e2b310</t>
-        </is>
-      </c>
-      <c r="AC9" s="2" t="inlineStr">
-        <is>
-          <t>6c24a6b651101bbd050a5c0b</t>
-        </is>
-      </c>
-      <c r="AD9" s="2" t="inlineStr">
-        <is>
-          <t>26926663a032f19c53fb3dcc</t>
-        </is>
-      </c>
-      <c r="AE9" s="2" t="inlineStr">
-        <is>
-          <t>BKNG-REGULATORY_INVESTIGATION-001</t>
-        </is>
-      </c>
-      <c r="AF9" s="2" t="inlineStr"/>
-      <c r="AG9" s="2" t="inlineStr"/>
-      <c r="AH9" s="2" t="inlineStr"/>
-      <c r="AI9" s="2" t="inlineStr"/>
-      <c r="AJ9" s="2" t="inlineStr"/>
-      <c r="AK9" s="2" t="inlineStr"/>
-      <c r="AL9" s="2" t="inlineStr"/>
-      <c r="AM9" s="2" t="inlineStr"/>
-      <c r="AN9" s="2" t="inlineStr"/>
-      <c r="AO9" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AP9" s="2" t="inlineStr"/>
-      <c r="AQ9" s="2" t="inlineStr"/>
-      <c r="AR9" s="2" t="inlineStr"/>
-      <c r="AS9" s="2" t="inlineStr"/>
-      <c r="AT9" s="2" t="inlineStr"/>
-      <c r="AU9" s="2" t="inlineStr"/>
-      <c r="AV9" s="2" t="inlineStr"/>
-      <c r="AW9" s="2" t="inlineStr"/>
-      <c r="AX9" s="2" t="inlineStr"/>
-      <c r="AY9" s="2" t="inlineStr"/>
-      <c r="AZ9" s="2" t="inlineStr"/>
-      <c r="BA9" s="2" t="inlineStr"/>
-      <c r="BB9" s="2" t="inlineStr">
-        <is>
-          <t>BKNG</t>
-        </is>
-      </c>
-      <c r="BC9" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD9" s="2" t="inlineStr">
-        <is>
-          <t>BKNG</t>
-        </is>
-      </c>
-      <c r="BE9" s="2" t="inlineStr">
+      <c r="BE8" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
-      <c r="BF9" s="2" t="inlineStr">
+      <c r="BF8" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
-      <c r="BG9" s="2" t="inlineStr"/>
-      <c r="BH9" s="2" t="inlineStr"/>
-      <c r="BI9" s="2" t="inlineStr">
+      <c r="BG8" s="2" t="inlineStr"/>
+      <c r="BH8" s="2" t="inlineStr"/>
+      <c r="BI8" s="2" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="BJ9" s="2" t="inlineStr"/>
-      <c r="BK9" s="2" t="inlineStr">
+      <c r="BJ8" s="2" t="inlineStr"/>
+      <c r="BK8" s="2" t="inlineStr">
         <is>
           <t>離線覆核</t>
         </is>
       </c>
-      <c r="BL9" s="2" t="inlineStr">
+      <c r="BL8" s="2" t="inlineStr">
         <is>
           <t>2026-10-26T15:42:35.885456+08:00</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BL9"/>
+  <autoFilter ref="A1:BL8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8313,7 +8355,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL2"/>
+  <dimension ref="A1:BL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -8704,190 +8746,8 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr"/>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>Constellation Brands</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-08T03:14:03+08:00</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>Modelo owner Constellation is getting creative to bring back beer drinkers as overall demand weakens</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr"/>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I2" s="4" t="inlineStr">
-        <is>
-          <t>營運惡化</t>
-        </is>
-      </c>
-      <c r="J2" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K2" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="4" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M2" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N2" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O2" s="4" t="inlineStr">
-        <is>
-          <t>0.294</t>
-        </is>
-      </c>
-      <c r="P2" s="4" t="inlineStr"/>
-      <c r="Q2" s="4" t="inlineStr"/>
-      <c r="R2" s="4" t="inlineStr"/>
-      <c r="S2" s="4" t="inlineStr"/>
-      <c r="T2" s="4" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U2" s="4" t="inlineStr">
-        <is>
-          <t>https://www.cnbc.com/2026/10/07/constellation-brands-earnings-beer-demand.html</t>
-        </is>
-      </c>
-      <c r="V2" s="4" t="inlineStr">
-        <is>
-          <t>CNBC</t>
-        </is>
-      </c>
-      <c r="W2" s="4" t="inlineStr"/>
-      <c r="X2" s="4" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y2" s="4" t="inlineStr">
-        <is>
-          <t>OPERATING_DETERIORATION</t>
-        </is>
-      </c>
-      <c r="Z2" s="4" t="inlineStr">
-        <is>
-          <t>demand weakens</t>
-        </is>
-      </c>
-      <c r="AA2" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="4" t="inlineStr"/>
-      <c r="AC2" s="4" t="inlineStr">
-        <is>
-          <t>8d8850558267dbf8d0d2266f</t>
-        </is>
-      </c>
-      <c r="AD2" s="4" t="inlineStr">
-        <is>
-          <t>1f8743088a62046a79eb1e82</t>
-        </is>
-      </c>
-      <c r="AE2" s="4" t="inlineStr">
-        <is>
-          <t>STZ-OPERATING_DETERIORATION-001</t>
-        </is>
-      </c>
-      <c r="AF2" s="4" t="inlineStr"/>
-      <c r="AG2" s="4" t="inlineStr"/>
-      <c r="AH2" s="4" t="inlineStr"/>
-      <c r="AI2" s="4" t="inlineStr"/>
-      <c r="AJ2" s="4" t="inlineStr"/>
-      <c r="AK2" s="4" t="inlineStr"/>
-      <c r="AL2" s="4" t="inlineStr"/>
-      <c r="AM2" s="4" t="inlineStr"/>
-      <c r="AN2" s="4" t="inlineStr"/>
-      <c r="AO2" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP2" s="4" t="inlineStr"/>
-      <c r="AQ2" s="4" t="inlineStr"/>
-      <c r="AR2" s="4" t="inlineStr"/>
-      <c r="AS2" s="4" t="inlineStr"/>
-      <c r="AT2" s="4" t="inlineStr"/>
-      <c r="AU2" s="4" t="inlineStr"/>
-      <c r="AV2" s="4" t="inlineStr"/>
-      <c r="AW2" s="4" t="inlineStr"/>
-      <c r="AX2" s="4" t="inlineStr"/>
-      <c r="AY2" s="4" t="inlineStr"/>
-      <c r="AZ2" s="4" t="inlineStr"/>
-      <c r="BA2" s="4" t="inlineStr"/>
-      <c r="BB2" s="4" t="inlineStr">
-        <is>
-          <t>STZ</t>
-        </is>
-      </c>
-      <c r="BC2" s="4" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD2" s="4" t="inlineStr">
-        <is>
-          <t>STZ</t>
-        </is>
-      </c>
-      <c r="BE2" s="4" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF2" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG2" s="4" t="inlineStr"/>
-      <c r="BH2" s="4" t="inlineStr"/>
-      <c r="BI2" s="4" t="inlineStr"/>
-      <c r="BJ2" s="4" t="inlineStr"/>
-      <c r="BK2" s="4" t="inlineStr"/>
-      <c r="BL2" s="4" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:BL2"/>
+  <autoFilter ref="A1:BL1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/news_daily/2026-10-08.xlsx
+++ b/news_daily/2026-10-08.xlsx
@@ -1090,28 +1090,32 @@
       <c r="G3" s="3" t="inlineStr"/>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
@@ -1151,7 +1155,7 @@
       </c>
       <c r="Y3" s="3" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z3" s="3" t="inlineStr">
@@ -1164,7 +1168,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB3" s="3" t="inlineStr"/>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>0f0f4ba6de04464fa2e46c4d447f860c</t>
+        </is>
+      </c>
       <c r="AC3" s="3" t="inlineStr">
         <is>
           <t>5626290fb8f91f33b57f7a63</t>
@@ -1189,7 +1197,11 @@
       <c r="AL3" s="3" t="inlineStr"/>
       <c r="AM3" s="3" t="inlineStr"/>
       <c r="AN3" s="3" t="inlineStr"/>
-      <c r="AO3" s="3" t="inlineStr"/>
+      <c r="AO3" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP3" s="3" t="inlineStr"/>
       <c r="AQ3" s="3" t="inlineStr"/>
       <c r="AR3" s="3" t="inlineStr"/>
@@ -1225,10 +1237,22 @@
         </is>
       </c>
       <c r="BH3" s="3" t="inlineStr"/>
-      <c r="BI3" s="3" t="inlineStr"/>
+      <c r="BI3" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ3" s="3" t="inlineStr"/>
-      <c r="BK3" s="3" t="inlineStr"/>
-      <c r="BL3" s="3" t="inlineStr"/>
+      <c r="BK3" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL3" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -2064,28 +2088,32 @@
       <c r="G8" s="3" t="inlineStr"/>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
@@ -2125,7 +2153,7 @@
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z8" s="3" t="inlineStr">
@@ -2138,7 +2166,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB8" s="3" t="inlineStr"/>
+      <c r="AB8" s="3" t="inlineStr">
+        <is>
+          <t>ec85fca9dba14c1d82e7f1336f3bf92f</t>
+        </is>
+      </c>
       <c r="AC8" s="3" t="inlineStr">
         <is>
           <t>aa1a5e357781eb3223625591</t>
@@ -2163,7 +2195,11 @@
       <c r="AL8" s="3" t="inlineStr"/>
       <c r="AM8" s="3" t="inlineStr"/>
       <c r="AN8" s="3" t="inlineStr"/>
-      <c r="AO8" s="3" t="inlineStr"/>
+      <c r="AO8" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP8" s="3" t="inlineStr"/>
       <c r="AQ8" s="3" t="inlineStr"/>
       <c r="AR8" s="3" t="inlineStr"/>
@@ -2207,10 +2243,22 @@
         </is>
       </c>
       <c r="BH8" s="3" t="inlineStr"/>
-      <c r="BI8" s="3" t="inlineStr"/>
+      <c r="BI8" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ8" s="3" t="inlineStr"/>
-      <c r="BK8" s="3" t="inlineStr"/>
-      <c r="BL8" s="3" t="inlineStr"/>
+      <c r="BK8" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL8" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -2653,13 +2701,17 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L11" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
@@ -2712,7 +2764,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB11" s="3" t="inlineStr"/>
+      <c r="AB11" s="3" t="inlineStr">
+        <is>
+          <t>f00fc57e0bfc4b37bfadf18feb3c9bde</t>
+        </is>
+      </c>
       <c r="AC11" s="3" t="inlineStr">
         <is>
           <t>813bc966d7b8684441b1c842</t>
@@ -2737,7 +2793,11 @@
       <c r="AL11" s="3" t="inlineStr"/>
       <c r="AM11" s="3" t="inlineStr"/>
       <c r="AN11" s="3" t="inlineStr"/>
-      <c r="AO11" s="3" t="inlineStr"/>
+      <c r="AO11" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP11" s="3" t="inlineStr"/>
       <c r="AQ11" s="3" t="inlineStr"/>
       <c r="AR11" s="3" t="inlineStr"/>
@@ -2775,8 +2835,16 @@
       <c r="BH11" s="3" t="inlineStr"/>
       <c r="BI11" s="3" t="inlineStr"/>
       <c r="BJ11" s="3" t="inlineStr"/>
-      <c r="BK11" s="3" t="inlineStr"/>
-      <c r="BL11" s="3" t="inlineStr"/>
+      <c r="BK11" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL11" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -2827,13 +2895,17 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L12" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
@@ -2886,7 +2958,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB12" s="3" t="inlineStr"/>
+      <c r="AB12" s="3" t="inlineStr">
+        <is>
+          <t>7200b3b149154778bf8a363cff46b3e3</t>
+        </is>
+      </c>
       <c r="AC12" s="3" t="inlineStr">
         <is>
           <t>622db825b71b2f4f41010581</t>
@@ -2911,7 +2987,11 @@
       <c r="AL12" s="3" t="inlineStr"/>
       <c r="AM12" s="3" t="inlineStr"/>
       <c r="AN12" s="3" t="inlineStr"/>
-      <c r="AO12" s="3" t="inlineStr"/>
+      <c r="AO12" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP12" s="3" t="inlineStr"/>
       <c r="AQ12" s="3" t="inlineStr"/>
       <c r="AR12" s="3" t="inlineStr"/>
@@ -2957,8 +3037,16 @@
       <c r="BH12" s="3" t="inlineStr"/>
       <c r="BI12" s="3" t="inlineStr"/>
       <c r="BJ12" s="3" t="inlineStr"/>
-      <c r="BK12" s="3" t="inlineStr"/>
-      <c r="BL12" s="3" t="inlineStr"/>
+      <c r="BK12" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL12" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -3009,13 +3097,17 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L13" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
@@ -3068,7 +3160,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB13" s="3" t="inlineStr"/>
+      <c r="AB13" s="3" t="inlineStr">
+        <is>
+          <t>ad47c121ba5e490eac9dc8462ba86652</t>
+        </is>
+      </c>
       <c r="AC13" s="3" t="inlineStr">
         <is>
           <t>c8572ab2ed8b230f447a218a</t>
@@ -3093,7 +3189,11 @@
       <c r="AL13" s="3" t="inlineStr"/>
       <c r="AM13" s="3" t="inlineStr"/>
       <c r="AN13" s="3" t="inlineStr"/>
-      <c r="AO13" s="3" t="inlineStr"/>
+      <c r="AO13" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP13" s="3" t="inlineStr"/>
       <c r="AQ13" s="3" t="inlineStr"/>
       <c r="AR13" s="3" t="inlineStr"/>
@@ -3139,8 +3239,16 @@
       <c r="BH13" s="3" t="inlineStr"/>
       <c r="BI13" s="3" t="inlineStr"/>
       <c r="BJ13" s="3" t="inlineStr"/>
-      <c r="BK13" s="3" t="inlineStr"/>
-      <c r="BL13" s="3" t="inlineStr"/>
+      <c r="BK13" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL13" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -3191,13 +3299,17 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L14" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
@@ -3250,7 +3362,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB14" s="3" t="inlineStr"/>
+      <c r="AB14" s="3" t="inlineStr">
+        <is>
+          <t>3d9ee36138b24f7ba4cdc38b801a6aac</t>
+        </is>
+      </c>
       <c r="AC14" s="3" t="inlineStr">
         <is>
           <t>546ff1e28e75e3970a4dfd1c</t>
@@ -3275,7 +3391,11 @@
       <c r="AL14" s="3" t="inlineStr"/>
       <c r="AM14" s="3" t="inlineStr"/>
       <c r="AN14" s="3" t="inlineStr"/>
-      <c r="AO14" s="3" t="inlineStr"/>
+      <c r="AO14" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP14" s="3" t="inlineStr"/>
       <c r="AQ14" s="3" t="inlineStr"/>
       <c r="AR14" s="3" t="inlineStr"/>
@@ -3313,8 +3433,16 @@
       <c r="BH14" s="3" t="inlineStr"/>
       <c r="BI14" s="3" t="inlineStr"/>
       <c r="BJ14" s="3" t="inlineStr"/>
-      <c r="BK14" s="3" t="inlineStr"/>
-      <c r="BL14" s="3" t="inlineStr"/>
+      <c r="BK14" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL14" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -3908,28 +4036,32 @@
       <c r="G18" s="3" t="inlineStr"/>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L18" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
@@ -3969,7 +4101,7 @@
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
@@ -3982,7 +4114,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB18" s="3" t="inlineStr"/>
+      <c r="AB18" s="3" t="inlineStr">
+        <is>
+          <t>7e31b36e21f640a293be638cffa59535</t>
+        </is>
+      </c>
       <c r="AC18" s="3" t="inlineStr">
         <is>
           <t>104577c9c3ccb416a54855e3</t>
@@ -4007,7 +4143,11 @@
       <c r="AL18" s="3" t="inlineStr"/>
       <c r="AM18" s="3" t="inlineStr"/>
       <c r="AN18" s="3" t="inlineStr"/>
-      <c r="AO18" s="3" t="inlineStr"/>
+      <c r="AO18" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP18" s="3" t="inlineStr"/>
       <c r="AQ18" s="3" t="inlineStr"/>
       <c r="AR18" s="3" t="inlineStr"/>
@@ -4051,10 +4191,22 @@
         </is>
       </c>
       <c r="BH18" s="3" t="inlineStr"/>
-      <c r="BI18" s="3" t="inlineStr"/>
+      <c r="BI18" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ18" s="3" t="inlineStr"/>
-      <c r="BK18" s="3" t="inlineStr"/>
-      <c r="BL18" s="3" t="inlineStr"/>
+      <c r="BK18" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL18" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -4288,28 +4440,32 @@
       <c r="G20" s="3" t="inlineStr"/>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L20" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
@@ -4349,7 +4505,7 @@
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z20" s="3" t="inlineStr">
@@ -4362,7 +4518,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB20" s="3" t="inlineStr"/>
+      <c r="AB20" s="3" t="inlineStr">
+        <is>
+          <t>32ada231479a4d26bdddb2a860275fea</t>
+        </is>
+      </c>
       <c r="AC20" s="3" t="inlineStr">
         <is>
           <t>c1f67a1fd8f79b26a049401d</t>
@@ -4387,7 +4547,11 @@
       <c r="AL20" s="3" t="inlineStr"/>
       <c r="AM20" s="3" t="inlineStr"/>
       <c r="AN20" s="3" t="inlineStr"/>
-      <c r="AO20" s="3" t="inlineStr"/>
+      <c r="AO20" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP20" s="3" t="inlineStr"/>
       <c r="AQ20" s="3" t="inlineStr"/>
       <c r="AR20" s="3" t="inlineStr"/>
@@ -4423,10 +4587,22 @@
         </is>
       </c>
       <c r="BH20" s="3" t="inlineStr"/>
-      <c r="BI20" s="3" t="inlineStr"/>
+      <c r="BI20" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ20" s="3" t="inlineStr"/>
-      <c r="BK20" s="3" t="inlineStr"/>
-      <c r="BL20" s="3" t="inlineStr"/>
+      <c r="BK20" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL20" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -5039,13 +5215,17 @@
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L24" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
@@ -5098,7 +5278,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB24" s="3" t="inlineStr"/>
+      <c r="AB24" s="3" t="inlineStr">
+        <is>
+          <t>05cecee0181048cfa4034946163f7c3b</t>
+        </is>
+      </c>
       <c r="AC24" s="3" t="inlineStr">
         <is>
           <t>d536e772e93431e05ce75aa2</t>
@@ -5123,7 +5307,11 @@
       <c r="AL24" s="3" t="inlineStr"/>
       <c r="AM24" s="3" t="inlineStr"/>
       <c r="AN24" s="3" t="inlineStr"/>
-      <c r="AO24" s="3" t="inlineStr"/>
+      <c r="AO24" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP24" s="3" t="inlineStr"/>
       <c r="AQ24" s="3" t="inlineStr"/>
       <c r="AR24" s="3" t="inlineStr"/>
@@ -5169,8 +5357,16 @@
       <c r="BH24" s="3" t="inlineStr"/>
       <c r="BI24" s="3" t="inlineStr"/>
       <c r="BJ24" s="3" t="inlineStr"/>
-      <c r="BK24" s="3" t="inlineStr"/>
-      <c r="BL24" s="3" t="inlineStr"/>
+      <c r="BK24" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL24" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
@@ -5427,13 +5623,17 @@
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L26" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
@@ -5486,7 +5686,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB26" s="3" t="inlineStr"/>
+      <c r="AB26" s="3" t="inlineStr">
+        <is>
+          <t>63a93f453ee9463bb15fbadd8fcc4024</t>
+        </is>
+      </c>
       <c r="AC26" s="3" t="inlineStr">
         <is>
           <t>ce2f2835a757d3fc5f50d9c5</t>
@@ -5511,7 +5715,11 @@
       <c r="AL26" s="3" t="inlineStr"/>
       <c r="AM26" s="3" t="inlineStr"/>
       <c r="AN26" s="3" t="inlineStr"/>
-      <c r="AO26" s="3" t="inlineStr"/>
+      <c r="AO26" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP26" s="3" t="inlineStr"/>
       <c r="AQ26" s="3" t="inlineStr"/>
       <c r="AR26" s="3" t="inlineStr"/>
@@ -5549,8 +5757,16 @@
       <c r="BH26" s="3" t="inlineStr"/>
       <c r="BI26" s="3" t="inlineStr"/>
       <c r="BJ26" s="3" t="inlineStr"/>
-      <c r="BK26" s="3" t="inlineStr"/>
-      <c r="BL26" s="3" t="inlineStr"/>
+      <c r="BK26" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL26" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">

--- a/news_daily/2026-10-08.xlsx
+++ b/news_daily/2026-10-08.xlsx
@@ -3476,10 +3476,14 @@
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr"/>
-      <c r="H15" s="3" t="inlineStr"/>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>一般公司更新</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -3492,7 +3496,11 @@
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="L15" s="3" t="inlineStr"/>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
           <t>True</t>
@@ -3535,7 +3543,7 @@
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
@@ -3548,7 +3556,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB15" s="3" t="inlineStr"/>
+      <c r="AB15" s="3" t="inlineStr">
+        <is>
+          <t>e7c2976cee68425cbbf5c21e9020ae14</t>
+        </is>
+      </c>
       <c r="AC15" s="3" t="inlineStr">
         <is>
           <t>a21436504e9b4b7baa2f629a</t>
@@ -3573,7 +3585,11 @@
       <c r="AL15" s="3" t="inlineStr"/>
       <c r="AM15" s="3" t="inlineStr"/>
       <c r="AN15" s="3" t="inlineStr"/>
-      <c r="AO15" s="3" t="inlineStr"/>
+      <c r="AO15" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP15" s="3" t="inlineStr"/>
       <c r="AQ15" s="3" t="inlineStr"/>
       <c r="AR15" s="3" t="inlineStr"/>
@@ -3597,10 +3613,22 @@
       <c r="BF15" s="3" t="inlineStr"/>
       <c r="BG15" s="3" t="inlineStr"/>
       <c r="BH15" s="3" t="inlineStr"/>
-      <c r="BI15" s="3" t="inlineStr"/>
+      <c r="BI15" s="3" t="inlineStr">
+        <is>
+          <t>Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ15" s="3" t="inlineStr"/>
-      <c r="BK15" s="3" t="inlineStr"/>
-      <c r="BL15" s="3" t="inlineStr"/>
+      <c r="BK15" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL15" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:26:33.476936+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -4842,10 +4870,14 @@
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr"/>
-      <c r="H22" s="3" t="inlineStr"/>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>一般公司更新</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -4858,7 +4890,11 @@
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="L22" s="3" t="inlineStr"/>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
           <t>True</t>
@@ -4901,7 +4937,7 @@
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t>REGULATORY_PENALTY</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z22" s="3" t="inlineStr">
@@ -4914,7 +4950,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB22" s="3" t="inlineStr"/>
+      <c r="AB22" s="3" t="inlineStr">
+        <is>
+          <t>5b4f0b6d31af415db42e2ca9da3a0a67</t>
+        </is>
+      </c>
       <c r="AC22" s="3" t="inlineStr">
         <is>
           <t>14ad2be25ebd9cf2f778c847</t>
@@ -4939,7 +4979,11 @@
       <c r="AL22" s="3" t="inlineStr"/>
       <c r="AM22" s="3" t="inlineStr"/>
       <c r="AN22" s="3" t="inlineStr"/>
-      <c r="AO22" s="3" t="inlineStr"/>
+      <c r="AO22" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP22" s="3" t="inlineStr"/>
       <c r="AQ22" s="3" t="inlineStr"/>
       <c r="AR22" s="3" t="inlineStr"/>
@@ -4963,10 +5007,22 @@
       <c r="BF22" s="3" t="inlineStr"/>
       <c r="BG22" s="3" t="inlineStr"/>
       <c r="BH22" s="3" t="inlineStr"/>
-      <c r="BI22" s="3" t="inlineStr"/>
+      <c r="BI22" s="3" t="inlineStr">
+        <is>
+          <t>Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ22" s="3" t="inlineStr"/>
-      <c r="BK22" s="3" t="inlineStr"/>
-      <c r="BL22" s="3" t="inlineStr"/>
+      <c r="BK22" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL22" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:26:33.476936+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
